--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH48"/>
+  <dimension ref="A1:BH41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
         <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G5" t="n">
         <v>5.8</v>
@@ -1354,7 +1354,7 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU6" t="n">
         <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.54</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H9" t="n">
         <v>3.5</v>
@@ -2127,7 +2127,7 @@
         <v>3.9</v>
       </c>
       <c r="J9" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K9" t="n">
         <v>3.1</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
         <v>1.94</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="H12" t="n">
         <v>3.5</v>
@@ -2709,7 +2709,7 @@
         <v>4.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
         <v>3.75</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Q13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>3.65</v>
       </c>
       <c r="G15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H15" t="n">
         <v>2.04</v>
@@ -3294,7 +3294,7 @@
         <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.81</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G16" t="n">
         <v>1.95</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>1.48</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I17" t="n">
         <v>11.5</v>
@@ -3682,7 +3682,7 @@
         <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
         <v>1.96</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G18" t="n">
         <v>2.94</v>
@@ -3870,13 +3870,13 @@
         <v>2.74</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J18" t="n">
         <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
         <v>1.76</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="H19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="G20" t="n">
         <v>2.3</v>
@@ -4264,7 +4264,7 @@
         <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>2.48</v>
       </c>
       <c r="G21" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H21" t="n">
         <v>2.8</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4476,7 +4476,7 @@
         <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G22" t="n">
         <v>2.28</v>
       </c>
       <c r="H22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
         <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -4822,62 +4822,62 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="H23" t="n">
-        <v>3.65</v>
+        <v>2.84</v>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="P23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U23" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.26</v>
-      </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
@@ -4885,123 +4885,123 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AA23" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AB23" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AF23" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI23" t="n">
-        <v>50</v>
+        <v>370</v>
       </c>
       <c r="AJ23" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AK23" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AL23" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR23" t="n">
         <v>16</v>
       </c>
-      <c r="AO23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AS23" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AX23" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>21</v>
       </c>
       <c r="BD23" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF23" t="n">
         <v>22</v>
       </c>
-      <c r="BE23" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BG23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,61 +5016,61 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>FC Ashdod</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="G24" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5079,116 +5079,116 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FC Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q26" t="n">
         <v>1.01</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="G27" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM27" t="n">
         <v>1000</v>
       </c>
-      <c r="H27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K27" t="n">
-        <v>950</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,31 +5792,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="G28" t="n">
-        <v>1.97</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K28" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -5986,31 +5986,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.74</v>
+        <v>1.86</v>
       </c>
       <c r="G29" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="I29" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="K29" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,31 +6180,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H30" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="J30" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>3.1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.07</v>
+        <v>1.41</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
         <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J31" t="n">
         <v>3.45</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -6607,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -7128,14 +7128,14 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Scottish Premiership</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7150,61 +7150,61 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.1</v>
+        <v>1.23</v>
       </c>
       <c r="G35" t="n">
-        <v>4.7</v>
+        <v>1.24</v>
       </c>
       <c r="H35" t="n">
-        <v>1.82</v>
+        <v>15</v>
       </c>
       <c r="I35" t="n">
-        <v>1.87</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="R35" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7213,116 +7213,116 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -7344,25 +7344,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="G36" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="J36" t="n">
         <v>4.7</v>
@@ -7374,31 +7374,31 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N36" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="O36" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="P36" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="R36" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S36" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="T36" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="U36" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7407,116 +7407,116 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Y36" t="n">
         <v>28</v>
       </c>
       <c r="Z36" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="AB36" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AE36" t="n">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="AF36" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG36" t="n">
         <v>10.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI36" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AJ36" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AL36" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AM36" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AN36" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO36" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AP36" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AQ36" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AS36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF36" t="n">
         <v>5.7</v>
       </c>
-      <c r="AT36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BG36" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -7538,61 +7538,61 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="G37" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="H37" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="I37" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="J37" t="n">
         <v>4.7</v>
       </c>
       <c r="K37" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N37" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="R37" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S37" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="T37" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="U37" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7601,123 +7601,123 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Y37" t="n">
         <v>28</v>
       </c>
       <c r="Z37" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AA37" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="AB37" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AC37" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AE37" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AF37" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG37" t="n">
         <v>10.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI37" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AJ37" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AK37" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AL37" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM37" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AN37" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AO37" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AP37" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AR37" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AT37" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU37" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AV37" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="AX37" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AY37" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ37" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>8.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC37" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>30</v>
+        <v>5.1</v>
       </c>
       <c r="BE37" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF37" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,61 +7732,61 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.23</v>
+        <v>4.1</v>
       </c>
       <c r="G38" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="H38" t="n">
-        <v>15</v>
+        <v>1.79</v>
       </c>
       <c r="I38" t="n">
-        <v>15.5</v>
+        <v>1.84</v>
       </c>
       <c r="J38" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="K38" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.94</v>
+        <v>2.46</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7795,116 +7795,116 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
         <v>3.45</v>
       </c>
       <c r="H39" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I39" t="n">
         <v>2.22</v>
@@ -7950,7 +7950,7 @@
         <v>3.9</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>27</v>
       </c>
       <c r="Y39" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z39" t="n">
         <v>18.5</v>
@@ -8004,7 +8004,7 @@
         <v>23</v>
       </c>
       <c r="AC39" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD39" t="n">
         <v>12.5</v>
@@ -8013,7 +8013,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG39" t="n">
         <v>15.5</v>
@@ -8028,10 +8028,10 @@
         <v>55</v>
       </c>
       <c r="AK39" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL39" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM39" t="n">
         <v>44</v>
@@ -8040,10 +8040,10 @@
         <v>19</v>
       </c>
       <c r="AO39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ39" t="n">
         <v>15.5</v>
@@ -8058,7 +8058,7 @@
         <v>20</v>
       </c>
       <c r="AU39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV39" t="n">
         <v>11</v>
@@ -8079,7 +8079,7 @@
         <v>23</v>
       </c>
       <c r="BB39" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC39" t="n">
         <v>25</v>
@@ -8094,11 +8094,11 @@
         <v>16.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -8129,16 +8129,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G40" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H40" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I40" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J40" t="n">
         <v>3.35</v>
@@ -8153,28 +8153,28 @@
         <v>1.11</v>
       </c>
       <c r="N40" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O40" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="P40" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="R40" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S40" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T40" t="n">
         <v>2.24</v>
       </c>
       <c r="U40" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8183,13 +8183,13 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y40" t="n">
         <v>10.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
@@ -8201,28 +8201,28 @@
         <v>7.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF40" t="n">
         <v>11</v>
       </c>
       <c r="AG40" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH40" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI40" t="n">
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AK40" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AL40" t="n">
         <v>1000</v>
@@ -8231,68 +8231,68 @@
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR40" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AS40" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV40" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AX40" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ40" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BA40" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BB40" t="n">
         <v>18.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BD40" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BE40" t="n">
         <v>48</v>
       </c>
       <c r="BF40" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BG40" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>
@@ -8486,1365 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 00:52:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>20:15:00</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Charlotte FC</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH42" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:52:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>CF Montreal</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J43" t="n">
-        <v>4</v>
-      </c>
-      <c r="K43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>19</v>
-      </c>
-      <c r="BH43" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:52:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Orlando City</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH44" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:52:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>FC Cincinnati</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Inter Miami CF</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="G45" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J45" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="U45" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG45" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH45" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:52:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>New England</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I46" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K46" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>15</v>
-      </c>
-      <c r="BH46" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:52:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>DC Utd</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Chicago Fire</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="G47" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H47" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U47" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>18</v>
-      </c>
-      <c r="BH47" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:52:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>New York Red Bulls</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Columbus</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="G48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H48" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH48" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:52:21</t>
+          <t>2026-05-11 03:07:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>4.9</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
         <v>1.81</v>
@@ -1372,7 +1372,7 @@
         <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -1533,28 +1533,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J6" t="n">
         <v>3.6</v>
       </c>
-      <c r="H6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K6" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1587,116 +1587,116 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.11</v>
+        <v>3.45</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.11</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.11</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.11</v>
+        <v>11.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.11</v>
+        <v>9.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.11</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.11</v>
+        <v>4.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.11</v>
+        <v>4.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.11</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.11</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.11</v>
+        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.11</v>
+        <v>4.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.11</v>
+        <v>4.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.11</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.11</v>
+        <v>13.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
         <v>2.8</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G12" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -2906,7 +2906,7 @@
         <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="H14" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>3.65</v>
       </c>
       <c r="G15" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H15" t="n">
         <v>2.04</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="G16" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H18" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I18" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J18" t="n">
         <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
         <v>2.04</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q19" t="n">
         <v>1.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>1.98</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="H20" t="n">
         <v>3.65</v>
@@ -4261,7 +4261,7 @@
         <v>4.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
         <v>4.2</v>
@@ -4282,7 +4282,7 @@
         <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.45</v>
       </c>
-      <c r="J21" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I22" t="n">
         <v>3.8</v>
@@ -4670,7 +4670,7 @@
         <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H23" t="n">
         <v>2.84</v>
@@ -4843,7 +4843,7 @@
         <v>2.92</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
         <v>3.4</v>
@@ -4918,7 +4918,7 @@
         <v>19</v>
       </c>
       <c r="AI23" t="n">
-        <v>370</v>
+        <v>65</v>
       </c>
       <c r="AJ23" t="n">
         <v>48</v>
@@ -4927,7 +4927,7 @@
         <v>36</v>
       </c>
       <c r="AL23" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4948,13 +4948,13 @@
         <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT23" t="n">
         <v>9</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
         <v>11.5</v>
@@ -4972,29 +4972,29 @@
         <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
         <v>25</v>
       </c>
       <c r="BC23" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BD23" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE23" t="n">
         <v>40</v>
       </c>
       <c r="BF23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BG23" t="n">
         <v>21</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
         <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
         <v>1000</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G27" t="n">
         <v>2.28</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
         <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
         <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J31" t="n">
         <v>3.45</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="G32" t="n">
         <v>2.06</v>
       </c>
       <c r="H32" t="n">
-        <v>1.94</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K32" t="n">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="Q32" t="n">
         <v>1.4</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="G33" t="n">
-        <v>970</v>
+        <v>1.55</v>
       </c>
       <c r="H33" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="K33" t="n">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6813,10 +6813,10 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6825,116 +6825,116 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -7171,10 +7171,10 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q35" t="n">
         <v>1.49</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="G36" t="n">
         <v>1.49</v>
@@ -7368,7 +7368,7 @@
         <v>4.7</v>
       </c>
       <c r="K36" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -7443,7 +7443,7 @@
         <v>120</v>
       </c>
       <c r="AJ36" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK36" t="n">
         <v>16</v>
@@ -7467,10 +7467,10 @@
         <v>23</v>
       </c>
       <c r="AR36" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT36" t="n">
         <v>8.199999999999999</v>
@@ -7479,7 +7479,7 @@
         <v>9.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>25</v>
+        <v>8.6</v>
       </c>
       <c r="AW36" t="n">
         <v>7.4</v>
@@ -7506,7 +7506,7 @@
         <v>30</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF36" t="n">
         <v>5.7</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>1.52</v>
       </c>
       <c r="G37" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H37" t="n">
         <v>6.2</v>
@@ -7559,7 +7559,7 @@
         <v>7</v>
       </c>
       <c r="J37" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K37" t="n">
         <v>5.3</v>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y37" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Z37" t="n">
         <v>65</v>
@@ -7616,7 +7616,7 @@
         <v>13</v>
       </c>
       <c r="AC37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD37" t="n">
         <v>26</v>
@@ -7631,7 +7631,7 @@
         <v>10.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI37" t="n">
         <v>70</v>
@@ -7685,19 +7685,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ37" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA37" t="n">
         <v>5.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC37" t="n">
         <v>11.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BE37" t="n">
         <v>5.7</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -7744,13 +7744,13 @@
         <v>4.1</v>
       </c>
       <c r="G38" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H38" t="n">
         <v>1.79</v>
       </c>
       <c r="I38" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J38" t="n">
         <v>4.1</v>
@@ -7765,16 +7765,16 @@
         <v>1.04</v>
       </c>
       <c r="N38" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O38" t="n">
         <v>1.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R38" t="n">
         <v>1.59</v>
@@ -7816,7 +7816,7 @@
         <v>10.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AF38" t="n">
         <v>42</v>
@@ -7849,43 +7849,43 @@
         <v>970</v>
       </c>
       <c r="AP38" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ38" t="n">
         <v>9.6</v>
       </c>
       <c r="AR38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW38" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AX38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY38" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>5.3</v>
       </c>
-      <c r="AZ38" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BA38" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC38" t="n">
         <v>6.2</v>
@@ -7897,14 +7897,14 @@
         <v>6.6</v>
       </c>
       <c r="BF38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG38" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -7935,19 +7935,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G39" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H39" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I39" t="n">
         <v>2.22</v>
       </c>
       <c r="J39" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K39" t="n">
         <v>3.95</v>
@@ -7992,7 +7992,7 @@
         <v>27</v>
       </c>
       <c r="Y39" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z39" t="n">
         <v>18.5</v>
@@ -8016,7 +8016,7 @@
         <v>32</v>
       </c>
       <c r="AG39" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH39" t="n">
         <v>13.5</v>
@@ -8031,7 +8031,7 @@
         <v>34</v>
       </c>
       <c r="AL39" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM39" t="n">
         <v>44</v>
@@ -8040,13 +8040,13 @@
         <v>19</v>
       </c>
       <c r="AO39" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP39" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AQ39" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR39" t="n">
         <v>16.5</v>
@@ -8061,13 +8061,13 @@
         <v>8.6</v>
       </c>
       <c r="AV39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW39" t="n">
         <v>17</v>
       </c>
       <c r="AX39" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY39" t="n">
         <v>13.5</v>
@@ -8082,7 +8082,7 @@
         <v>29</v>
       </c>
       <c r="BC39" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD39" t="n">
         <v>21</v>
@@ -8094,11 +8094,11 @@
         <v>16.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
         <v>2.26</v>
       </c>
       <c r="H40" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I40" t="n">
         <v>3.95</v>
@@ -8150,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N40" t="n">
         <v>2.78</v>
@@ -8165,13 +8165,13 @@
         <v>2.58</v>
       </c>
       <c r="R40" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S40" t="n">
         <v>5.4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U40" t="n">
         <v>1.76</v>
@@ -8183,7 +8183,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y40" t="n">
         <v>10.5</v>
@@ -8210,7 +8210,7 @@
         <v>11</v>
       </c>
       <c r="AG40" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH40" t="n">
         <v>27</v>
@@ -8264,7 +8264,7 @@
         <v>10</v>
       </c>
       <c r="AY40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ40" t="n">
         <v>24</v>
@@ -8279,7 +8279,7 @@
         <v>25</v>
       </c>
       <c r="BD40" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BE40" t="n">
         <v>48</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="G41" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H41" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K41" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -8353,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 03:07:42</t>
+          <t>2026-05-11 05:23:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH41"/>
+  <dimension ref="A1:BH42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -954,16 +954,16 @@
         <v>1.92</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
         <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q3" t="n">
         <v>2.1</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="H5" t="n">
         <v>1.81</v>
@@ -1351,10 +1351,10 @@
         <v>1.96</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
         <v>3.8</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1590,40 +1590,40 @@
         <v>16.5</v>
       </c>
       <c r="Y6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC6" t="n">
         <v>9.6</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
       </c>
       <c r="AE6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF6" t="n">
         <v>30</v>
       </c>
-      <c r="AF6" t="n">
-        <v>32</v>
-      </c>
       <c r="AG6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
         <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="n">
         <v>55</v>
@@ -1635,68 +1635,68 @@
         <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP6" t="n">
-        <v>11.5</v>
+        <v>3.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>11.5</v>
+        <v>3.35</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>2.98</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>3.25</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>3.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="AY6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB6" t="n">
         <v>4.1</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC6" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BG6" t="n">
-        <v>13.5</v>
+        <v>3.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>620</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="H8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
         <v>85</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -2118,20 +2118,20 @@
         <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H9" t="n">
         <v>3.1</v>
       </c>
       <c r="I9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>3.75</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>2.26</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>1.77</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
         <v>5.9</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="H12" t="n">
         <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G14" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="J14" t="n">
         <v>3.2</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H15" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J15" t="n">
         <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
         <v>2</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G16" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I16" t="n">
         <v>6.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3673,10 +3673,10 @@
         <v>1.48</v>
       </c>
       <c r="H17" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="I17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
         <v>4.4</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G18" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="H18" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I18" t="n">
         <v>3.45</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -4058,16 +4058,16 @@
         <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="H19" t="n">
         <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
         <v>4.6</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
         <v>1.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>1.98</v>
       </c>
       <c r="G20" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="H20" t="n">
         <v>3.65</v>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
         <v>4.2</v>
@@ -4282,7 +4282,7 @@
         <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J21" t="n">
         <v>3.45</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J22" t="n">
         <v>3.45</v>
       </c>
-      <c r="I22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,11 +4667,11 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1.89</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="G23" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="H23" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="I23" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J23" t="n">
         <v>3.35</v>
@@ -4873,10 +4873,10 @@
         <v>4.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4891,7 +4891,7 @@
         <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
         <v>48</v>
@@ -4918,10 +4918,10 @@
         <v>19</v>
       </c>
       <c r="AI23" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ23" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK23" t="n">
         <v>36</v>
@@ -4939,7 +4939,7 @@
         <v>36</v>
       </c>
       <c r="AP23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
         <v>9</v>
@@ -4948,13 +4948,13 @@
         <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
         <v>11.5</v>
@@ -4972,29 +4972,29 @@
         <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BB23" t="n">
         <v>25</v>
       </c>
       <c r="BC23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD23" t="n">
         <v>28</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>44</v>
       </c>
       <c r="BE23" t="n">
         <v>40</v>
       </c>
       <c r="BF23" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BG23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FC Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q24" t="n">
         <v>1.01</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,61 +5404,61 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J26" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>1.07</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5467,123 +5467,123 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,61 +5598,61 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Ashdod</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -5661,116 +5661,116 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J28" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="K28" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I29" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6028,7 +6028,7 @@
         <v>1.71</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G30" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="H30" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I30" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="J30" t="n">
         <v>2.68</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -6389,13 +6389,13 @@
         <v>1.99</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="I31" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J31" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="K31" t="n">
         <v>4.1</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>1.72</v>
       </c>
       <c r="G32" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="H32" t="n">
         <v>4</v>
@@ -6592,7 +6592,7 @@
         <v>3.8</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G33" t="n">
         <v>1.55</v>
       </c>
       <c r="H33" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J33" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="K33" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6813,10 +6813,10 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U33" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y33" t="n">
         <v>36</v>
       </c>
       <c r="Z33" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD33" t="n">
         <v>36</v>
@@ -6873,68 +6873,68 @@
         <v>130</v>
       </c>
       <c r="AN33" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO33" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP33" t="n">
-        <v>17.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="AU33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC33" t="n">
         <v>3.95</v>
       </c>
-      <c r="AV33" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>11</v>
-      </c>
       <c r="BD33" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -6965,19 +6965,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G34" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="H34" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I34" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -7165,17 +7165,17 @@
         <v>1.24</v>
       </c>
       <c r="H35" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J35" t="n">
+        <v>8</v>
+      </c>
+      <c r="K35" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="K35" t="n">
-        <v>8.4</v>
-      </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
@@ -7189,7 +7189,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
         <v>1.49</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G36" t="n">
         <v>1.49</v>
@@ -7362,13 +7362,13 @@
         <v>7.6</v>
       </c>
       <c r="I36" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>4.7</v>
       </c>
       <c r="K36" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -7380,22 +7380,22 @@
         <v>4.5</v>
       </c>
       <c r="O36" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P36" t="n">
         <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="R36" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S36" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="T36" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="U36" t="n">
         <v>1.92</v>
@@ -7413,19 +7413,19 @@
         <v>28</v>
       </c>
       <c r="Z36" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA36" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AB36" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC36" t="n">
         <v>11.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE36" t="n">
         <v>140</v>
@@ -7440,10 +7440,10 @@
         <v>25</v>
       </c>
       <c r="AI36" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ36" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK36" t="n">
         <v>16</v>
@@ -7455,34 +7455,34 @@
         <v>140</v>
       </c>
       <c r="AN36" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO36" t="n">
         <v>170</v>
       </c>
       <c r="AP36" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>23</v>
       </c>
       <c r="AR36" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AT36" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV36" t="n">
-        <v>8.6</v>
+        <v>25</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AX36" t="n">
         <v>8</v>
@@ -7494,7 +7494,7 @@
         <v>20</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB36" t="n">
         <v>11</v>
@@ -7503,20 +7503,20 @@
         <v>13</v>
       </c>
       <c r="BD36" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF36" t="n">
         <v>5.7</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G37" t="n">
         <v>1.57</v>
@@ -7556,28 +7556,28 @@
         <v>6.2</v>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J37" t="n">
         <v>4.6</v>
       </c>
       <c r="K37" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N37" t="n">
         <v>5.3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P37" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q37" t="n">
         <v>1.51</v>
@@ -7586,13 +7586,13 @@
         <v>1.57</v>
       </c>
       <c r="S37" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="T37" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="U37" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7604,13 +7604,13 @@
         <v>28</v>
       </c>
       <c r="Y37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z37" t="n">
         <v>65</v>
       </c>
       <c r="AA37" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AB37" t="n">
         <v>13</v>
@@ -7619,13 +7619,13 @@
         <v>13</v>
       </c>
       <c r="AD37" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE37" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF37" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG37" t="n">
         <v>10.5</v>
@@ -7634,7 +7634,7 @@
         <v>23</v>
       </c>
       <c r="AI37" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ37" t="n">
         <v>970</v>
@@ -7643,7 +7643,7 @@
         <v>970</v>
       </c>
       <c r="AL37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM37" t="n">
         <v>100</v>
@@ -7652,19 +7652,19 @@
         <v>7</v>
       </c>
       <c r="AO37" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP37" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ37" t="n">
         <v>19</v>
       </c>
       <c r="AR37" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS37" t="n">
         <v>5.5</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>5.8</v>
       </c>
       <c r="AT37" t="n">
         <v>9.800000000000001</v>
@@ -7673,10 +7673,10 @@
         <v>10</v>
       </c>
       <c r="AV37" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX37" t="n">
         <v>9.6</v>
@@ -7688,29 +7688,29 @@
         <v>16.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BB37" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC37" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BF37" t="n">
         <v>5.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -7741,16 +7741,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G38" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H38" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="I38" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="J38" t="n">
         <v>4.1</v>
@@ -7765,7 +7765,7 @@
         <v>1.04</v>
       </c>
       <c r="N38" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O38" t="n">
         <v>1.2</v>
@@ -7780,10 +7780,10 @@
         <v>1.59</v>
       </c>
       <c r="S38" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T38" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U38" t="n">
         <v>2.42</v>
@@ -7804,10 +7804,10 @@
         <v>970</v>
       </c>
       <c r="AA38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC38" t="n">
         <v>970</v>
@@ -7816,16 +7816,16 @@
         <v>10.5</v>
       </c>
       <c r="AE38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH38" t="n">
         <v>970</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>19</v>
       </c>
       <c r="AI38" t="n">
         <v>30</v>
@@ -7834,7 +7834,7 @@
         <v>95</v>
       </c>
       <c r="AK38" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL38" t="n">
         <v>55</v>
@@ -7846,31 +7846,31 @@
         <v>40</v>
       </c>
       <c r="AO38" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AP38" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ38" t="n">
         <v>9.6</v>
       </c>
       <c r="AR38" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT38" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU38" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV38" t="n">
         <v>9</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX38" t="n">
         <v>6.2</v>
@@ -7882,29 +7882,29 @@
         <v>5.3</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB38" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC38" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC38" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD38" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE38" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF38" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG38" t="n">
         <v>7.2</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G39" t="n">
         <v>3.45</v>
       </c>
-      <c r="G39" t="n">
-        <v>3.55</v>
-      </c>
       <c r="H39" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I39" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="J39" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K39" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -7971,16 +7971,16 @@
         <v>1.52</v>
       </c>
       <c r="R39" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S39" t="n">
         <v>2.26</v>
       </c>
       <c r="T39" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U39" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -7992,13 +7992,13 @@
         <v>27</v>
       </c>
       <c r="Y39" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z39" t="n">
         <v>18.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB39" t="n">
         <v>23</v>
@@ -8010,13 +8010,13 @@
         <v>12.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG39" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH39" t="n">
         <v>13.5</v>
@@ -8034,28 +8034,28 @@
         <v>36</v>
       </c>
       <c r="AM39" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AN39" t="n">
         <v>19</v>
       </c>
       <c r="AO39" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ39" t="n">
         <v>15</v>
       </c>
       <c r="AR39" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS39" t="n">
         <v>24</v>
       </c>
       <c r="AT39" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU39" t="n">
         <v>8.6</v>
@@ -8064,10 +8064,10 @@
         <v>10.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AY39" t="n">
         <v>13.5</v>
@@ -8079,26 +8079,26 @@
         <v>23</v>
       </c>
       <c r="BB39" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD39" t="n">
         <v>29</v>
       </c>
-      <c r="BC39" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>21</v>
-      </c>
       <c r="BE39" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BF39" t="n">
         <v>16.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G40" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H40" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I40" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J40" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K40" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -8153,28 +8153,28 @@
         <v>1.12</v>
       </c>
       <c r="N40" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O40" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P40" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="R40" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S40" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T40" t="n">
         <v>2.22</v>
       </c>
       <c r="U40" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8183,7 +8183,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y40" t="n">
         <v>10.5</v>
@@ -8192,37 +8192,37 @@
         <v>25</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC40" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>7.6</v>
       </c>
       <c r="AD40" t="n">
         <v>17.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG40" t="n">
         <v>12.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI40" t="n">
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK40" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL40" t="n">
         <v>1000</v>
@@ -8231,262 +8231,456 @@
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS40" t="n">
         <v>34</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU40" t="n">
         <v>7</v>
       </c>
       <c r="AV40" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW40" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AX40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY40" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ40" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA40" t="n">
         <v>36</v>
       </c>
       <c r="BB40" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC40" t="n">
         <v>25</v>
       </c>
       <c r="BD40" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE40" t="n">
         <v>48</v>
       </c>
       <c r="BF40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG40" t="n">
         <v>36</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 05:23:19</t>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-05-11 07:38:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Tolima</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F42" t="n">
         <v>2.1</v>
       </c>
-      <c r="G41" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="H41" t="n">
+      <c r="G42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J42" t="n">
         <v>3</v>
       </c>
-      <c r="I41" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K41" t="n">
+      <c r="K42" t="n">
         <v>3.65</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q42" t="n">
         <v>2.06</v>
       </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH41" t="inlineStr">
-        <is>
-          <t>2026-05-11 05:23:19</t>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-05-11 07:38:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
         <v>870</v>
       </c>
       <c r="H2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="I2" t="n">
-        <v>660</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -957,164 +957,164 @@
         <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="I5" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
         <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -1536,55 +1536,55 @@
         <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I6" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X6" t="n">
         <v>16.5</v>
@@ -1602,7 +1602,7 @@
         <v>15.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
@@ -1617,86 +1617,86 @@
         <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
         <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO6" t="n">
         <v>25</v>
       </c>
       <c r="AP6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AR6" t="n">
         <v>3.4</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AS6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA6" t="n">
         <v>3.9</v>
       </c>
-      <c r="AT6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG6" t="n">
         <v>3.6</v>
       </c>
-      <c r="BA6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -1730,167 +1730,167 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>410</v>
+        <v>600</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>620</v>
+        <v>870</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.01</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>1.06</v>
       </c>
       <c r="G8" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="H8" t="n">
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>520</v>
+        <v>870</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>85</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="H9" t="n">
         <v>3.1</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J9" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -2318,10 +2318,10 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
         <v>3.8</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="I12" t="n">
         <v>4.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="K12" t="n">
         <v>3.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="Q13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3091,13 @@
         <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I14" t="n">
         <v>3.55</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="K14" t="n">
         <v>3.75</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
         <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -3479,16 +3479,16 @@
         <v>1.76</v>
       </c>
       <c r="H16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>1.41</v>
       </c>
       <c r="G17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H17" t="n">
         <v>9.4</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J17" t="n">
         <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>1.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -3867,13 +3867,13 @@
         <v>2.82</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="I18" t="n">
         <v>3.45</v>
       </c>
       <c r="J18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>2.48</v>
       </c>
       <c r="G21" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H21" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I21" t="n">
         <v>3.15</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G22" t="n">
         <v>2.28</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G23" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I23" t="n">
         <v>2.92</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.96</v>
       </c>
       <c r="J23" t="n">
         <v>3.35</v>
@@ -4891,13 +4891,13 @@
         <v>10</v>
       </c>
       <c r="Z23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
         <v>7.4</v>
@@ -4921,13 +4921,13 @@
         <v>55</v>
       </c>
       <c r="AJ23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK23" t="n">
         <v>36</v>
       </c>
       <c r="AL23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4960,7 +4960,7 @@
         <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AX23" t="n">
         <v>16</v>
@@ -4972,7 +4972,7 @@
         <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
         <v>25</v>
@@ -4987,14 +4987,14 @@
         <v>40</v>
       </c>
       <c r="BF23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG23" t="n">
         <v>22</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H24" t="n">
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K24" t="n">
         <v>950</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H25" t="n">
         <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
         <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
         <v>1.89</v>
@@ -5458,7 +5458,7 @@
         <v>1.73</v>
       </c>
       <c r="U26" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5482,7 +5482,7 @@
         <v>11</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD26" t="n">
         <v>16</v>
@@ -5518,7 +5518,7 @@
         <v>15</v>
       </c>
       <c r="AO26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP26" t="n">
         <v>13.5</v>
@@ -5527,7 +5527,7 @@
         <v>13</v>
       </c>
       <c r="AR26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AS26" t="n">
         <v>32</v>
@@ -5557,7 +5557,7 @@
         <v>27</v>
       </c>
       <c r="BB26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5610,16 +5610,16 @@
         <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H27" t="n">
         <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K27" t="n">
         <v>950</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G28" t="n">
         <v>3.55</v>
       </c>
       <c r="H28" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I28" t="n">
         <v>3.15</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="G29" t="n">
         <v>1.97</v>
       </c>
       <c r="H29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="G30" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H30" t="n">
         <v>3.05</v>
       </c>
       <c r="I30" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J30" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="K30" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
         <v>1.99</v>
       </c>
       <c r="H31" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I31" t="n">
         <v>6.2</v>
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
         <v>1.96</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>1.4</v>
       </c>
       <c r="G33" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H33" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="I33" t="n">
         <v>10.5</v>
       </c>
       <c r="J33" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K33" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6813,10 +6813,10 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U33" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6825,25 +6825,25 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="Y33" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="Z33" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC33" t="n">
         <v>14</v>
       </c>
       <c r="AD33" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AE33" t="n">
         <v>130</v>
@@ -6855,13 +6855,13 @@
         <v>12</v>
       </c>
       <c r="AH33" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI33" t="n">
         <v>110</v>
       </c>
       <c r="AJ33" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK33" t="n">
         <v>17</v>
@@ -6882,59 +6882,59 @@
         <v>4.4</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT33" t="n">
         <v>3.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA33" t="n">
         <v>5</v>
       </c>
-      <c r="AX33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BB33" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BC33" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF33" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="BG33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>2.12</v>
       </c>
       <c r="G34" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="H34" t="n">
         <v>3.35</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -7165,13 +7165,13 @@
         <v>1.24</v>
       </c>
       <c r="H35" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="I35" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="K35" t="n">
         <v>8.199999999999999</v>
@@ -7180,31 +7180,31 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7213,116 +7213,116 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>1.47</v>
       </c>
       <c r="G36" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H36" t="n">
         <v>7.6</v>
@@ -7386,19 +7386,19 @@
         <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="R36" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S36" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="T36" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U36" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7407,10 +7407,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z36" t="n">
         <v>75</v>
@@ -7425,7 +7425,7 @@
         <v>11.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE36" t="n">
         <v>140</v>
@@ -7443,7 +7443,7 @@
         <v>110</v>
       </c>
       <c r="AJ36" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK36" t="n">
         <v>16</v>
@@ -7461,25 +7461,25 @@
         <v>170</v>
       </c>
       <c r="AP36" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ36" t="n">
         <v>23</v>
       </c>
       <c r="AR36" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS36" t="n">
         <v>10</v>
       </c>
       <c r="AT36" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU36" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV36" t="n">
-        <v>25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW36" t="n">
         <v>9</v>
@@ -7491,10 +7491,10 @@
         <v>9</v>
       </c>
       <c r="AZ36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB36" t="n">
         <v>11</v>
@@ -7506,17 +7506,17 @@
         <v>10</v>
       </c>
       <c r="BE36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF36" t="n">
         <v>5.7</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G37" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H37" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" t="n">
         <v>6.2</v>
-      </c>
-      <c r="I37" t="n">
-        <v>6.8</v>
       </c>
       <c r="J37" t="n">
         <v>4.6</v>
@@ -7577,19 +7577,19 @@
         <v>1.19</v>
       </c>
       <c r="P37" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q37" t="n">
         <v>1.51</v>
       </c>
       <c r="R37" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S37" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T37" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U37" t="n">
         <v>2.14</v>
@@ -7601,7 +7601,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y37" t="n">
         <v>32</v>
@@ -7610,7 +7610,7 @@
         <v>65</v>
       </c>
       <c r="AA37" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB37" t="n">
         <v>13</v>
@@ -7619,13 +7619,13 @@
         <v>13</v>
       </c>
       <c r="AD37" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE37" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF37" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG37" t="n">
         <v>10.5</v>
@@ -7634,7 +7634,7 @@
         <v>23</v>
       </c>
       <c r="AI37" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ37" t="n">
         <v>970</v>
@@ -7652,7 +7652,7 @@
         <v>7</v>
       </c>
       <c r="AO37" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP37" t="n">
         <v>20</v>
@@ -7661,10 +7661,10 @@
         <v>19</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT37" t="n">
         <v>9.800000000000001</v>
@@ -7673,10 +7673,10 @@
         <v>10</v>
       </c>
       <c r="AV37" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX37" t="n">
         <v>9.6</v>
@@ -7688,10 +7688,10 @@
         <v>16.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC37" t="n">
         <v>12.5</v>
@@ -7700,17 +7700,17 @@
         <v>22</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF37" t="n">
         <v>5.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -7744,13 +7744,13 @@
         <v>4.3</v>
       </c>
       <c r="G38" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
         <v>1.77</v>
       </c>
       <c r="I38" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="J38" t="n">
         <v>4.1</v>
@@ -7771,13 +7771,13 @@
         <v>1.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R38" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S38" t="n">
         <v>2.42</v>
@@ -7795,13 +7795,13 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y38" t="n">
         <v>970</v>
       </c>
       <c r="Z38" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AA38" t="n">
         <v>23</v>
@@ -7816,10 +7816,10 @@
         <v>10.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AF38" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AG38" t="n">
         <v>21</v>
@@ -7849,62 +7849,62 @@
         <v>9.4</v>
       </c>
       <c r="AP38" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ38" t="n">
         <v>9.6</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT38" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV38" t="n">
         <v>9</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX38" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY38" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BA38" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB38" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC38" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF38" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG38" t="n">
         <v>7.2</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -7935,19 +7935,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G39" t="n">
         <v>3.45</v>
       </c>
       <c r="H39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I39" t="n">
         <v>2.22</v>
       </c>
-      <c r="I39" t="n">
-        <v>2.26</v>
-      </c>
       <c r="J39" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K39" t="n">
         <v>3.9</v>
@@ -7962,19 +7962,19 @@
         <v>6.4</v>
       </c>
       <c r="O39" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P39" t="n">
         <v>2.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R39" t="n">
         <v>1.72</v>
       </c>
       <c r="S39" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="T39" t="n">
         <v>1.5</v>
@@ -7992,19 +7992,19 @@
         <v>27</v>
       </c>
       <c r="Y39" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z39" t="n">
         <v>18.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB39" t="n">
         <v>23</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD39" t="n">
         <v>12.5</v>
@@ -8016,7 +8016,7 @@
         <v>30</v>
       </c>
       <c r="AG39" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH39" t="n">
         <v>13.5</v>
@@ -8028,7 +8028,7 @@
         <v>55</v>
       </c>
       <c r="AK39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL39" t="n">
         <v>36</v>
@@ -8037,13 +8037,13 @@
         <v>46</v>
       </c>
       <c r="AN39" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO39" t="n">
         <v>9.6</v>
       </c>
       <c r="AP39" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ39" t="n">
         <v>15</v>
@@ -8067,7 +8067,7 @@
         <v>17.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AY39" t="n">
         <v>13.5</v>
@@ -8079,26 +8079,26 @@
         <v>23</v>
       </c>
       <c r="BB39" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BC39" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD39" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BE39" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF39" t="n">
         <v>16.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -8138,28 +8138,28 @@
         <v>3.7</v>
       </c>
       <c r="I40" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K40" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N40" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O40" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P40" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
         <v>2.74</v>
@@ -8171,10 +8171,10 @@
         <v>5.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U40" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -8183,7 +8183,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y40" t="n">
         <v>10.5</v>
@@ -8201,7 +8201,7 @@
         <v>7.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE40" t="n">
         <v>60</v>
@@ -8210,7 +8210,7 @@
         <v>12</v>
       </c>
       <c r="AG40" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH40" t="n">
         <v>26</v>
@@ -8237,7 +8237,7 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ40" t="n">
         <v>9.199999999999999</v>
@@ -8249,19 +8249,19 @@
         <v>34</v>
       </c>
       <c r="AT40" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU40" t="n">
         <v>7</v>
       </c>
       <c r="AV40" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AX40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY40" t="n">
         <v>11.5</v>
@@ -8273,26 +8273,26 @@
         <v>36</v>
       </c>
       <c r="BB40" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BD40" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BE40" t="n">
         <v>48</v>
       </c>
       <c r="BF40" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG40" t="n">
         <v>36</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="G41" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H41" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="I41" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="K41" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -8353,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>
@@ -8520,16 +8520,16 @@
         <v>2.1</v>
       </c>
       <c r="G42" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="H42" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
         <v>4.6</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K42" t="n">
         <v>3.65</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-11 07:38:53</t>
+          <t>2026-05-11 09:56:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH42"/>
+  <dimension ref="A1:BH44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,152 +775,152 @@
         <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
         <v>1.48</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
         <v>1.01</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
         <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -972,31 +972,31 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1008,7 +1008,7 @@
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
         <v>44</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>26</v>
@@ -1029,13 +1029,13 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1059,40 +1059,40 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.64</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AT3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AU3" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.9</v>
       </c>
       <c r="AV3" t="n">
         <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.64</v>
+        <v>8.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.56</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
@@ -1101,20 +1101,20 @@
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>2.52</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H4" t="n">
         <v>2.94</v>
       </c>
       <c r="I4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.25</v>
       </c>
       <c r="K4" t="n">
         <v>3.6</v>
@@ -1169,7 +1169,7 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.36</v>
@@ -1220,7 +1220,7 @@
         <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
@@ -1241,7 +1241,7 @@
         <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>130</v>
@@ -1265,50 +1265,50 @@
         <v>4</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AX4" t="n">
         <v>12.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.95</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
         <v>19.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1342,22 @@
         <v>4.9</v>
       </c>
       <c r="G5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="I5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1375,10 +1375,10 @@
         <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
         <v>2.02</v>
@@ -1402,7 +1402,7 @@
         <v>12.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AB5" t="n">
         <v>18.5</v>
@@ -1411,31 +1411,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AG5" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AK5" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL5" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM5" t="n">
         <v>190</v>
@@ -1444,65 +1444,65 @@
         <v>150</v>
       </c>
       <c r="AO5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY5" t="n">
         <v>18</v>
       </c>
-      <c r="AT5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="AZ5" t="n">
         <v>19</v>
       </c>
-      <c r="AX5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
         <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="I6" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
         <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
         <v>1.79</v>
@@ -1581,7 +1581,7 @@
         <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="W6" t="n">
         <v>1.36</v>
@@ -1593,22 +1593,22 @@
         <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB6" t="n">
         <v>15.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF6" t="n">
         <v>30</v>
@@ -1617,86 +1617,86 @@
         <v>18</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="n">
         <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.3</v>
+        <v>9.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.92</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.2</v>
+        <v>9.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.7</v>
+        <v>18.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.7</v>
+        <v>17.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.4</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.55</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF6" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF6" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG6" t="n">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -1730,13 +1730,13 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J7" t="n">
         <v>1.04</v>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.15</v>
@@ -1769,10 +1769,10 @@
         <v>1.15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
         <v>600</v>
       </c>
       <c r="H8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
         <v>870</v>
@@ -1936,155 +1936,155 @@
         <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P8" t="n">
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.01</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -2130,155 +2130,155 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P9" t="n">
         <v>1.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -2309,34 +2309,34 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
         <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
         <v>1.87</v>
@@ -2345,134 +2345,134 @@
         <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -2521,152 +2521,152 @@
         <v>4.7</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
         <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -2700,167 +2700,167 @@
         <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P12" t="n">
         <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="G13" t="n">
         <v>600</v>
       </c>
       <c r="H13" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="I13" t="n">
         <v>870</v>
@@ -2906,155 +2906,155 @@
         <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="P13" t="n">
-        <v>1.31</v>
+        <v>2.52</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.01</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="H14" t="n">
         <v>2.88</v>
       </c>
       <c r="I14" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="J14" t="n">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
         <v>3.75</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="I15" t="n">
         <v>2.26</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H16" t="n">
         <v>5.7</v>
@@ -3485,10 +3485,10 @@
         <v>6.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>1.41</v>
       </c>
       <c r="G17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H17" t="n">
         <v>9.4</v>
@@ -3682,7 +3682,7 @@
         <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G18" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H18" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I18" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>1.98</v>
       </c>
       <c r="G20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H20" t="n">
         <v>3.65</v>
       </c>
       <c r="I20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
         <v>4.2</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="G21" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.15</v>
       </c>
-      <c r="J21" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4476,7 +4476,7 @@
         <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J22" t="n">
         <v>3.5</v>
       </c>
-      <c r="I22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.45</v>
-      </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H23" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="I23" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>3.35</v>
@@ -4876,7 +4876,7 @@
         <v>1.95</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4894,10 +4894,10 @@
         <v>18.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC23" t="n">
         <v>7.4</v>
@@ -4939,7 +4939,7 @@
         <v>36</v>
       </c>
       <c r="AP23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>9</v>
@@ -4951,7 +4951,7 @@
         <v>26</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU23" t="n">
         <v>6.8</v>
@@ -4960,7 +4960,7 @@
         <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AX23" t="n">
         <v>16</v>
@@ -4972,7 +4972,7 @@
         <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BB23" t="n">
         <v>25</v>
@@ -4981,20 +4981,20 @@
         <v>21</v>
       </c>
       <c r="BD23" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE23" t="n">
         <v>40</v>
       </c>
       <c r="BF23" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BG23" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -5016,31 +5016,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G24" t="n">
-        <v>600</v>
+        <v>2.78</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="I24" t="n">
-        <v>870</v>
+        <v>3.25</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.07</v>
+        <v>2.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -5210,31 +5210,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="G25" t="n">
-        <v>600</v>
+        <v>2.44</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I25" t="n">
-        <v>870</v>
+        <v>5.2</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.07</v>
+        <v>1.69</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,61 +5404,61 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Ashdod</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Hapoel Jerusalem</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="G26" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="H26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.7</v>
       </c>
-      <c r="I26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5467,116 +5467,116 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -5598,31 +5598,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FC Ashdod</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Jerusalem</t>
+          <t>Hapoel Kiryat Shmona</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="G27" t="n">
-        <v>600</v>
+        <v>3.45</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="I27" t="n">
-        <v>870</v>
+        <v>3.15</v>
       </c>
       <c r="J27" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="K27" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,31 +5792,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.84</v>
+        <v>1.73</v>
       </c>
       <c r="G28" t="n">
-        <v>3.55</v>
+        <v>1.89</v>
       </c>
       <c r="H28" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="I28" t="n">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -5986,31 +5986,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.76</v>
+        <v>2.74</v>
       </c>
       <c r="G29" t="n">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="I29" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,61 +6180,61 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="G30" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="H30" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="I30" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S30" t="n">
         <v>3.2</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6243,116 +6243,116 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="G31" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="G32" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H32" t="n">
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J32" t="n">
         <v>3.8</v>
       </c>
       <c r="K32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6610,7 +6610,7 @@
         <v>2.68</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>1.4</v>
       </c>
       <c r="G33" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="H33" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J33" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="K33" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6813,7 +6813,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U33" t="n">
         <v>1.94</v>
@@ -6831,7 +6831,7 @@
         <v>950</v>
       </c>
       <c r="Z33" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
@@ -6846,7 +6846,7 @@
         <v>950</v>
       </c>
       <c r="AE33" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF33" t="n">
         <v>11</v>
@@ -6858,10 +6858,10 @@
         <v>950</v>
       </c>
       <c r="AI33" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK33" t="n">
         <v>17</v>
@@ -6870,71 +6870,71 @@
         <v>38</v>
       </c>
       <c r="AM33" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN33" t="n">
         <v>6.6</v>
       </c>
       <c r="AO33" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.4</v>
+        <v>17.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW33" t="n">
         <v>5</v>
       </c>
-      <c r="AS33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AX33" t="n">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="AY33" t="n">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="BA33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE33" t="n">
         <v>5</v>
       </c>
-      <c r="BB33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF33" t="n">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -6965,19 +6965,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G34" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H34" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I34" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J34" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
         <v>15</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="J35" t="n">
         <v>7.8</v>
@@ -7180,31 +7180,31 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O35" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P35" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R35" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="S35" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="T35" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U35" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC35" t="n">
         <v>18.5</v>
@@ -7234,19 +7234,19 @@
         <v>55</v>
       </c>
       <c r="AE35" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="AF35" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG35" t="n">
         <v>11.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI35" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ35" t="n">
         <v>9</v>
@@ -7258,71 +7258,71 @@
         <v>38</v>
       </c>
       <c r="AM35" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AO35" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="AP35" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AQ35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR35" t="n">
         <v>44</v>
       </c>
       <c r="AS35" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AT35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU35" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW35" t="n">
         <v>48</v>
       </c>
       <c r="AX35" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AY35" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA35" t="n">
         <v>44</v>
       </c>
       <c r="BB35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC35" t="n">
         <v>11.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BE35" t="n">
         <v>75</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BG35" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G36" t="n">
         <v>1.48</v>
       </c>
       <c r="H36" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J36" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K36" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -7380,7 +7380,7 @@
         <v>4.5</v>
       </c>
       <c r="O36" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P36" t="n">
         <v>2.2</v>
@@ -7392,13 +7392,13 @@
         <v>1.55</v>
       </c>
       <c r="S36" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T36" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U36" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7410,25 +7410,25 @@
         <v>21</v>
       </c>
       <c r="Y36" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Z36" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA36" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB36" t="n">
         <v>9.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AD36" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE36" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF36" t="n">
         <v>10.5</v>
@@ -7437,13 +7437,13 @@
         <v>10.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI36" t="n">
         <v>110</v>
       </c>
       <c r="AJ36" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK36" t="n">
         <v>16</v>
@@ -7455,10 +7455,10 @@
         <v>140</v>
       </c>
       <c r="AN36" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO36" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP36" t="n">
         <v>17</v>
@@ -7467,34 +7467,34 @@
         <v>23</v>
       </c>
       <c r="AR36" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS36" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AT36" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AW36" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AX36" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY36" t="n">
         <v>9</v>
       </c>
       <c r="AZ36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA36" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="BB36" t="n">
         <v>11</v>
@@ -7503,20 +7503,20 @@
         <v>13</v>
       </c>
       <c r="BD36" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BG36" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G37" t="n">
         <v>1.58</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I37" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J37" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K37" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -7577,16 +7577,16 @@
         <v>1.19</v>
       </c>
       <c r="P37" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S37" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T37" t="n">
         <v>1.73</v>
@@ -7604,13 +7604,13 @@
         <v>29</v>
       </c>
       <c r="Y37" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z37" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA37" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB37" t="n">
         <v>13</v>
@@ -7619,7 +7619,7 @@
         <v>13</v>
       </c>
       <c r="AD37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE37" t="n">
         <v>85</v>
@@ -7634,7 +7634,7 @@
         <v>23</v>
       </c>
       <c r="AI37" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ37" t="n">
         <v>970</v>
@@ -7652,19 +7652,19 @@
         <v>7</v>
       </c>
       <c r="AO37" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP37" t="n">
         <v>20</v>
       </c>
       <c r="AQ37" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT37" t="n">
         <v>9.800000000000001</v>
@@ -7673,10 +7673,10 @@
         <v>10</v>
       </c>
       <c r="AV37" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX37" t="n">
         <v>9.6</v>
@@ -7688,7 +7688,7 @@
         <v>16.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB37" t="n">
         <v>13</v>
@@ -7700,17 +7700,17 @@
         <v>22</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF37" t="n">
         <v>5.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -7744,13 +7744,13 @@
         <v>4.3</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H38" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="I38" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="J38" t="n">
         <v>4.1</v>
@@ -7771,19 +7771,19 @@
         <v>1.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T38" t="n">
         <v>1.58</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.6</v>
       </c>
       <c r="U38" t="n">
         <v>2.42</v>
@@ -7795,19 +7795,19 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="Y38" t="n">
         <v>970</v>
       </c>
       <c r="Z38" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA38" t="n">
         <v>23</v>
       </c>
       <c r="AB38" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AC38" t="n">
         <v>970</v>
@@ -7822,7 +7822,7 @@
         <v>44</v>
       </c>
       <c r="AG38" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AH38" t="n">
         <v>970</v>
@@ -7840,7 +7840,7 @@
         <v>55</v>
       </c>
       <c r="AM38" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN38" t="n">
         <v>40</v>
@@ -7849,62 +7849,62 @@
         <v>9.4</v>
       </c>
       <c r="AP38" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ38" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AS38" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV38" t="n">
         <v>9</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX38" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AY38" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AZ38" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA38" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB38" t="n">
         <v>7.4</v>
       </c>
       <c r="BC38" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF38" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG38" t="n">
         <v>7.2</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>3.4</v>
       </c>
       <c r="G39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H39" t="n">
         <v>2.2</v>
@@ -7947,10 +7947,10 @@
         <v>2.22</v>
       </c>
       <c r="J39" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K39" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -7971,7 +7971,7 @@
         <v>1.54</v>
       </c>
       <c r="R39" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S39" t="n">
         <v>2.3</v>
@@ -7989,16 +7989,16 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y39" t="n">
         <v>17.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA39" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB39" t="n">
         <v>23</v>
@@ -8007,34 +8007,34 @@
         <v>9.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF39" t="n">
         <v>30</v>
       </c>
       <c r="AG39" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH39" t="n">
         <v>13.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ39" t="n">
         <v>55</v>
       </c>
       <c r="AK39" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL39" t="n">
         <v>36</v>
       </c>
       <c r="AM39" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AN39" t="n">
         <v>19.5</v>
@@ -8052,13 +8052,13 @@
         <v>16</v>
       </c>
       <c r="AS39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT39" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU39" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV39" t="n">
         <v>10.5</v>
@@ -8067,7 +8067,7 @@
         <v>17.5</v>
       </c>
       <c r="AX39" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AY39" t="n">
         <v>13.5</v>
@@ -8079,26 +8079,26 @@
         <v>23</v>
       </c>
       <c r="BB39" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC39" t="n">
         <v>27</v>
       </c>
       <c r="BD39" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BE39" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF39" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG39" t="n">
         <v>8.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G40" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H40" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I40" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>3.25</v>
       </c>
       <c r="K40" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -8153,10 +8153,10 @@
         <v>1.13</v>
       </c>
       <c r="N40" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O40" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P40" t="n">
         <v>1.55</v>
@@ -8186,52 +8186,52 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Y40" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z40" t="n">
         <v>25</v>
       </c>
       <c r="AA40" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
         <v>7.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF40" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG40" t="n">
         <v>13</v>
       </c>
       <c r="AH40" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI40" t="n">
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK40" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM40" t="n">
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
@@ -8240,13 +8240,13 @@
         <v>8</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR40" t="n">
         <v>21</v>
       </c>
       <c r="AS40" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT40" t="n">
         <v>6.8</v>
@@ -8255,28 +8255,28 @@
         <v>7</v>
       </c>
       <c r="AV40" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW40" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AX40" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY40" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA40" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB40" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC40" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BD40" t="n">
         <v>32</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G41" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="H41" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J41" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -8353,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -8486,201 +8486,589 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 09:56:00</t>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Carabobo FC</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Estudiantes de Merida</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K42" t="n">
+        <v>950</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:37:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Deportivo Pasto</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Tolima</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F43" t="n">
         <v>2.1</v>
       </c>
-      <c r="G42" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H42" t="n">
-        <v>3</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="G43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I43" t="n">
         <v>4.6</v>
       </c>
-      <c r="J42" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K42" t="n">
+      <c r="J43" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K43" t="n">
         <v>3.65</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q43" t="n">
         <v>2.06</v>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH42" t="inlineStr">
-        <is>
-          <t>2026-05-11 09:56:00</t>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:37:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Portuguesa FC</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K44" t="n">
+        <v>950</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:37:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
         <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -784,13 +784,13 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.37</v>
@@ -984,7 +984,7 @@
         <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>1.31</v>
@@ -993,7 +993,7 @@
         <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U3" t="n">
         <v>1.98</v>
@@ -1023,13 +1023,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -1059,19 +1059,19 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AU3" t="n">
         <v>6.2</v>
@@ -1080,10 +1080,10 @@
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY3" t="n">
         <v>8.4</v>
@@ -1092,7 +1092,7 @@
         <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
@@ -1101,20 +1101,20 @@
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.52</v>
       </c>
       <c r="G4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
         <v>2.94</v>
@@ -1175,7 +1175,7 @@
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
         <v>2.06</v>
@@ -1196,7 +1196,7 @@
         <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
         <v>15.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>4.9</v>
       </c>
       <c r="G5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="J5" t="n">
         <v>3.5</v>
@@ -1357,7 +1357,7 @@
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1366,10 +1366,10 @@
         <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
         <v>2.2</v>
@@ -1384,7 +1384,7 @@
         <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1393,10 +1393,10 @@
         <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z5" t="n">
         <v>12.5</v>
@@ -1417,25 +1417,25 @@
         <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG5" t="n">
         <v>26</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AK5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL5" t="n">
         <v>110</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>120</v>
       </c>
       <c r="AM5" t="n">
         <v>190</v>
@@ -1480,29 +1480,29 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
         <v>12</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
         <v>2.08</v>
@@ -1611,7 +1611,7 @@
         <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
         <v>13.5</v>
@@ -1626,7 +1626,7 @@
         <v>60</v>
       </c>
       <c r="AK6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="n">
         <v>60</v>
@@ -1650,7 +1650,7 @@
         <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
         <v>17.5</v>
@@ -1677,13 +1677,13 @@
         <v>4.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC6" t="n">
         <v>4.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
         <v>4.6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>1.25</v>
       </c>
       <c r="H7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="I7" t="n">
         <v>24</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>1.38</v>
       </c>
       <c r="G8" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="I8" t="n">
         <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>5.5</v>
@@ -1954,7 +1954,7 @@
         <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
         <v>1.38</v>
@@ -1972,7 +1972,7 @@
         <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="X8" t="n">
         <v>17.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>2.9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I9" t="n">
         <v>3.45</v>
@@ -2163,10 +2163,10 @@
         <v>1.69</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
         <v>16</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
         <v>12.5</v>
@@ -2441,38 +2441,38 @@
         <v>18</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BA10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD10" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE10" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BG10" t="n">
         <v>13.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G11" t="n">
         <v>1.76</v>
@@ -2530,7 +2530,7 @@
         <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
         <v>2.36</v>
@@ -2650,7 +2650,7 @@
         <v>14.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD11" t="n">
         <v>3.8</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -2897,13 +2897,13 @@
         <v>1.29</v>
       </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="I13" t="n">
         <v>21</v>
       </c>
       <c r="J13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K13" t="n">
         <v>12.5</v>
@@ -2915,7 +2915,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>1.14</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G14" t="n">
         <v>2.86</v>
@@ -3115,7 +3115,7 @@
         <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -3303,22 +3303,22 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
         <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q15" t="n">
         <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>3.35</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -3497,16 +3497,16 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -3691,22 +3691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="R17" t="n">
         <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>1.72</v>
       </c>
       <c r="G18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J18" t="n">
         <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3888,13 +3888,13 @@
         <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="R18" t="n">
         <v>1.35</v>
@@ -3909,34 +3909,34 @@
         <v>1.97</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X18" t="n">
         <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Z18" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF18" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
         <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK18" t="n">
         <v>19</v>
@@ -3966,19 +3966,19 @@
         <v>11.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS18" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>15.5</v>
       </c>
       <c r="AT18" t="n">
         <v>7.4</v>
@@ -3987,10 +3987,10 @@
         <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>19.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AX18" t="n">
         <v>8.800000000000001</v>
@@ -3999,32 +3999,32 @@
         <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BB18" t="n">
         <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="H19" t="n">
         <v>9.4</v>
@@ -4085,10 +4085,10 @@
         <v>1.33</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R19" t="n">
         <v>1.31</v>
@@ -4106,7 +4106,7 @@
         <v>1.09</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="X19" t="n">
         <v>15</v>
@@ -4124,7 +4124,7 @@
         <v>7.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
         <v>40</v>
@@ -4139,10 +4139,10 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI19" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ19" t="n">
         <v>12.5</v>
@@ -4166,13 +4166,13 @@
         <v>12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT19" t="n">
         <v>5.9</v>
@@ -4181,10 +4181,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX19" t="n">
         <v>6.6</v>
@@ -4193,10 +4193,10 @@
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB19" t="n">
         <v>10</v>
@@ -4205,20 +4205,20 @@
         <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF19" t="n">
         <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
         <v>1.82</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
         <v>2.4</v>
@@ -4306,7 +4306,7 @@
         <v>25</v>
       </c>
       <c r="Y20" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z20" t="n">
         <v>30</v>
@@ -4333,7 +4333,7 @@
         <v>18</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI20" t="n">
         <v>55</v>
@@ -4351,68 +4351,68 @@
         <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="AY20" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="BC20" t="n">
         <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.4</v>
+        <v>12</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.4</v>
+        <v>14.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -4476,10 +4476,10 @@
         <v>2.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S21" t="n">
         <v>2.52</v>
@@ -4551,7 +4551,7 @@
         <v>48</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.7</v>
+        <v>17</v>
       </c>
       <c r="AQ21" t="n">
         <v>15.5</v>
@@ -4563,10 +4563,10 @@
         <v>4.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AU21" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AV21" t="n">
         <v>13</v>
@@ -4578,16 +4578,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="BA21" t="n">
         <v>3.95</v>
       </c>
       <c r="BB21" t="n">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="BC21" t="n">
         <v>12.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
         <v>2.14</v>
       </c>
       <c r="H22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
         <v>3.75</v>
@@ -4661,7 +4661,7 @@
         <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.85</v>
+        <v>2.32</v>
       </c>
       <c r="O22" t="n">
         <v>1.22</v>
@@ -4676,19 +4676,19 @@
         <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T22" t="n">
-        <v>1.51</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
         <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X22" t="n">
         <v>24</v>
@@ -4709,7 +4709,7 @@
         <v>11</v>
       </c>
       <c r="AD22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>50</v>
@@ -4745,13 +4745,13 @@
         <v>42</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.65</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
         <v>12.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="AS22" t="n">
         <v>4.1</v>
@@ -4772,7 +4772,7 @@
         <v>3.45</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
         <v>12</v>
@@ -4781,10 +4781,10 @@
         <v>4</v>
       </c>
       <c r="BB22" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="BD22" t="n">
         <v>3.85</v>
@@ -4793,14 +4793,14 @@
         <v>4.1</v>
       </c>
       <c r="BF22" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG22" t="n">
         <v>3.9</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="G23" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="H23" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="I23" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K23" t="n">
         <v>3.55</v>
@@ -4852,149 +4852,149 @@
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q23" t="n">
         <v>1.93</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>1.93</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U23" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="V23" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="W23" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X23" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH23" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>20</v>
-      </c>
       <c r="AI23" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AK23" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL23" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM23" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.12</v>
+        <v>12</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.28</v>
+        <v>36</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF23" t="n">
         <v>21</v>
       </c>
-      <c r="AX23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BG23" t="n">
-        <v>2.4</v>
+        <v>21</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -5136,59 +5136,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -5243,13 +5243,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P25" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q25" t="n">
         <v>1.24</v>
@@ -5327,52 +5327,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K26" t="n">
         <v>950</v>
@@ -5443,16 +5443,16 @@
         <v>1.21</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -5521,52 +5521,52 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -5631,13 +5631,13 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O27" t="n">
         <v>1.19</v>
       </c>
       <c r="P27" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q27" t="n">
         <v>1.19</v>
@@ -5715,52 +5715,52 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
         <v>1.01</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>2.8</v>
       </c>
       <c r="H28" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I28" t="n">
         <v>2.94</v>
@@ -5843,7 +5843,7 @@
         <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U28" t="n">
         <v>2.02</v>
@@ -5858,7 +5858,7 @@
         <v>11</v>
       </c>
       <c r="Y28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z28" t="n">
         <v>18</v>
@@ -5924,7 +5924,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>12</v>
@@ -5945,7 +5945,7 @@
         <v>46</v>
       </c>
       <c r="BB28" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BC28" t="n">
         <v>30</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>2.18</v>
       </c>
       <c r="H29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I29" t="n">
         <v>3.95</v>
@@ -6010,7 +6010,7 @@
         <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L29" t="n">
         <v>1.39</v>
@@ -6037,7 +6037,7 @@
         <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U29" t="n">
         <v>2.28</v>
@@ -6070,7 +6070,7 @@
         <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF29" t="n">
         <v>14</v>
@@ -6088,7 +6088,7 @@
         <v>26</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
         <v>34</v>
@@ -6112,7 +6112,7 @@
         <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AT29" t="n">
         <v>9.800000000000001</v>
@@ -6121,7 +6121,7 @@
         <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW29" t="n">
         <v>38</v>
@@ -6136,7 +6136,7 @@
         <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB29" t="n">
         <v>23</v>
@@ -6151,14 +6151,14 @@
         <v>34</v>
       </c>
       <c r="BF29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG29" t="n">
         <v>34</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6231,10 +6231,10 @@
         <v>2.52</v>
       </c>
       <c r="T30" t="n">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V30" t="n">
         <v>1.47</v>
@@ -6255,10 +6255,10 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -6267,25 +6267,25 @@
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
@@ -6297,52 +6297,52 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
         <v>1.01</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G31" t="n">
         <v>2.14</v>
@@ -6398,7 +6398,7 @@
         <v>3.2</v>
       </c>
       <c r="K31" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6407,7 +6407,7 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O31" t="n">
         <v>1.32</v>
@@ -6416,7 +6416,7 @@
         <v>1.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R31" t="n">
         <v>1.26</v>
@@ -6434,7 +6434,7 @@
         <v>1.23</v>
       </c>
       <c r="W31" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6491,52 +6491,52 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>2.62</v>
       </c>
       <c r="I32" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J32" t="n">
         <v>2.94</v>
@@ -6601,7 +6601,7 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
         <v>1.33</v>
@@ -6685,52 +6685,52 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G33" t="n">
         <v>3.4</v>
       </c>
       <c r="H33" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I33" t="n">
         <v>2.98</v>
@@ -6795,7 +6795,7 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="O33" t="n">
         <v>1.4</v>
@@ -6879,52 +6879,52 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
         <v>2.6</v>
       </c>
       <c r="I34" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J34" t="n">
         <v>3.7</v>
@@ -6989,16 +6989,16 @@
         <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P34" t="n">
         <v>2.18</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R34" t="n">
         <v>1.45</v>
@@ -7007,10 +7007,10 @@
         <v>3.05</v>
       </c>
       <c r="T34" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U34" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V34" t="n">
         <v>1.6</v>
@@ -7031,16 +7031,16 @@
         <v>38</v>
       </c>
       <c r="AB34" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD34" t="n">
         <v>12</v>
       </c>
       <c r="AE34" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF34" t="n">
         <v>20</v>
@@ -7049,7 +7049,7 @@
         <v>12.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI34" t="n">
         <v>36</v>
@@ -7118,7 +7118,7 @@
         <v>34</v>
       </c>
       <c r="BE34" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF34" t="n">
         <v>20</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -7162,16 +7162,16 @@
         <v>1.75</v>
       </c>
       <c r="G35" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H35" t="n">
         <v>4.8</v>
       </c>
       <c r="I35" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K35" t="n">
         <v>4.3</v>
@@ -7198,7 +7198,7 @@
         <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
         <v>1.9</v>
@@ -7213,10 +7213,10 @@
         <v>2.12</v>
       </c>
       <c r="X35" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y35" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="Z35" t="n">
         <v>48</v>
@@ -7231,19 +7231,19 @@
         <v>10.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE35" t="n">
         <v>90</v>
       </c>
       <c r="AF35" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG35" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH35" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI35" t="n">
         <v>90</v>
@@ -7261,7 +7261,7 @@
         <v>150</v>
       </c>
       <c r="AN35" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AO35" t="n">
         <v>110</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>2.74</v>
       </c>
       <c r="G36" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H36" t="n">
         <v>3.05</v>
@@ -7404,7 +7404,7 @@
         <v>1.4</v>
       </c>
       <c r="W36" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X36" t="n">
         <v>7.4</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -7571,13 +7571,13 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="O37" t="n">
         <v>1.01</v>
       </c>
       <c r="P37" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q37" t="n">
         <v>1.25</v>
@@ -7586,7 +7586,7 @@
         <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T37" t="n">
         <v>1.11</v>
@@ -7655,52 +7655,52 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
         <v>1.01</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O38" t="n">
         <v>1.01</v>
@@ -7849,52 +7849,52 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
         <v>1.01</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8043,52 +8043,52 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF39" t="n">
         <v>1.01</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8153,13 +8153,13 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O40" t="n">
         <v>1.22</v>
       </c>
       <c r="P40" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q40" t="n">
         <v>1.22</v>
@@ -8168,7 +8168,7 @@
         <v>1.24</v>
       </c>
       <c r="S40" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T40" t="n">
         <v>1.11</v>
@@ -8237,52 +8237,52 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF40" t="n">
         <v>1.01</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G41" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I41" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J41" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K41" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8347,34 +8347,34 @@
         <v>1.07</v>
       </c>
       <c r="N41" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O41" t="n">
         <v>1.33</v>
       </c>
       <c r="P41" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
         <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U41" t="n">
         <v>1.93</v>
       </c>
       <c r="V41" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W41" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X41" t="n">
         <v>15</v>
@@ -8401,10 +8401,10 @@
         <v>80</v>
       </c>
       <c r="AF41" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH41" t="n">
         <v>25</v>
@@ -8416,7 +8416,7 @@
         <v>23</v>
       </c>
       <c r="AK41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL41" t="n">
         <v>46</v>
@@ -8425,7 +8425,7 @@
         <v>150</v>
       </c>
       <c r="AN41" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO41" t="n">
         <v>120</v>
@@ -8437,10 +8437,10 @@
         <v>14.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS41" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT41" t="n">
         <v>7</v>
@@ -8452,7 +8452,7 @@
         <v>17.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX41" t="n">
         <v>9</v>
@@ -8464,7 +8464,7 @@
         <v>17.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB41" t="n">
         <v>16</v>
@@ -8473,20 +8473,20 @@
         <v>16.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF41" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
         <v>2.7</v>
       </c>
       <c r="O42" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P42" t="n">
         <v>2.7</v>
@@ -8559,10 +8559,10 @@
         <v>1.98</v>
       </c>
       <c r="T42" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
         <v>1.2</v>
@@ -8574,37 +8574,37 @@
         <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA42" t="n">
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AC42" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AD42" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF42" t="n">
         <v>21</v>
       </c>
       <c r="AG42" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH42" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ42" t="n">
         <v>29</v>
@@ -8625,16 +8625,16 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="AT42" t="n">
         <v>8.800000000000001</v>
@@ -8643,10 +8643,10 @@
         <v>7.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="AX42" t="n">
         <v>8.800000000000001</v>
@@ -8655,32 +8655,32 @@
         <v>6.8</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="BC42" t="n">
         <v>9.6</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.03</v>
+        <v>1.89</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8735,16 +8735,16 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="O43" t="n">
         <v>1.18</v>
       </c>
       <c r="P43" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="R43" t="n">
         <v>1.24</v>
@@ -8819,52 +8819,52 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
         <v>1.01</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>1.38</v>
       </c>
       <c r="G44" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H44" t="n">
         <v>7.4</v>
@@ -8917,7 +8917,7 @@
         <v>11</v>
       </c>
       <c r="J44" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K44" t="n">
         <v>5.8</v>
@@ -8956,7 +8956,7 @@
         <v>1.1</v>
       </c>
       <c r="W44" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X44" t="n">
         <v>950</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>2.1</v>
       </c>
       <c r="G45" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="H45" t="n">
         <v>3.4</v>
@@ -9123,34 +9123,34 @@
         <v>1.05</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P45" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R45" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S45" t="n">
-        <v>1.81</v>
+        <v>2.96</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V45" t="n">
         <v>1.35</v>
       </c>
       <c r="W45" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9201,13 +9201,13 @@
         <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO45" t="n">
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AQ45" t="n">
         <v>10.5</v>
@@ -9216,53 +9216,53 @@
         <v>18</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AV45" t="n">
         <v>10.5</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AX45" t="n">
         <v>10</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.61</v>
+        <v>10</v>
       </c>
       <c r="BG45" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -9302,10 +9302,10 @@
         <v>15.5</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J46" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K46" t="n">
         <v>8.4</v>
@@ -9326,7 +9326,7 @@
         <v>3.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R46" t="n">
         <v>1.87</v>
@@ -9338,7 +9338,7 @@
         <v>2.06</v>
       </c>
       <c r="U46" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V46" t="n">
         <v>1.06</v>
@@ -9347,28 +9347,28 @@
         <v>5.3</v>
       </c>
       <c r="X46" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Y46" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z46" t="n">
         <v>150</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>720</v>
       </c>
       <c r="AB46" t="n">
         <v>12.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AD46" t="n">
         <v>55</v>
       </c>
       <c r="AE46" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AF46" t="n">
         <v>8.800000000000001</v>
@@ -9377,13 +9377,13 @@
         <v>12</v>
       </c>
       <c r="AH46" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI46" t="n">
         <v>170</v>
       </c>
       <c r="AJ46" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AK46" t="n">
         <v>13</v>
@@ -9398,46 +9398,46 @@
         <v>3.3</v>
       </c>
       <c r="AO46" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AP46" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AQ46" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AR46" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AS46" t="n">
         <v>150</v>
       </c>
       <c r="AT46" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU46" t="n">
         <v>16.5</v>
       </c>
       <c r="AV46" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AW46" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AX46" t="n">
         <v>8.4</v>
       </c>
       <c r="AY46" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ46" t="n">
         <v>29</v>
       </c>
       <c r="BA46" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BB46" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC46" t="n">
         <v>12</v>
@@ -9449,14 +9449,14 @@
         <v>75</v>
       </c>
       <c r="BF46" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BG46" t="n">
         <v>65</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
         <v>50</v>
       </c>
       <c r="AM47" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN47" t="n">
         <v>18</v>
@@ -9625,7 +9625,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ47" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA47" t="n">
         <v>6.8</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -9687,16 +9687,16 @@
         <v>3.65</v>
       </c>
       <c r="H48" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I48" t="n">
         <v>2.08</v>
       </c>
       <c r="J48" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K48" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L48" t="n">
         <v>1.24</v>
@@ -9729,13 +9729,13 @@
         <v>2.74</v>
       </c>
       <c r="V48" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W48" t="n">
         <v>1.37</v>
       </c>
       <c r="X48" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Y48" t="n">
         <v>15.5</v>
@@ -9756,7 +9756,7 @@
         <v>11.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF48" t="n">
         <v>32</v>
@@ -9825,7 +9825,7 @@
         <v>22</v>
       </c>
       <c r="BB48" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC48" t="n">
         <v>26</v>
@@ -9834,7 +9834,7 @@
         <v>25</v>
       </c>
       <c r="BE48" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF48" t="n">
         <v>19.5</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -9875,25 +9875,25 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G49" t="n">
         <v>1.48</v>
       </c>
       <c r="H49" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I49" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J49" t="n">
         <v>4.8</v>
       </c>
       <c r="K49" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L49" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M49" t="n">
         <v>1.05</v>
@@ -9911,7 +9911,7 @@
         <v>1.69</v>
       </c>
       <c r="R49" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S49" t="n">
         <v>2.74</v>
@@ -9932,28 +9932,28 @@
         <v>20</v>
       </c>
       <c r="Y49" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z49" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA49" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AB49" t="n">
         <v>11</v>
       </c>
       <c r="AC49" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD49" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AE49" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG49" t="n">
         <v>9.800000000000001</v>
@@ -9971,28 +9971,28 @@
         <v>15</v>
       </c>
       <c r="AL49" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM49" t="n">
         <v>120</v>
       </c>
       <c r="AN49" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO49" t="n">
         <v>150</v>
       </c>
       <c r="AP49" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ49" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT49" t="n">
         <v>8.199999999999999</v>
@@ -10001,10 +10001,10 @@
         <v>9.6</v>
       </c>
       <c r="AV49" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW49" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX49" t="n">
         <v>8.199999999999999</v>
@@ -10016,29 +10016,29 @@
         <v>21</v>
       </c>
       <c r="BA49" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB49" t="n">
         <v>11.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD49" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="BE49" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG49" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -10078,13 +10078,13 @@
         <v>5.7</v>
       </c>
       <c r="I50" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J50" t="n">
         <v>4.8</v>
       </c>
       <c r="K50" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -10102,7 +10102,7 @@
         <v>2.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="R50" t="n">
         <v>1.57</v>
@@ -10120,7 +10120,7 @@
         <v>1.18</v>
       </c>
       <c r="W50" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X50" t="n">
         <v>26</v>
@@ -10129,10 +10129,10 @@
         <v>30</v>
       </c>
       <c r="Z50" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA50" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB50" t="n">
         <v>12</v>
@@ -10144,7 +10144,7 @@
         <v>24</v>
       </c>
       <c r="AE50" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF50" t="n">
         <v>12</v>
@@ -10156,7 +10156,7 @@
         <v>22</v>
       </c>
       <c r="AI50" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ50" t="n">
         <v>15.5</v>
@@ -10213,10 +10213,10 @@
         <v>8.6</v>
       </c>
       <c r="BB50" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC50" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD50" t="n">
         <v>24</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -10263,16 +10263,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G51" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H51" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I51" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>4.3</v>
@@ -10293,28 +10293,28 @@
         <v>1.2</v>
       </c>
       <c r="P51" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q51" t="n">
         <v>1.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S51" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T51" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U51" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V51" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="W51" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X51" t="n">
         <v>25</v>
@@ -10323,10 +10323,10 @@
         <v>12.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA51" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AB51" t="n">
         <v>25</v>
@@ -10338,25 +10338,25 @@
         <v>10</v>
       </c>
       <c r="AE51" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF51" t="n">
         <v>40</v>
       </c>
       <c r="AG51" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AH51" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI51" t="n">
         <v>29</v>
       </c>
       <c r="AJ51" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL51" t="n">
         <v>48</v>
@@ -10368,10 +10368,10 @@
         <v>40</v>
       </c>
       <c r="AO51" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AP51" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ51" t="n">
         <v>11</v>
@@ -10380,13 +10380,13 @@
         <v>11.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU51" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV51" t="n">
         <v>9.199999999999999</v>
@@ -10395,7 +10395,7 @@
         <v>14.5</v>
       </c>
       <c r="AX51" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY51" t="n">
         <v>16.5</v>
@@ -10404,19 +10404,19 @@
         <v>15</v>
       </c>
       <c r="BA51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB51" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD51" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BE51" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF51" t="n">
         <v>24</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -10457,19 +10457,19 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G52" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I52" t="n">
         <v>2.22</v>
       </c>
-      <c r="I52" t="n">
-        <v>2.24</v>
-      </c>
       <c r="J52" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K52" t="n">
         <v>4</v>
@@ -10490,25 +10490,25 @@
         <v>2.78</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R52" t="n">
         <v>1.71</v>
       </c>
       <c r="S52" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T52" t="n">
         <v>1.5</v>
       </c>
       <c r="U52" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V52" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W52" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X52" t="n">
         <v>25</v>
@@ -10517,7 +10517,7 @@
         <v>16.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA52" t="n">
         <v>28</v>
@@ -10571,16 +10571,16 @@
         <v>15</v>
       </c>
       <c r="AR52" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT52" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU52" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV52" t="n">
         <v>10.5</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G53" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H53" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I53" t="n">
         <v>3.9</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3.95</v>
       </c>
       <c r="J53" t="n">
         <v>3.25</v>
@@ -10678,7 +10678,7 @@
         <v>2.72</v>
       </c>
       <c r="O53" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P53" t="n">
         <v>1.55</v>
@@ -10699,10 +10699,10 @@
         <v>1.75</v>
       </c>
       <c r="V53" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W53" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X53" t="n">
         <v>8.6</v>
@@ -10753,7 +10753,7 @@
         <v>200</v>
       </c>
       <c r="AN53" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO53" t="n">
         <v>95</v>
@@ -10765,7 +10765,7 @@
         <v>9.6</v>
       </c>
       <c r="AR53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS53" t="n">
         <v>36</v>
@@ -10777,7 +10777,7 @@
         <v>7</v>
       </c>
       <c r="AV53" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW53" t="n">
         <v>55</v>
@@ -10795,7 +10795,7 @@
         <v>38</v>
       </c>
       <c r="BB53" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC53" t="n">
         <v>26</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -10845,170 +10845,170 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="G54" t="n">
-        <v>600</v>
+        <v>2.08</v>
       </c>
       <c r="H54" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I54" t="n">
-        <v>870</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K54" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P54" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -11057,152 +11057,152 @@
         <v>3.15</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P55" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11245,7 @@
         <v>4.6</v>
       </c>
       <c r="J56" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="K56" t="n">
         <v>3.65</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-11 17:12:02</t>
+          <t>2026-05-11 19:26:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
@@ -769,7 +769,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G3" t="n">
         <v>2.02</v>
@@ -963,7 +963,7 @@
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
         <v>3.8</v>
@@ -972,37 +972,37 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
         <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
@@ -1011,10 +1011,10 @@
         <v>16</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
         <v>8.4</v>
@@ -1029,7 +1029,7 @@
         <v>70</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1047,13 +1047,13 @@
         <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
         <v>85</v>
@@ -1065,22 +1065,22 @@
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="AT3" t="n">
         <v>7.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
         <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
@@ -1101,20 +1101,20 @@
         <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>2.52</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H4" t="n">
         <v>2.92</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
         <v>3.2</v>
@@ -1298,7 +1298,7 @@
         <v>4.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF4" t="n">
         <v>19.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -1351,10 +1351,10 @@
         <v>1.95</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.39</v>
@@ -1366,28 +1366,28 @@
         <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="W5" t="n">
         <v>1.18</v>
@@ -1402,10 +1402,10 @@
         <v>11</v>
       </c>
       <c r="AA5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC5" t="n">
         <v>8.199999999999999</v>
@@ -1453,7 +1453,7 @@
         <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS5" t="n">
         <v>18</v>
@@ -1483,26 +1483,26 @@
         <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG5" t="n">
         <v>14</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>2.84</v>
       </c>
       <c r="G6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H6" t="n">
         <v>2.46</v>
       </c>
       <c r="I6" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
@@ -1554,7 +1554,7 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
         <v>3.4</v>
@@ -1569,76 +1569,76 @@
         <v>2.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
         <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN6" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP6" t="n">
         <v>11.5</v>
@@ -1650,7 +1650,7 @@
         <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.69</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.12</v>
+        <v>4.4</v>
       </c>
       <c r="AX6" t="n">
         <v>17.5</v>
@@ -1674,29 +1674,29 @@
         <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.63</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.26</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.04</v>
+        <v>4.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.26</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.36</v>
+        <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.04</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
         <v>18.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -1930,16 +1930,16 @@
         <v>7.2</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
         <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -1966,13 +1966,13 @@
         <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X8" t="n">
         <v>17.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I9" t="n">
         <v>3.45</v>
       </c>
       <c r="J9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
@@ -2136,43 +2136,43 @@
         <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q9" t="n">
         <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="T9" t="n">
         <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
         <v>20</v>
@@ -2196,7 +2196,7 @@
         <v>16.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH9" t="n">
         <v>27</v>
@@ -2208,7 +2208,7 @@
         <v>48</v>
       </c>
       <c r="AK9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL9" t="n">
         <v>85</v>
@@ -2217,7 +2217,7 @@
         <v>220</v>
       </c>
       <c r="AN9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
         <v>80</v>
@@ -2226,10 +2226,10 @@
         <v>6.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="AS9" t="n">
         <v>42</v>
@@ -2238,47 +2238,47 @@
         <v>6.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.96</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AY9" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G10" t="n">
         <v>4.6</v>
@@ -2318,10 +2318,10 @@
         <v>1.96</v>
       </c>
       <c r="I10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
         <v>3.85</v>
@@ -2342,22 +2342,22 @@
         <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
         <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
         <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="W10" t="n">
         <v>1.27</v>
@@ -2372,7 +2372,7 @@
         <v>14.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB10" t="n">
         <v>16.5</v>
@@ -2441,7 +2441,7 @@
         <v>17.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G11" t="n">
         <v>1.76</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
         <v>5.9</v>
@@ -2518,7 +2518,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2545,7 +2545,7 @@
         <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U11" t="n">
         <v>2.14</v>
@@ -2563,13 +2563,13 @@
         <v>27</v>
       </c>
       <c r="Z11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA11" t="n">
         <v>150</v>
       </c>
       <c r="AB11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC11" t="n">
         <v>12</v>
@@ -2593,7 +2593,7 @@
         <v>75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK11" t="n">
         <v>20</v>
@@ -2605,7 +2605,7 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO11" t="n">
         <v>75</v>
@@ -2617,10 +2617,10 @@
         <v>18.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
@@ -2632,7 +2632,7 @@
         <v>17.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.94</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
         <v>9.800000000000001</v>
@@ -2644,7 +2644,7 @@
         <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.94</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
         <v>14.5</v>
@@ -2656,17 +2656,17 @@
         <v>4.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="BF11" t="n">
         <v>6.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.94</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -2721,28 +2721,28 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="O12" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P12" t="n">
         <v>1.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T12" t="n">
         <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
         <v>1.31</v>
@@ -2775,10 +2775,10 @@
         <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -2814,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
@@ -2826,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX12" t="n">
         <v>11.5</v>
@@ -2838,10 +2838,10 @@
         <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC12" t="n">
         <v>6.2</v>
@@ -2856,11 +2856,11 @@
         <v>24</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
         <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V13" t="n">
         <v>1.05</v>
@@ -3014,7 +3014,7 @@
         <v>4.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV13" t="n">
         <v>5.4</v>
@@ -3023,10 +3023,10 @@
         <v>5.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ13" t="n">
         <v>5.1</v>
@@ -3035,10 +3035,10 @@
         <v>5.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD13" t="n">
         <v>5.2</v>
@@ -3047,14 +3047,14 @@
         <v>5.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BG13" t="n">
         <v>5.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I14" t="n">
         <v>3.75</v>
@@ -3115,7 +3115,7 @@
         <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>3.85</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -3306,7 +3306,7 @@
         <v>2.84</v>
       </c>
       <c r="O15" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="P15" t="n">
         <v>1.81</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -3500,13 +3500,13 @@
         <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
         <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -3960,7 +3960,7 @@
         <v>40</v>
       </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN18" t="n">
         <v>11.5</v>
@@ -3981,7 +3981,7 @@
         <v>13.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
@@ -4002,7 +4002,7 @@
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB18" t="n">
         <v>15</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
         <v>1.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R19" t="n">
         <v>1.31</v>
@@ -4193,7 +4193,7 @@
         <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA19" t="n">
         <v>8.6</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -4261,10 +4261,10 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4357,52 +4357,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
         <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V21" t="n">
         <v>1.48</v>
@@ -4500,7 +4500,7 @@
         <v>25</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z21" t="n">
         <v>30</v>
@@ -4551,52 +4551,52 @@
         <v>36</v>
       </c>
       <c r="AP21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>2.5</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AR21" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="AS21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BB21" t="n">
         <v>2.72</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>2.64</v>
       </c>
       <c r="BC21" t="n">
         <v>18.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BF21" t="n">
         <v>12</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -4745,16 +4745,16 @@
         <v>48</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AR22" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT22" t="n">
         <v>10.5</v>
@@ -4763,25 +4763,25 @@
         <v>9</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BC22" t="n">
         <v>12.5</v>
@@ -4796,11 +4796,11 @@
         <v>6.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -4864,13 +4864,13 @@
         <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="T23" t="n">
         <v>1.51</v>
@@ -4939,62 +4939,62 @@
         <v>42</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.5</v>
+        <v>3.75</v>
       </c>
       <c r="AR23" t="n">
         <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
         <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="AX23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>3.75</v>
       </c>
       <c r="BA23" t="n">
         <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="BC23" t="n">
-        <v>14.5</v>
+        <v>3.9</v>
       </c>
       <c r="BD23" t="n">
-        <v>22</v>
+        <v>4.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.800000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
         <v>2.24</v>
       </c>
       <c r="V24" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W24" t="n">
         <v>1.53</v>
@@ -5154,7 +5154,7 @@
         <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX24" t="n">
         <v>16</v>
@@ -5172,7 +5172,7 @@
         <v>30</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD24" t="n">
         <v>30</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G25" t="n">
         <v>2.3</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5425,10 +5425,10 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,7 +5437,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O26" t="n">
         <v>1.21</v>
@@ -5521,52 +5521,52 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -5813,10 +5813,10 @@
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5825,7 +5825,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O28" t="n">
         <v>1.01</v>
@@ -5909,52 +5909,52 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
         <v>1.94</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
         <v>1.51</v>
@@ -6339,7 +6339,7 @@
         <v>30</v>
       </c>
       <c r="BD30" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE30" t="n">
         <v>40</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6407,13 +6407,13 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O31" t="n">
         <v>1.19</v>
       </c>
       <c r="P31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
         <v>2.74</v>
       </c>
       <c r="H32" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I32" t="n">
         <v>3.1</v>
@@ -6610,7 +6610,7 @@
         <v>2.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R32" t="n">
         <v>1.48</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
         <v>1.84</v>
       </c>
       <c r="X33" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y33" t="n">
         <v>15.5</v>
@@ -6900,7 +6900,7 @@
         <v>14</v>
       </c>
       <c r="AW33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX33" t="n">
         <v>12.5</v>
@@ -6912,7 +6912,7 @@
         <v>15.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BB33" t="n">
         <v>23</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -6989,13 +6989,13 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="O34" t="n">
         <v>1.22</v>
       </c>
       <c r="P34" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q34" t="n">
         <v>1.22</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -7556,10 +7556,10 @@
         <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="K37" t="n">
         <v>3.2</v>
@@ -7571,10 +7571,10 @@
         <v>1.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="O37" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P37" t="n">
         <v>1.4</v>
@@ -7583,19 +7583,19 @@
         <v>2.96</v>
       </c>
       <c r="R37" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S37" t="n">
         <v>6.4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U37" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W37" t="n">
         <v>1.48</v>
@@ -7610,7 +7610,7 @@
         <v>21</v>
       </c>
       <c r="AA37" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB37" t="n">
         <v>7.8</v>
@@ -7622,7 +7622,7 @@
         <v>16.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF37" t="n">
         <v>17.5</v>
@@ -7634,28 +7634,28 @@
         <v>29</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ37" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK37" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN37" t="n">
         <v>70</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AQ37" t="n">
         <v>7</v>
@@ -7664,7 +7664,7 @@
         <v>16.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AT37" t="n">
         <v>6.2</v>
@@ -7676,7 +7676,7 @@
         <v>13</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AX37" t="n">
         <v>14</v>
@@ -7685,32 +7685,32 @@
         <v>12</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BA37" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB37" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC37" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BD37" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF37" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
         <v>1.52</v>
       </c>
       <c r="X39" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y39" t="n">
         <v>13</v>
@@ -8004,7 +8004,7 @@
         <v>13.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD39" t="n">
         <v>12</v>
@@ -8031,7 +8031,7 @@
         <v>32</v>
       </c>
       <c r="AL39" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM39" t="n">
         <v>70</v>
@@ -8049,10 +8049,10 @@
         <v>12</v>
       </c>
       <c r="AR39" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AT39" t="n">
         <v>12.5</v>
@@ -8064,7 +8064,7 @@
         <v>11</v>
       </c>
       <c r="AW39" t="n">
-        <v>9.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AX39" t="n">
         <v>18.5</v>
@@ -8076,10 +8076,10 @@
         <v>14.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BB39" t="n">
-        <v>14.5</v>
+        <v>38</v>
       </c>
       <c r="BC39" t="n">
         <v>26</v>
@@ -8088,17 +8088,17 @@
         <v>34</v>
       </c>
       <c r="BE39" t="n">
-        <v>9.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG39" t="n">
         <v>17.5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -8129,16 +8129,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G40" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H40" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I40" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="J40" t="n">
         <v>3.05</v>
@@ -8147,16 +8147,16 @@
         <v>3.95</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M40" t="n">
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="O40" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="P40" t="n">
         <v>1.64</v>
@@ -8168,7 +8168,7 @@
         <v>1.22</v>
       </c>
       <c r="S40" t="n">
-        <v>2.52</v>
+        <v>3.85</v>
       </c>
       <c r="T40" t="n">
         <v>1.11</v>
@@ -8177,10 +8177,10 @@
         <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W40" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G41" t="n">
         <v>3.1</v>
       </c>
       <c r="H41" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I41" t="n">
         <v>3.05</v>
@@ -8341,22 +8341,22 @@
         <v>4.1</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M41" t="n">
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.1</v>
+        <v>2.88</v>
       </c>
       <c r="O41" t="n">
         <v>1.33</v>
       </c>
       <c r="P41" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="R41" t="n">
         <v>1.26</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
         <v>7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M42" t="n">
         <v>1.01</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N43" t="n">
         <v>3.5</v>
@@ -8747,16 +8747,16 @@
         <v>1.98</v>
       </c>
       <c r="R43" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T43" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U43" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V43" t="n">
         <v>1.2</v>
@@ -8768,7 +8768,7 @@
         <v>970</v>
       </c>
       <c r="Y43" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z43" t="n">
         <v>48</v>
@@ -8789,10 +8789,10 @@
         <v>90</v>
       </c>
       <c r="AF43" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH43" t="n">
         <v>950</v>
@@ -8828,31 +8828,31 @@
         <v>4.8</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AV43" t="n">
         <v>4.4</v>
       </c>
       <c r="AW43" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX43" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AY43" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AZ43" t="n">
         <v>4.4</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB43" t="n">
         <v>4.3</v>
@@ -8864,7 +8864,7 @@
         <v>4.7</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF43" t="n">
         <v>9.800000000000001</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -8914,10 +8914,10 @@
         <v>5.1</v>
       </c>
       <c r="I44" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J44" t="n">
-        <v>1.09</v>
+        <v>3.65</v>
       </c>
       <c r="K44" t="n">
         <v>4.4</v>
@@ -8926,91 +8926,91 @@
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N44" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="O44" t="n">
         <v>1.33</v>
       </c>
       <c r="P44" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S44" t="n">
         <v>3.4</v>
       </c>
       <c r="T44" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U44" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="V44" t="n">
         <v>1.2</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB44" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD44" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE44" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI44" t="n">
         <v>85</v>
       </c>
-      <c r="AF44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>90</v>
-      </c>
       <c r="AJ44" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL44" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM44" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP44" t="n">
         <v>12</v>
@@ -9019,10 +9019,10 @@
         <v>14.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.21</v>
+        <v>4.6</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.21</v>
+        <v>4.8</v>
       </c>
       <c r="AT44" t="n">
         <v>6.8</v>
@@ -9034,41 +9034,41 @@
         <v>17.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX44" t="n">
         <v>9</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.21</v>
+        <v>8.4</v>
       </c>
       <c r="AZ44" t="n">
         <v>17.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB44" t="n">
         <v>16</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.21</v>
+        <v>16</v>
       </c>
       <c r="BD44" t="n">
-        <v>1.21</v>
+        <v>4.6</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.21</v>
+        <v>4.8</v>
       </c>
       <c r="BF44" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.21</v>
+        <v>4.7</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G45" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="H45" t="n">
         <v>3.85</v>
@@ -9114,16 +9114,16 @@
         <v>3.75</v>
       </c>
       <c r="K45" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="L45" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M45" t="n">
         <v>1.02</v>
       </c>
       <c r="N45" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="O45" t="n">
         <v>1.12</v>
@@ -9150,7 +9150,7 @@
         <v>1.18</v>
       </c>
       <c r="W45" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9210,10 +9210,10 @@
         <v>1.89</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AS45" t="n">
         <v>1.89</v>
@@ -9225,10 +9225,10 @@
         <v>7.2</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AX45" t="n">
         <v>8.800000000000001</v>
@@ -9237,19 +9237,19 @@
         <v>6.8</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BC45" t="n">
         <v>9.6</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="BE45" t="n">
         <v>1.89</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O46" t="n">
         <v>1.17</v>
@@ -9326,13 +9326,13 @@
         <v>1.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R46" t="n">
         <v>1.24</v>
       </c>
       <c r="S46" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T46" t="n">
         <v>1.11</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -9499,10 +9499,10 @@
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K47" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9511,7 +9511,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O47" t="n">
         <v>1.18</v>
@@ -9595,52 +9595,52 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF47" t="n">
         <v>1.01</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -9684,10 +9684,10 @@
         <v>1.38</v>
       </c>
       <c r="G48" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H48" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I48" t="n">
         <v>11</v>
@@ -9705,16 +9705,16 @@
         <v>1.03</v>
       </c>
       <c r="N48" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="O48" t="n">
         <v>1.2</v>
       </c>
       <c r="P48" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R48" t="n">
         <v>1.53</v>
@@ -9732,7 +9732,7 @@
         <v>1.1</v>
       </c>
       <c r="W48" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X48" t="n">
         <v>950</v>
@@ -9804,7 +9804,7 @@
         <v>7.6</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="AV48" t="n">
         <v>4.6</v>
@@ -9819,7 +9819,7 @@
         <v>8</v>
       </c>
       <c r="AZ48" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BA48" t="n">
         <v>5.1</v>
@@ -9837,14 +9837,14 @@
         <v>5.1</v>
       </c>
       <c r="BF48" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG48" t="n">
         <v>5.1</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G49" t="n">
         <v>2.28</v>
@@ -9884,16 +9884,16 @@
         <v>3.4</v>
       </c>
       <c r="I49" t="n">
-        <v>4.2</v>
+        <v>870</v>
       </c>
       <c r="J49" t="n">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="K49" t="n">
         <v>4.8</v>
       </c>
       <c r="L49" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="n">
         <v>1.05</v>
@@ -10019,7 +10019,7 @@
         <v>1.77</v>
       </c>
       <c r="BB49" t="n">
-        <v>18.5</v>
+        <v>1.69</v>
       </c>
       <c r="BC49" t="n">
         <v>1.77</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
         <v>5.3</v>
       </c>
       <c r="O50" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P50" t="n">
         <v>2.46</v>
@@ -10111,7 +10111,7 @@
         <v>2.4</v>
       </c>
       <c r="T50" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U50" t="n">
         <v>2.4</v>
@@ -10126,10 +10126,10 @@
         <v>24</v>
       </c>
       <c r="Y50" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA50" t="n">
         <v>22</v>
@@ -10138,7 +10138,7 @@
         <v>950</v>
       </c>
       <c r="AC50" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD50" t="n">
         <v>10.5</v>
@@ -10186,19 +10186,19 @@
         <v>12</v>
       </c>
       <c r="AS50" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AT50" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AU50" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV50" t="n">
         <v>9.4</v>
       </c>
       <c r="AW50" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX50" t="n">
         <v>13</v>
@@ -10210,29 +10210,29 @@
         <v>14.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BB50" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="BC50" t="n">
         <v>14</v>
       </c>
       <c r="BD50" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE50" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BF50" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="BG50" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -10293,10 +10293,10 @@
         <v>1.2</v>
       </c>
       <c r="P51" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="R51" t="n">
         <v>1.57</v>
@@ -10305,10 +10305,10 @@
         <v>2.46</v>
       </c>
       <c r="T51" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U51" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V51" t="n">
         <v>1.17</v>
@@ -10338,13 +10338,13 @@
         <v>24</v>
       </c>
       <c r="AE51" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF51" t="n">
         <v>11.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH51" t="n">
         <v>20</v>
@@ -10359,13 +10359,13 @@
         <v>15.5</v>
       </c>
       <c r="AL51" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM51" t="n">
         <v>95</v>
       </c>
       <c r="AN51" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AO51" t="n">
         <v>75</v>
@@ -10377,10 +10377,10 @@
         <v>22</v>
       </c>
       <c r="AR51" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT51" t="n">
         <v>10</v>
@@ -10392,7 +10392,7 @@
         <v>19.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AX51" t="n">
         <v>9.800000000000001</v>
@@ -10404,7 +10404,7 @@
         <v>15.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BB51" t="n">
         <v>13</v>
@@ -10416,17 +10416,17 @@
         <v>24</v>
       </c>
       <c r="BE51" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG51" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10463,7 @@
         <v>1.47</v>
       </c>
       <c r="H52" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I52" t="n">
         <v>8.800000000000001</v>
@@ -10475,7 +10475,7 @@
         <v>5.2</v>
       </c>
       <c r="L52" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M52" t="n">
         <v>1.05</v>
@@ -10511,7 +10511,7 @@
         <v>3.1</v>
       </c>
       <c r="X52" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y52" t="n">
         <v>29</v>
@@ -10520,10 +10520,10 @@
         <v>75</v>
       </c>
       <c r="AA52" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AB52" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC52" t="n">
         <v>11.5</v>
@@ -10538,7 +10538,7 @@
         <v>9.4</v>
       </c>
       <c r="AG52" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH52" t="n">
         <v>27</v>
@@ -10559,7 +10559,7 @@
         <v>120</v>
       </c>
       <c r="AN52" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO52" t="n">
         <v>150</v>
@@ -10571,25 +10571,25 @@
         <v>24</v>
       </c>
       <c r="AR52" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS52" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AT52" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU52" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV52" t="n">
         <v>26</v>
       </c>
       <c r="AW52" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AX52" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY52" t="n">
         <v>9.199999999999999</v>
@@ -10598,29 +10598,29 @@
         <v>21</v>
       </c>
       <c r="BA52" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB52" t="n">
         <v>11.5</v>
       </c>
       <c r="BC52" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="BE52" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG52" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -10705,7 +10705,7 @@
         <v>5.4</v>
       </c>
       <c r="X53" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y53" t="n">
         <v>60</v>
@@ -10720,13 +10720,13 @@
         <v>12.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AD53" t="n">
-        <v>260</v>
+        <v>55</v>
       </c>
       <c r="AE53" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF53" t="n">
         <v>8.800000000000001</v>
@@ -10735,10 +10735,10 @@
         <v>12</v>
       </c>
       <c r="AH53" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI53" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AJ53" t="n">
         <v>8.800000000000001</v>
@@ -10750,13 +10750,13 @@
         <v>38</v>
       </c>
       <c r="AM53" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AN53" t="n">
         <v>3.3</v>
       </c>
       <c r="AO53" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AP53" t="n">
         <v>34</v>
@@ -10789,10 +10789,10 @@
         <v>11</v>
       </c>
       <c r="AZ53" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA53" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BB53" t="n">
         <v>8.4</v>
@@ -10807,14 +10807,14 @@
         <v>85</v>
       </c>
       <c r="BF53" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BG53" t="n">
         <v>65</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -10869,10 +10869,10 @@
         <v>1.09</v>
       </c>
       <c r="N54" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O54" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P54" t="n">
         <v>1.74</v>
@@ -10887,7 +10887,7 @@
         <v>4</v>
       </c>
       <c r="T54" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U54" t="n">
         <v>1.86</v>
@@ -10911,7 +10911,7 @@
         <v>140</v>
       </c>
       <c r="AB54" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC54" t="n">
         <v>8.4</v>
@@ -10926,7 +10926,7 @@
         <v>13</v>
       </c>
       <c r="AG54" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH54" t="n">
         <v>25</v>
@@ -10959,10 +10959,10 @@
         <v>11.5</v>
       </c>
       <c r="AR54" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT54" t="n">
         <v>6.8</v>
@@ -10974,7 +10974,7 @@
         <v>16</v>
       </c>
       <c r="AW54" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX54" t="n">
         <v>9.800000000000001</v>
@@ -10986,7 +10986,7 @@
         <v>19</v>
       </c>
       <c r="BA54" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB54" t="n">
         <v>19.5</v>
@@ -10995,20 +10995,20 @@
         <v>19.5</v>
       </c>
       <c r="BD54" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE54" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF54" t="n">
         <v>14.5</v>
       </c>
       <c r="BG54" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G55" t="n">
         <v>3.7</v>
@@ -11051,13 +11051,13 @@
         <v>2.06</v>
       </c>
       <c r="J55" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K55" t="n">
         <v>4.5</v>
       </c>
       <c r="L55" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M55" t="n">
         <v>1.03</v>
@@ -11069,7 +11069,7 @@
         <v>1.18</v>
       </c>
       <c r="P55" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q55" t="n">
         <v>1.55</v>
@@ -11078,13 +11078,13 @@
         <v>1.71</v>
       </c>
       <c r="S55" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T55" t="n">
         <v>1.53</v>
       </c>
       <c r="U55" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V55" t="n">
         <v>1.94</v>
@@ -11120,7 +11120,7 @@
         <v>36</v>
       </c>
       <c r="AG55" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH55" t="n">
         <v>15.5</v>
@@ -11144,19 +11144,19 @@
         <v>26</v>
       </c>
       <c r="AO55" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP55" t="n">
         <v>24</v>
       </c>
       <c r="AQ55" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR55" t="n">
         <v>15</v>
       </c>
       <c r="AS55" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="AT55" t="n">
         <v>19</v>
@@ -11168,10 +11168,10 @@
         <v>10</v>
       </c>
       <c r="AW55" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX55" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AY55" t="n">
         <v>14.5</v>
@@ -11180,19 +11180,19 @@
         <v>13.5</v>
       </c>
       <c r="BA55" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BB55" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE55" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>7.4</v>
       </c>
       <c r="BF55" t="n">
         <v>19.5</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -11233,22 +11233,22 @@
         </is>
       </c>
       <c r="F56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G56" t="n">
         <v>3.4</v>
       </c>
-      <c r="G56" t="n">
-        <v>3.45</v>
-      </c>
       <c r="H56" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J56" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L56" t="n">
         <v>1.27</v>
@@ -11281,16 +11281,16 @@
         <v>2.82</v>
       </c>
       <c r="V56" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W56" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X56" t="n">
         <v>25</v>
       </c>
       <c r="Y56" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z56" t="n">
         <v>17.5</v>
@@ -11308,7 +11308,7 @@
         <v>11.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF56" t="n">
         <v>29</v>
@@ -11347,13 +11347,13 @@
         <v>15</v>
       </c>
       <c r="AR56" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS56" t="n">
         <v>24</v>
       </c>
       <c r="AT56" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU56" t="n">
         <v>9</v>
@@ -11365,7 +11365,7 @@
         <v>17.5</v>
       </c>
       <c r="AX56" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY56" t="n">
         <v>14</v>
@@ -11377,10 +11377,10 @@
         <v>23</v>
       </c>
       <c r="BB56" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BC56" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD56" t="n">
         <v>30</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -11430,13 +11430,13 @@
         <v>2.26</v>
       </c>
       <c r="G57" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H57" t="n">
         <v>3.85</v>
       </c>
       <c r="I57" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J57" t="n">
         <v>3.25</v>
@@ -11454,10 +11454,10 @@
         <v>2.74</v>
       </c>
       <c r="O57" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P57" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q57" t="n">
         <v>2.74</v>
@@ -11475,10 +11475,10 @@
         <v>1.75</v>
       </c>
       <c r="V57" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W57" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X57" t="n">
         <v>8.6</v>
@@ -11502,7 +11502,7 @@
         <v>17.5</v>
       </c>
       <c r="AE57" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF57" t="n">
         <v>11.5</v>
@@ -11541,7 +11541,7 @@
         <v>9.6</v>
       </c>
       <c r="AR57" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AS57" t="n">
         <v>36</v>
@@ -11556,7 +11556,7 @@
         <v>16</v>
       </c>
       <c r="AW57" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AX57" t="n">
         <v>10.5</v>
@@ -11571,13 +11571,13 @@
         <v>38</v>
       </c>
       <c r="BB57" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC57" t="n">
         <v>26</v>
       </c>
       <c r="BD57" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BE57" t="n">
         <v>48</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -11621,22 +11621,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H58" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I58" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K58" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11651,13 +11651,13 @@
         <v>1.33</v>
       </c>
       <c r="P58" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q58" t="n">
         <v>1.9</v>
       </c>
       <c r="R58" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -11669,10 +11669,10 @@
         <v>1.11</v>
       </c>
       <c r="V58" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W58" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X58" t="n">
         <v>1000</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11827,7 @@
         <v>4.2</v>
       </c>
       <c r="J59" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
         <v>3.15</v>
@@ -11848,19 +11848,19 @@
         <v>1.55</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R59" t="n">
         <v>1.2</v>
       </c>
       <c r="S59" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T59" t="n">
         <v>2.1</v>
       </c>
       <c r="U59" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V59" t="n">
         <v>1.32</v>
@@ -11869,7 +11869,7 @@
         <v>1.71</v>
       </c>
       <c r="X59" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y59" t="n">
         <v>14</v>
@@ -11884,7 +11884,7 @@
         <v>7.8</v>
       </c>
       <c r="AC59" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD59" t="n">
         <v>950</v>
@@ -11914,7 +11914,7 @@
         <v>65</v>
       </c>
       <c r="AM59" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN59" t="n">
         <v>38</v>
@@ -11923,62 +11923,62 @@
         <v>120</v>
       </c>
       <c r="AP59" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AQ59" t="n">
         <v>10</v>
       </c>
       <c r="AR59" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ59" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS59" t="n">
+      <c r="BA59" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD59" t="n">
         <v>5</v>
       </c>
-      <c r="AT59" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD59" t="n">
+      <c r="BE59" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF59" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE59" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF59" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG59" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -12012,13 +12012,13 @@
         <v>2.1</v>
       </c>
       <c r="G60" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="H60" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J60" t="n">
         <v>3.15</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -12203,46 +12203,46 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="G61" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="H61" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="I61" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J61" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="K61" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L61" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M61" t="n">
         <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O61" t="n">
         <v>1.28</v>
       </c>
       <c r="P61" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R61" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S61" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T61" t="n">
         <v>1.11</v>
@@ -12251,10 +12251,10 @@
         <v>1.11</v>
       </c>
       <c r="V61" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W61" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -12397,13 +12397,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G62" t="n">
         <v>2.38</v>
       </c>
       <c r="H62" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I62" t="n">
         <v>3.35</v>
@@ -12412,31 +12412,31 @@
         <v>3.65</v>
       </c>
       <c r="K62" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L62" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M62" t="n">
         <v>1.05</v>
       </c>
       <c r="N62" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O62" t="n">
         <v>1.26</v>
       </c>
       <c r="P62" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R62" t="n">
         <v>1.46</v>
       </c>
       <c r="S62" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T62" t="n">
         <v>1.67</v>
@@ -12448,7 +12448,7 @@
         <v>1.42</v>
       </c>
       <c r="W62" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X62" t="n">
         <v>21</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -12591,16 +12591,16 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H63" t="n">
         <v>2.38</v>
       </c>
       <c r="I63" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>3.95</v>
@@ -12609,37 +12609,37 @@
         <v>4.4</v>
       </c>
       <c r="L63" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M63" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N63" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O63" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P63" t="n">
         <v>2.8</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="R63" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V63" t="n">
         <v>1.67</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="U63" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.66</v>
       </c>
       <c r="W63" t="n">
         <v>1.5</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -12785,46 +12785,46 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G64" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H64" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I64" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K64" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L64" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M64" t="n">
         <v>1.06</v>
       </c>
       <c r="N64" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O64" t="n">
         <v>1.3</v>
       </c>
       <c r="P64" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R64" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S64" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T64" t="n">
         <v>1.7</v>
@@ -12833,10 +12833,10 @@
         <v>2.24</v>
       </c>
       <c r="V64" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W64" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X64" t="n">
         <v>16</v>
@@ -12908,7 +12908,7 @@
         <v>11</v>
       </c>
       <c r="AU64" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV64" t="n">
         <v>10.5</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -12997,28 +12997,28 @@
         <v>3.75</v>
       </c>
       <c r="L65" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M65" t="n">
         <v>1.06</v>
       </c>
       <c r="N65" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O65" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P65" t="n">
         <v>2.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R65" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S65" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T65" t="n">
         <v>1.67</v>
@@ -13027,7 +13027,7 @@
         <v>2.32</v>
       </c>
       <c r="V65" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W65" t="n">
         <v>1.51</v>
@@ -13036,7 +13036,7 @@
         <v>16.5</v>
       </c>
       <c r="Y65" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z65" t="n">
         <v>18</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -13173,46 +13173,46 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G66" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H66" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I66" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J66" t="n">
         <v>3.75</v>
       </c>
       <c r="K66" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L66" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M66" t="n">
         <v>1.05</v>
       </c>
       <c r="N66" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O66" t="n">
         <v>1.24</v>
       </c>
       <c r="P66" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R66" t="n">
         <v>1.49</v>
       </c>
       <c r="S66" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="T66" t="n">
         <v>1.64</v>
@@ -13224,7 +13224,7 @@
         <v>1.73</v>
       </c>
       <c r="W66" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X66" t="n">
         <v>970</v>
@@ -13281,7 +13281,7 @@
         <v>14.5</v>
       </c>
       <c r="AP66" t="n">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="AQ66" t="n">
         <v>11</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
         <v>1.99</v>
       </c>
       <c r="G67" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H67" t="n">
         <v>3.7</v>
@@ -13385,28 +13385,28 @@
         <v>4.3</v>
       </c>
       <c r="L67" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M67" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N67" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O67" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P67" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S67" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S67" t="n">
-        <v>2.42</v>
       </c>
       <c r="T67" t="n">
         <v>1.56</v>
@@ -13418,7 +13418,7 @@
         <v>1.34</v>
       </c>
       <c r="W67" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X67" t="n">
         <v>29</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13579,7 @@
         <v>4.7</v>
       </c>
       <c r="L68" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M68" t="n">
         <v>1.02</v>
@@ -13591,16 +13591,16 @@
         <v>1.12</v>
       </c>
       <c r="P68" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="R68" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S68" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T68" t="n">
         <v>1.42</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>
@@ -13755,22 +13755,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="G69" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H69" t="n">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="I69" t="n">
-        <v>870</v>
+        <v>7.8</v>
       </c>
       <c r="J69" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="K69" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
@@ -13779,22 +13779,22 @@
         <v>1.01</v>
       </c>
       <c r="N69" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="O69" t="n">
         <v>1.02</v>
       </c>
       <c r="P69" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
         <v>1.18</v>
       </c>
       <c r="S69" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="T69" t="n">
         <v>1.01</v>
@@ -13803,10 +13803,10 @@
         <v>1.01</v>
       </c>
       <c r="V69" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W69" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X69" t="n">
         <v>1000</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-05-11 21:43:43</t>
+          <t>2026-05-11 23:59:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G2" t="n">
-        <v>990</v>
+        <v>2.32</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.27</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.5</v>
@@ -969,37 +969,37 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
         <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
         <v>1.79</v>
@@ -1047,19 +1047,19 @@
         <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO3" t="n">
         <v>85</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>12.5</v>
@@ -1068,7 +1068,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT3" t="n">
         <v>7.4</v>
@@ -1080,7 +1080,7 @@
         <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
         <v>9.199999999999999</v>
@@ -1104,17 +1104,17 @@
         <v>8.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3" t="n">
         <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.25</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1172,31 +1172,31 @@
         <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
         <v>15.5</v>
@@ -1262,7 +1262,7 @@
         <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
         <v>8.800000000000001</v>
@@ -1274,7 +1274,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AX4" t="n">
         <v>14.5</v>
@@ -1286,29 +1286,29 @@
         <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
         <v>19.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
         <v>4.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G6" t="n">
         <v>3.1</v>
@@ -1551,13 +1551,13 @@
         <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.36</v>
@@ -1566,7 +1566,7 @@
         <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R6" t="n">
         <v>1.31</v>
@@ -1575,7 +1575,7 @@
         <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
         <v>2.06</v>
@@ -1602,7 +1602,7 @@
         <v>13.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>14.5</v>
@@ -1650,7 +1650,7 @@
         <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AX6" t="n">
         <v>17.5</v>
@@ -1674,29 +1674,29 @@
         <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BB6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF6" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
         <v>18.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -1730,31 +1730,31 @@
         <v>1.17</v>
       </c>
       <c r="G7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="I7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J7" t="n">
         <v>7.4</v>
       </c>
       <c r="K7" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
         <v>2.54</v>
@@ -1763,16 +1763,16 @@
         <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
         <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V7" t="n">
         <v>1.04</v>
@@ -1793,7 +1793,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>970</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
@@ -1817,13 +1817,13 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AK7" t="n">
         <v>970</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ7" t="n">
         <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="AT7" t="n">
         <v>7.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.44</v>
+        <v>6.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="AX7" t="n">
         <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="BB7" t="n">
         <v>6.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="BF7" t="n">
         <v>3.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>11</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -1951,31 +1951,31 @@
         <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
         <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T8" t="n">
         <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
         <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="n">
         <v>32</v>
@@ -2017,7 +2017,7 @@
         <v>16.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM8" t="n">
         <v>200</v>
@@ -2029,62 +2029,62 @@
         <v>290</v>
       </c>
       <c r="AP8" t="n">
-        <v>14.5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="AR8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS8" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS8" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA8" t="n">
         <v>6.4</v>
       </c>
-      <c r="AY8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG8" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2121,19 +2121,19 @@
         <v>2.96</v>
       </c>
       <c r="H9" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="M9" t="n">
         <v>1.13</v>
@@ -2142,7 +2142,7 @@
         <v>2.46</v>
       </c>
       <c r="O9" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="P9" t="n">
         <v>1.48</v>
@@ -2154,7 +2154,7 @@
         <v>1.16</v>
       </c>
       <c r="S9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
         <v>2.16</v>
@@ -2163,10 +2163,10 @@
         <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
         <v>60</v>
       </c>
       <c r="AO9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP9" t="n">
         <v>6.6</v>
@@ -2229,7 +2229,7 @@
         <v>5.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AS9" t="n">
         <v>42</v>
@@ -2238,13 +2238,13 @@
         <v>6.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
         <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX9" t="n">
         <v>6.2</v>
@@ -2265,7 +2265,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BE9" t="n">
         <v>5.8</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H10" t="n">
         <v>1.95</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J10" t="n">
         <v>3.5</v>
@@ -2330,7 +2330,7 @@
         <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
         <v>3.3</v>
@@ -2342,25 +2342,25 @@
         <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
         <v>1.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
         <v>15</v>
@@ -2393,7 +2393,7 @@
         <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>46</v>
@@ -2402,19 +2402,19 @@
         <v>110</v>
       </c>
       <c r="AK10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP10" t="n">
         <v>9.800000000000001</v>
@@ -2432,7 +2432,7 @@
         <v>10.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
         <v>8.199999999999999</v>
@@ -2441,38 +2441,38 @@
         <v>17.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC10" t="n">
         <v>5.6</v>
       </c>
-      <c r="BC10" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
         <v>13.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G11" t="n">
         <v>1.75</v>
@@ -2530,13 +2530,13 @@
         <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
         <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R11" t="n">
         <v>1.5</v>
@@ -2554,7 +2554,7 @@
         <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X11" t="n">
         <v>25</v>
@@ -2602,10 +2602,10 @@
         <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO11" t="n">
         <v>75</v>
@@ -2617,7 +2617,7 @@
         <v>18.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS11" t="n">
         <v>4.4</v>
@@ -2644,7 +2644,7 @@
         <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB11" t="n">
         <v>14.5</v>
@@ -2656,17 +2656,17 @@
         <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
         <v>4.3</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2697,73 +2697,73 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="O12" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="X12" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA12" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC12" t="n">
         <v>8.199999999999999</v>
@@ -2772,7 +2772,7 @@
         <v>17.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
         <v>14</v>
@@ -2781,31 +2781,31 @@
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AN12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>9.199999999999999</v>
@@ -2814,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
@@ -2835,7 +2835,7 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
         <v>7.2</v>
@@ -2844,23 +2844,23 @@
         <v>6.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BG12" t="n">
         <v>7.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -2900,16 +2900,16 @@
         <v>13.5</v>
       </c>
       <c r="I13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="K13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
@@ -2921,19 +2921,19 @@
         <v>1.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="S13" t="n">
         <v>2.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U13" t="n">
         <v>1.69</v>
@@ -2942,7 +2942,7 @@
         <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -2951,7 +2951,7 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -2981,13 +2981,13 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK13" t="n">
         <v>16.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
         <v>260</v>
@@ -2999,16 +2999,16 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AQ13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR13" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR13" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
         <v>9.800000000000001</v>
@@ -3017,10 +3017,10 @@
         <v>5.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
         <v>7</v>
@@ -3029,32 +3029,32 @@
         <v>4.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
         <v>2.94</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="H14" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.75</v>
       </c>
-      <c r="J14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.14</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G15" t="n">
         <v>4.2</v>
@@ -3288,7 +3288,7 @@
         <v>2.06</v>
       </c>
       <c r="I15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J15" t="n">
         <v>3.3</v>
@@ -3300,10 +3300,10 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.35</v>
@@ -3330,13 +3330,13 @@
         <v>1.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
         <v>15</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
         <v>14</v>
@@ -3381,7 +3381,7 @@
         <v>130</v>
       </c>
       <c r="AN15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO15" t="n">
         <v>19.5</v>
@@ -3396,7 +3396,7 @@
         <v>11</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT15" t="n">
         <v>11.5</v>
@@ -3411,7 +3411,7 @@
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY15" t="n">
         <v>13.5</v>
@@ -3420,19 +3420,19 @@
         <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD15" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7</v>
-      </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
         <v>40</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3512,7 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -3867,34 +3867,34 @@
         <v>1.76</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
         <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P18" t="n">
         <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>1.34</v>
@@ -3903,10 +3903,10 @@
         <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U18" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
         <v>1.19</v>
@@ -3915,19 +3915,19 @@
         <v>2.3</v>
       </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z18" t="n">
         <v>46</v>
       </c>
       <c r="AA18" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>8.6</v>
@@ -3939,16 +3939,16 @@
         <v>90</v>
       </c>
       <c r="AF18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ18" t="n">
         <v>17</v>
@@ -3969,16 +3969,16 @@
         <v>110</v>
       </c>
       <c r="AP18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
         <v>38</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AT18" t="n">
         <v>7.2</v>
@@ -3990,10 +3990,10 @@
         <v>21</v>
       </c>
       <c r="AW18" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY18" t="n">
         <v>9</v>
@@ -4002,7 +4002,7 @@
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB18" t="n">
         <v>15.5</v>
@@ -4014,17 +4014,17 @@
         <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G19" t="n">
         <v>1.5</v>
@@ -4070,10 +4070,10 @@
         <v>4.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
@@ -4097,7 +4097,7 @@
         <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
         <v>1.67</v>
@@ -4115,10 +4115,10 @@
         <v>27</v>
       </c>
       <c r="Z19" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA19" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="AB19" t="n">
         <v>7.4</v>
@@ -4154,13 +4154,13 @@
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AO19" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AP19" t="n">
         <v>11.5</v>
@@ -4181,7 +4181,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW19" t="n">
         <v>8.800000000000001</v>
@@ -4196,7 +4196,7 @@
         <v>7.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB19" t="n">
         <v>10</v>
@@ -4214,11 +4214,11 @@
         <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H20" t="n">
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K20" t="n">
         <v>950</v>
@@ -4279,10 +4279,10 @@
         <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
@@ -4291,10 +4291,10 @@
         <v>1.15</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -4357,52 +4357,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -4464,13 +4464,13 @@
         <v>1.31</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P21" t="n">
         <v>2.02</v>
@@ -4479,16 +4479,16 @@
         <v>1.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U21" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="V21" t="n">
         <v>1.48</v>
@@ -4497,116 +4497,116 @@
         <v>1.6</v>
       </c>
       <c r="X21" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z21" t="n">
         <v>25</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC21" t="n">
         <v>19</v>
       </c>
-      <c r="Z21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="BD21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG21" t="n">
         <v>18</v>
       </c>
-      <c r="AC21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G22" t="n">
         <v>1.88</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
@@ -4661,22 +4661,22 @@
         <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R22" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S22" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="T22" t="n">
         <v>1.63</v>
@@ -4685,7 +4685,7 @@
         <v>2.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
         <v>2.12</v>
@@ -4715,7 +4715,7 @@
         <v>60</v>
       </c>
       <c r="AF22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
         <v>13</v>
@@ -4727,7 +4727,7 @@
         <v>60</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK22" t="n">
         <v>970</v>
@@ -4739,7 +4739,7 @@
         <v>85</v>
       </c>
       <c r="AN22" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO22" t="n">
         <v>48</v>
@@ -4748,13 +4748,13 @@
         <v>4.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS22" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.3</v>
       </c>
       <c r="AT22" t="n">
         <v>10.5</v>
@@ -4763,22 +4763,22 @@
         <v>9</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AZ22" t="n">
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB22" t="n">
         <v>4</v>
@@ -4790,17 +4790,17 @@
         <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF22" t="n">
         <v>6.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G23" t="n">
         <v>2.16</v>
@@ -4840,7 +4840,7 @@
         <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J23" t="n">
         <v>3.75</v>
@@ -4849,37 +4849,37 @@
         <v>4.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P23" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
         <v>1.86</v>
@@ -4921,7 +4921,7 @@
         <v>55</v>
       </c>
       <c r="AJ23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK23" t="n">
         <v>25</v>
@@ -4942,10 +4942,10 @@
         <v>3.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AR23" t="n">
-        <v>21</v>
+        <v>3.9</v>
       </c>
       <c r="AS23" t="n">
         <v>4.2</v>
@@ -4957,10 +4957,10 @@
         <v>8</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AX23" t="n">
         <v>12.5</v>
@@ -4975,10 +4975,10 @@
         <v>4.3</v>
       </c>
       <c r="BB23" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="BC23" t="n">
-        <v>14.5</v>
+        <v>3.9</v>
       </c>
       <c r="BD23" t="n">
         <v>4.3</v>
@@ -4987,14 +4987,14 @@
         <v>4.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG23" t="n">
         <v>4.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H24" t="n">
         <v>3.45</v>
@@ -5046,13 +5046,13 @@
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
         <v>1.93</v>
@@ -5061,134 +5061,134 @@
         <v>1.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V24" t="n">
         <v>1.37</v>
       </c>
       <c r="W24" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H25" t="n">
         <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -5246,19 +5246,19 @@
         <v>1.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="R25" t="n">
         <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -5327,52 +5327,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -5446,13 +5446,13 @@
         <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
         <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -5616,10 +5616,10 @@
         <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K27" t="n">
         <v>950</v>
@@ -5640,19 +5640,19 @@
         <v>1.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="R27" t="n">
         <v>1.24</v>
       </c>
       <c r="S27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
@@ -5715,52 +5715,52 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
         <v>1.01</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O28" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P28" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q28" t="n">
         <v>1.01</v>
@@ -5840,7 +5840,7 @@
         <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -6019,13 +6019,13 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O29" t="n">
         <v>1.2</v>
       </c>
       <c r="P29" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q29" t="n">
         <v>1.2</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -6195,16 +6195,16 @@
         <v>2.78</v>
       </c>
       <c r="H30" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I30" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.35</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.4</v>
       </c>
       <c r="L30" t="n">
         <v>1.49</v>
@@ -6213,7 +6213,7 @@
         <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>1.42</v>
@@ -6231,7 +6231,7 @@
         <v>4.3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U30" t="n">
         <v>2.02</v>
@@ -6255,10 +6255,10 @@
         <v>48</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
         <v>13</v>
@@ -6306,7 +6306,7 @@
         <v>17</v>
       </c>
       <c r="AS30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT30" t="n">
         <v>9.199999999999999</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G31" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H31" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="I31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>3.2</v>
@@ -6401,7 +6401,7 @@
         <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
@@ -6413,7 +6413,7 @@
         <v>1.31</v>
       </c>
       <c r="P31" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q31" t="n">
         <v>1.95</v>
@@ -6422,7 +6422,7 @@
         <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T31" t="n">
         <v>1.68</v>
@@ -6431,7 +6431,7 @@
         <v>2.24</v>
       </c>
       <c r="V31" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.53</v>
@@ -6443,10 +6443,10 @@
         <v>14</v>
       </c>
       <c r="Z31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA31" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB31" t="n">
         <v>12.5</v>
@@ -6455,10 +6455,10 @@
         <v>7.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF31" t="n">
         <v>20</v>
@@ -6482,13 +6482,13 @@
         <v>42</v>
       </c>
       <c r="AM31" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN31" t="n">
         <v>26</v>
       </c>
       <c r="AO31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP31" t="n">
         <v>11.5</v>
@@ -6500,7 +6500,7 @@
         <v>18</v>
       </c>
       <c r="AS31" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
@@ -6509,10 +6509,10 @@
         <v>6.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX31" t="n">
         <v>16</v>
@@ -6524,29 +6524,29 @@
         <v>13</v>
       </c>
       <c r="BA31" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BC31" t="n">
         <v>7.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF31" t="n">
         <v>21</v>
       </c>
       <c r="BG31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>2.38</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H32" t="n">
         <v>2.7</v>
@@ -6592,10 +6592,10 @@
         <v>3.6</v>
       </c>
       <c r="K32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
         <v>1.04</v>
@@ -6613,22 +6613,22 @@
         <v>1.67</v>
       </c>
       <c r="R32" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S32" t="n">
         <v>2.6</v>
       </c>
       <c r="T32" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="U32" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W32" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X32" t="n">
         <v>25</v>
@@ -6658,7 +6658,7 @@
         <v>23</v>
       </c>
       <c r="AG32" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH32" t="n">
         <v>16</v>
@@ -6667,19 +6667,19 @@
         <v>36</v>
       </c>
       <c r="AJ32" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK32" t="n">
         <v>30</v>
       </c>
       <c r="AL32" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM32" t="n">
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO32" t="n">
         <v>23</v>
@@ -6694,7 +6694,7 @@
         <v>15.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT32" t="n">
         <v>10</v>
@@ -6718,19 +6718,19 @@
         <v>11</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC32" t="n">
         <v>18</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF32" t="n">
         <v>11.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="G33" t="n">
         <v>990</v>
       </c>
       <c r="H33" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="I33" t="n">
         <v>990</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -6989,22 +6989,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="R34" t="n">
         <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>2.16</v>
       </c>
       <c r="G35" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H35" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K35" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L35" t="n">
         <v>1.39</v>
@@ -7183,7 +7183,7 @@
         <v>1.07</v>
       </c>
       <c r="N35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O35" t="n">
         <v>1.29</v>
@@ -7192,25 +7192,25 @@
         <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S35" t="n">
         <v>3.25</v>
       </c>
       <c r="T35" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U35" t="n">
         <v>2.28</v>
       </c>
       <c r="V35" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X35" t="n">
         <v>15</v>
@@ -7222,16 +7222,16 @@
         <v>28</v>
       </c>
       <c r="AA35" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB35" t="n">
         <v>10.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE35" t="n">
         <v>42</v>
@@ -7267,7 +7267,7 @@
         <v>40</v>
       </c>
       <c r="AP35" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ35" t="n">
         <v>14.5</v>
@@ -7282,7 +7282,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU35" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV35" t="n">
         <v>14</v>
@@ -7294,10 +7294,10 @@
         <v>12.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ35" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA35" t="n">
         <v>44</v>
@@ -7312,17 +7312,17 @@
         <v>30</v>
       </c>
       <c r="BE35" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="BF35" t="n">
         <v>13</v>
       </c>
       <c r="BG35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>3.6</v>
+        <v>1.26</v>
       </c>
       <c r="O36" t="n">
         <v>1.02</v>
@@ -7386,7 +7386,7 @@
         <v>1.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R36" t="n">
         <v>1.24</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -7550,37 +7550,37 @@
         <v>2.78</v>
       </c>
       <c r="G37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H37" t="n">
         <v>3</v>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>2.84</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L37" t="n">
         <v>1.62</v>
       </c>
       <c r="M37" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N37" t="n">
         <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P37" t="n">
         <v>1.41</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
         <v>1.14</v>
@@ -7595,16 +7595,16 @@
         <v>1.66</v>
       </c>
       <c r="V37" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W37" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X37" t="n">
         <v>7.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z37" t="n">
         <v>21</v>
@@ -7616,7 +7616,7 @@
         <v>7.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD37" t="n">
         <v>16.5</v>
@@ -7646,7 +7646,7 @@
         <v>110</v>
       </c>
       <c r="AM37" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN37" t="n">
         <v>70</v>
@@ -7664,7 +7664,7 @@
         <v>16.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT37" t="n">
         <v>6.2</v>
@@ -7676,7 +7676,7 @@
         <v>13</v>
       </c>
       <c r="AW37" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX37" t="n">
         <v>14</v>
@@ -7685,32 +7685,32 @@
         <v>12</v>
       </c>
       <c r="AZ37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA37" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB37" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB37" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BC37" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD37" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG37" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF37" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
         <v>1.24</v>
       </c>
       <c r="S38" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T38" t="n">
         <v>1.11</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>2.82</v>
       </c>
       <c r="G39" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H39" t="n">
         <v>2.6</v>
@@ -7947,10 +7947,10 @@
         <v>2.64</v>
       </c>
       <c r="J39" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K39" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,7 +7959,7 @@
         <v>1.06</v>
       </c>
       <c r="N39" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O39" t="n">
         <v>1.27</v>
@@ -7968,16 +7968,16 @@
         <v>2.18</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R39" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S39" t="n">
         <v>3.05</v>
       </c>
       <c r="T39" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U39" t="n">
         <v>2.4</v>
@@ -7986,7 +7986,7 @@
         <v>1.6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X39" t="n">
         <v>16.5</v>
@@ -8028,7 +8028,7 @@
         <v>44</v>
       </c>
       <c r="AK39" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL39" t="n">
         <v>38</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -8129,170 +8129,170 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G40" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H40" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I40" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J40" t="n">
         <v>3.05</v>
       </c>
       <c r="K40" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M40" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>1.89</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>1.4</v>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q40" t="n">
         <v>2.16</v>
       </c>
       <c r="R40" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
         <v>3.85</v>
       </c>
       <c r="T40" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U40" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V40" t="n">
         <v>1.53</v>
       </c>
       <c r="W40" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y40" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -8347,13 +8347,13 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="O41" t="n">
         <v>1.33</v>
       </c>
       <c r="P41" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q41" t="n">
         <v>1.98</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -8517,170 +8517,170 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="G42" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="H42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N42" t="n">
         <v>3.55</v>
       </c>
-      <c r="I42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K42" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.74</v>
-      </c>
       <c r="O42" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P42" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="R42" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S42" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U42" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V42" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W42" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -8720,43 +8720,43 @@
         <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K43" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M43" t="n">
         <v>1.07</v>
       </c>
       <c r="N43" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R43" t="n">
         <v>1.34</v>
       </c>
-      <c r="P43" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S43" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T43" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="U43" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="V43" t="n">
         <v>1.2</v>
@@ -8774,19 +8774,19 @@
         <v>48</v>
       </c>
       <c r="AA43" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB43" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AC43" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD43" t="n">
         <v>950</v>
       </c>
       <c r="AE43" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF43" t="n">
         <v>12</v>
@@ -8798,7 +8798,7 @@
         <v>950</v>
       </c>
       <c r="AI43" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ43" t="n">
         <v>22</v>
@@ -8810,71 +8810,71 @@
         <v>44</v>
       </c>
       <c r="AM43" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN43" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AO43" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP43" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY43" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS43" t="n">
+      <c r="AZ43" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT43" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW43" t="n">
+      <c r="BA43" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB43" t="n">
         <v>5.1</v>
       </c>
-      <c r="AX43" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BC43" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF43" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -8923,40 +8923,40 @@
         <v>4.3</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M44" t="n">
         <v>1.07</v>
       </c>
       <c r="N44" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O44" t="n">
         <v>1.33</v>
       </c>
       <c r="P44" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R44" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T44" t="n">
         <v>1.87</v>
       </c>
       <c r="U44" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V44" t="n">
         <v>1.2</v>
       </c>
       <c r="W44" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X44" t="n">
         <v>17.5</v>
@@ -8974,7 +8974,7 @@
         <v>9.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD44" t="n">
         <v>26</v>
@@ -8983,7 +8983,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG44" t="n">
         <v>12</v>
@@ -8992,22 +8992,22 @@
         <v>26</v>
       </c>
       <c r="AI44" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="n">
         <v>23</v>
       </c>
       <c r="AK44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL44" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM44" t="n">
         <v>150</v>
       </c>
       <c r="AN44" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO44" t="n">
         <v>110</v>
@@ -9019,10 +9019,10 @@
         <v>14.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT44" t="n">
         <v>6.8</v>
@@ -9034,7 +9034,7 @@
         <v>17.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX44" t="n">
         <v>9</v>
@@ -9046,7 +9046,7 @@
         <v>17.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB44" t="n">
         <v>16</v>
@@ -9055,20 +9055,20 @@
         <v>16</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF44" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG44" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -9099,28 +9099,28 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G45" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="H45" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I45" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K45" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="L45" t="n">
         <v>1.17</v>
       </c>
       <c r="M45" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N45" t="n">
         <v>2.4</v>
@@ -9147,10 +9147,10 @@
         <v>1.11</v>
       </c>
       <c r="V45" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W45" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9305,7 @@
         <v>990</v>
       </c>
       <c r="J46" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="K46" t="n">
         <v>950</v>
@@ -9317,22 +9317,22 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="O46" t="n">
         <v>1.17</v>
       </c>
       <c r="P46" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="R46" t="n">
         <v>1.24</v>
       </c>
       <c r="S46" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T46" t="n">
         <v>1.11</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K47" t="n">
         <v>950</v>
@@ -9511,13 +9511,13 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="O47" t="n">
         <v>1.18</v>
       </c>
       <c r="P47" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q47" t="n">
         <v>1.18</v>
@@ -9529,10 +9529,10 @@
         <v>1.18</v>
       </c>
       <c r="T47" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U47" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V47" t="n">
         <v>1.01</v>
@@ -9595,52 +9595,52 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF47" t="n">
         <v>1.01</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -9681,58 +9681,58 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="G48" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="H48" t="n">
         <v>7.6</v>
       </c>
       <c r="I48" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="J48" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N48" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O48" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P48" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="R48" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S48" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="T48" t="n">
         <v>1.86</v>
       </c>
       <c r="U48" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V48" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W48" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
         <v>950</v>
@@ -9741,22 +9741,22 @@
         <v>950</v>
       </c>
       <c r="Z48" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA48" t="n">
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD48" t="n">
         <v>950</v>
       </c>
       <c r="AE48" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF48" t="n">
         <v>970</v>
@@ -9768,10 +9768,10 @@
         <v>950</v>
       </c>
       <c r="AI48" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ48" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK48" t="n">
         <v>16.5</v>
@@ -9780,49 +9780,49 @@
         <v>38</v>
       </c>
       <c r="AM48" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN48" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO48" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP48" t="n">
         <v>19</v>
       </c>
       <c r="AQ48" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AR48" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS48" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT48" t="n">
         <v>8</v>
       </c>
       <c r="AU48" t="n">
-        <v>10.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV48" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AW48" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX48" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY48" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ48" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BA48" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB48" t="n">
         <v>9.199999999999999</v>
@@ -9831,20 +9831,20 @@
         <v>11</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE48" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF48" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BG48" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G49" t="n">
         <v>2.28</v>
@@ -9884,19 +9884,19 @@
         <v>3.4</v>
       </c>
       <c r="I49" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="K49" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M49" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N49" t="n">
         <v>4.7</v>
@@ -9905,22 +9905,22 @@
         <v>1.26</v>
       </c>
       <c r="P49" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="R49" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S49" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U49" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V49" t="n">
         <v>1.36</v>
@@ -9929,116 +9929,116 @@
         <v>1.79</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y49" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z49" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL49" t="n">
         <v>36</v>
       </c>
-      <c r="AA49" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC49" t="n">
+      <c r="AM49" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ49" t="n">
         <v>11</v>
       </c>
-      <c r="AD49" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AQ49" t="n">
+      <c r="AR49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX49" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR49" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AV49" t="n">
+      <c r="AY49" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF49" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>10</v>
-      </c>
       <c r="BG49" t="n">
-        <v>1.77</v>
+        <v>3.85</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -10069,13 +10069,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="G50" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H50" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I50" t="n">
         <v>6.8</v>
@@ -10084,7 +10084,7 @@
         <v>4.8</v>
       </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -10093,40 +10093,40 @@
         <v>1.03</v>
       </c>
       <c r="N50" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O50" t="n">
         <v>1.2</v>
       </c>
       <c r="P50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S50" t="n">
         <v>2.48</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.44</v>
       </c>
       <c r="T50" t="n">
         <v>1.73</v>
       </c>
       <c r="U50" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V50" t="n">
         <v>1.17</v>
       </c>
       <c r="W50" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="X50" t="n">
         <v>24</v>
       </c>
       <c r="Y50" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="Z50" t="n">
         <v>60</v>
@@ -10141,13 +10141,13 @@
         <v>11.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE50" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF50" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG50" t="n">
         <v>10.5</v>
@@ -10159,7 +10159,7 @@
         <v>85</v>
       </c>
       <c r="AJ50" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK50" t="n">
         <v>15.5</v>
@@ -10174,7 +10174,7 @@
         <v>6.4</v>
       </c>
       <c r="AO50" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP50" t="n">
         <v>21</v>
@@ -10183,10 +10183,10 @@
         <v>22</v>
       </c>
       <c r="AR50" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS50" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT50" t="n">
         <v>10</v>
@@ -10195,10 +10195,10 @@
         <v>10</v>
       </c>
       <c r="AV50" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX50" t="n">
         <v>9.800000000000001</v>
@@ -10207,10 +10207,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ50" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB50" t="n">
         <v>13</v>
@@ -10222,17 +10222,17 @@
         <v>24</v>
       </c>
       <c r="BE50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF50" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG50" t="n">
-        <v>13.5</v>
+        <v>50</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
         <v>4.8</v>
       </c>
       <c r="K51" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L51" t="n">
         <v>1.3</v>
@@ -10287,79 +10287,79 @@
         <v>1.05</v>
       </c>
       <c r="N51" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O51" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P51" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="R51" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S51" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="T51" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U51" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V51" t="n">
         <v>1.13</v>
       </c>
       <c r="W51" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X51" t="n">
         <v>19</v>
       </c>
       <c r="Y51" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Z51" t="n">
         <v>75</v>
       </c>
       <c r="AA51" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB51" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC51" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD51" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AE51" t="n">
         <v>130</v>
       </c>
       <c r="AF51" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AG51" t="n">
         <v>10.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI51" t="n">
         <v>120</v>
       </c>
       <c r="AJ51" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK51" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL51" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM51" t="n">
         <v>120</v>
@@ -10368,31 +10368,31 @@
         <v>7.4</v>
       </c>
       <c r="AO51" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP51" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ51" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="AR51" t="n">
-        <v>3.35</v>
+        <v>8.6</v>
       </c>
       <c r="AS51" t="n">
-        <v>3.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT51" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU51" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV51" t="n">
-        <v>5.1</v>
+        <v>26</v>
       </c>
       <c r="AW51" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX51" t="n">
         <v>8.199999999999999</v>
@@ -10404,29 +10404,29 @@
         <v>21</v>
       </c>
       <c r="BA51" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB51" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC51" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.2</v>
+        <v>17.5</v>
       </c>
       <c r="BE51" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF51" t="n">
         <v>6</v>
       </c>
       <c r="BG51" t="n">
-        <v>3.25</v>
+        <v>9</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -10457,22 +10457,22 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G52" t="n">
         <v>4.9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="I52" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="J52" t="n">
         <v>4.3</v>
       </c>
       <c r="K52" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10481,19 +10481,19 @@
         <v>1.04</v>
       </c>
       <c r="N52" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O52" t="n">
         <v>1.19</v>
       </c>
       <c r="P52" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="R52" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S52" t="n">
         <v>2.4</v>
@@ -10502,13 +10502,13 @@
         <v>1.6</v>
       </c>
       <c r="U52" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V52" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="W52" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X52" t="n">
         <v>950</v>
@@ -10520,7 +10520,7 @@
         <v>14</v>
       </c>
       <c r="AA52" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AB52" t="n">
         <v>950</v>
@@ -10538,13 +10538,13 @@
         <v>40</v>
       </c>
       <c r="AG52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH52" t="n">
         <v>17</v>
       </c>
       <c r="AI52" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ52" t="n">
         <v>110</v>
@@ -10556,7 +10556,7 @@
         <v>55</v>
       </c>
       <c r="AM52" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN52" t="n">
         <v>42</v>
@@ -10565,7 +10565,7 @@
         <v>8.4</v>
       </c>
       <c r="AP52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ52" t="n">
         <v>11</v>
@@ -10574,22 +10574,22 @@
         <v>12</v>
       </c>
       <c r="AS52" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AT52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU52" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV52" t="n">
         <v>9.4</v>
       </c>
       <c r="AW52" t="n">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX52" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY52" t="n">
         <v>16.5</v>
@@ -10598,29 +10598,29 @@
         <v>15</v>
       </c>
       <c r="BA52" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB52" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC52" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BD52" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BE52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BF52" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
         <v>1.01</v>
       </c>
       <c r="M53" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N53" t="n">
         <v>3.15</v>
@@ -10681,22 +10681,22 @@
         <v>1.39</v>
       </c>
       <c r="P53" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q53" t="n">
         <v>2.14</v>
       </c>
       <c r="R53" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
       </c>
       <c r="T53" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U53" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V53" t="n">
         <v>1.26</v>
@@ -10714,10 +10714,10 @@
         <v>40</v>
       </c>
       <c r="AA53" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB53" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC53" t="n">
         <v>8.4</v>
@@ -10738,25 +10738,25 @@
         <v>25</v>
       </c>
       <c r="AI53" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL53" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM53" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN53" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO53" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP53" t="n">
         <v>10.5</v>
@@ -10765,10 +10765,10 @@
         <v>11.5</v>
       </c>
       <c r="AR53" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS53" t="n">
         <v>6</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>6.6</v>
       </c>
       <c r="AT53" t="n">
         <v>6.8</v>
@@ -10780,7 +10780,7 @@
         <v>16</v>
       </c>
       <c r="AW53" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AX53" t="n">
         <v>9.800000000000001</v>
@@ -10792,7 +10792,7 @@
         <v>19</v>
       </c>
       <c r="BA53" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB53" t="n">
         <v>19.5</v>
@@ -10801,7 +10801,7 @@
         <v>19.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE53" t="n">
         <v>6</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -10854,13 +10854,13 @@
         <v>16</v>
       </c>
       <c r="I54" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L54" t="n">
         <v>1.24</v>
@@ -10881,13 +10881,13 @@
         <v>1.44</v>
       </c>
       <c r="R54" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S54" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T54" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U54" t="n">
         <v>1.89</v>
@@ -10899,7 +10899,7 @@
         <v>5.4</v>
       </c>
       <c r="X54" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y54" t="n">
         <v>60</v>
@@ -10923,7 +10923,7 @@
         <v>240</v>
       </c>
       <c r="AF54" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG54" t="n">
         <v>12</v>
@@ -10935,16 +10935,16 @@
         <v>170</v>
       </c>
       <c r="AJ54" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AK54" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL54" t="n">
         <v>38</v>
       </c>
       <c r="AM54" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN54" t="n">
         <v>3.25</v>
@@ -10953,16 +10953,16 @@
         <v>340</v>
       </c>
       <c r="AP54" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AQ54" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AR54" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AS54" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AT54" t="n">
         <v>12</v>
@@ -10971,7 +10971,7 @@
         <v>17</v>
       </c>
       <c r="AV54" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AW54" t="n">
         <v>75</v>
@@ -10983,22 +10983,22 @@
         <v>11</v>
       </c>
       <c r="AZ54" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA54" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BB54" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC54" t="n">
         <v>12</v>
       </c>
       <c r="BD54" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE54" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="BF54" t="n">
         <v>3.15</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
         <v>3.55</v>
       </c>
       <c r="G55" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H55" t="n">
         <v>2.02</v>
@@ -11051,7 +11051,7 @@
         <v>2.06</v>
       </c>
       <c r="J55" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K55" t="n">
         <v>4.5</v>
@@ -11093,55 +11093,55 @@
         <v>1.37</v>
       </c>
       <c r="X55" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y55" t="n">
         <v>15</v>
       </c>
       <c r="Z55" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AB55" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AC55" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD55" t="n">
         <v>11</v>
       </c>
-      <c r="AD55" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AE55" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AF55" t="n">
         <v>32</v>
       </c>
       <c r="AG55" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI55" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AJ55" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK55" t="n">
         <v>36</v>
       </c>
       <c r="AL55" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM55" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN55" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO55" t="n">
         <v>8.6</v>
@@ -11150,16 +11150,16 @@
         <v>24</v>
       </c>
       <c r="AQ55" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR55" t="n">
         <v>15</v>
       </c>
       <c r="AS55" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT55" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU55" t="n">
         <v>9.6</v>
@@ -11171,7 +11171,7 @@
         <v>16.5</v>
       </c>
       <c r="AX55" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AY55" t="n">
         <v>14.5</v>
@@ -11183,26 +11183,26 @@
         <v>22</v>
       </c>
       <c r="BB55" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BC55" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BD55" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE55" t="n">
-        <v>7.8</v>
+        <v>46</v>
       </c>
       <c r="BF55" t="n">
         <v>19.5</v>
       </c>
       <c r="BG55" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G56" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H56" t="n">
         <v>2.18</v>
@@ -11272,7 +11272,7 @@
         <v>1.72</v>
       </c>
       <c r="S56" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T56" t="n">
         <v>1.51</v>
@@ -11281,16 +11281,16 @@
         <v>2.82</v>
       </c>
       <c r="V56" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W56" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X56" t="n">
         <v>25</v>
       </c>
       <c r="Y56" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z56" t="n">
         <v>17.5</v>
@@ -11314,7 +11314,7 @@
         <v>29</v>
       </c>
       <c r="AG56" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH56" t="n">
         <v>14</v>
@@ -11335,7 +11335,7 @@
         <v>48</v>
       </c>
       <c r="AN56" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO56" t="n">
         <v>9.6</v>
@@ -11353,7 +11353,7 @@
         <v>25</v>
       </c>
       <c r="AT56" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU56" t="n">
         <v>9</v>
@@ -11365,7 +11365,7 @@
         <v>17.5</v>
       </c>
       <c r="AX56" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY56" t="n">
         <v>14</v>
@@ -11377,7 +11377,7 @@
         <v>24</v>
       </c>
       <c r="BB56" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC56" t="n">
         <v>28</v>
@@ -11389,14 +11389,14 @@
         <v>40</v>
       </c>
       <c r="BF56" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG56" t="n">
         <v>8.6</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -11430,13 +11430,13 @@
         <v>2.26</v>
       </c>
       <c r="G57" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H57" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I57" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
         <v>3.25</v>
@@ -11454,13 +11454,13 @@
         <v>2.74</v>
       </c>
       <c r="O57" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P57" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R57" t="n">
         <v>1.2</v>
@@ -11469,22 +11469,22 @@
         <v>5.7</v>
       </c>
       <c r="T57" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U57" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V57" t="n">
         <v>1.33</v>
       </c>
       <c r="W57" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X57" t="n">
         <v>8.6</v>
       </c>
       <c r="Y57" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z57" t="n">
         <v>25</v>
@@ -11496,7 +11496,7 @@
         <v>7.4</v>
       </c>
       <c r="AC57" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD57" t="n">
         <v>17.5</v>
@@ -11511,7 +11511,7 @@
         <v>12.5</v>
       </c>
       <c r="AH57" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI57" t="n">
         <v>95</v>
@@ -11568,7 +11568,7 @@
         <v>23</v>
       </c>
       <c r="BA57" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="BB57" t="n">
         <v>26</v>
@@ -11586,11 +11586,11 @@
         <v>26</v>
       </c>
       <c r="BG57" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11648,7 @@
         <v>3.3</v>
       </c>
       <c r="O58" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P58" t="n">
         <v>1.87</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G59" t="n">
         <v>2.38</v>
@@ -11827,7 +11827,7 @@
         <v>4.2</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K59" t="n">
         <v>3.15</v>
@@ -11836,7 +11836,7 @@
         <v>1.01</v>
       </c>
       <c r="M59" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N59" t="n">
         <v>2.62</v>
@@ -11845,13 +11845,13 @@
         <v>1.54</v>
       </c>
       <c r="P59" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="R59" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S59" t="n">
         <v>5.3</v>
@@ -11863,7 +11863,7 @@
         <v>1.79</v>
       </c>
       <c r="V59" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W59" t="n">
         <v>1.72</v>
@@ -11881,19 +11881,19 @@
         <v>110</v>
       </c>
       <c r="AB59" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AC59" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD59" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE59" t="n">
         <v>80</v>
       </c>
       <c r="AF59" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AG59" t="n">
         <v>13</v>
@@ -11905,80 +11905,80 @@
         <v>110</v>
       </c>
       <c r="AJ59" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK59" t="n">
         <v>38</v>
       </c>
-      <c r="AK59" t="n">
-        <v>32</v>
-      </c>
       <c r="AL59" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM59" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN59" t="n">
         <v>38</v>
       </c>
       <c r="AO59" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP59" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AQ59" t="n">
         <v>10</v>
       </c>
       <c r="AR59" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AS59" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT59" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="AU59" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AV59" t="n">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="AW59" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX59" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AY59" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AZ59" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BA59" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB59" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BC59" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BD59" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE59" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF59" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BG59" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -12009,19 +12009,19 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G60" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H60" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I60" t="n">
         <v>4.1</v>
       </c>
       <c r="J60" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K60" t="n">
         <v>3.65</v>
@@ -12033,7 +12033,7 @@
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O60" t="n">
         <v>1.45</v>
@@ -12060,7 +12060,7 @@
         <v>1.32</v>
       </c>
       <c r="W60" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -12206,7 +12206,7 @@
         <v>1.46</v>
       </c>
       <c r="G61" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="H61" t="n">
         <v>5</v>
@@ -12215,7 +12215,7 @@
         <v>10.5</v>
       </c>
       <c r="J61" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="K61" t="n">
         <v>5.1</v>
@@ -12236,7 +12236,7 @@
         <v>1.81</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="R61" t="n">
         <v>1.28</v>
@@ -12254,7 +12254,7 @@
         <v>1.1</v>
       </c>
       <c r="W61" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -12403,7 +12403,7 @@
         <v>2.36</v>
       </c>
       <c r="H62" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I62" t="n">
         <v>3.35</v>
@@ -12412,7 +12412,7 @@
         <v>3.65</v>
       </c>
       <c r="K62" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L62" t="n">
         <v>1.36</v>
@@ -12439,7 +12439,7 @@
         <v>3</v>
       </c>
       <c r="T62" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U62" t="n">
         <v>2.36</v>
@@ -12448,7 +12448,7 @@
         <v>1.42</v>
       </c>
       <c r="W62" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X62" t="n">
         <v>21</v>
@@ -12466,7 +12466,7 @@
         <v>14</v>
       </c>
       <c r="AC62" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD62" t="n">
         <v>16.5</v>
@@ -12478,7 +12478,7 @@
         <v>19</v>
       </c>
       <c r="AG62" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH62" t="n">
         <v>18.5</v>
@@ -12499,7 +12499,7 @@
         <v>85</v>
       </c>
       <c r="AN62" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO62" t="n">
         <v>32</v>
@@ -12514,7 +12514,7 @@
         <v>21</v>
       </c>
       <c r="AS62" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT62" t="n">
         <v>10.5</v>
@@ -12526,7 +12526,7 @@
         <v>12</v>
       </c>
       <c r="AW62" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AX62" t="n">
         <v>14.5</v>
@@ -12538,19 +12538,19 @@
         <v>14</v>
       </c>
       <c r="BA62" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB62" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC62" t="n">
         <v>20</v>
       </c>
       <c r="BD62" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE62" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF62" t="n">
         <v>11.5</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -12591,170 +12591,170 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="G63" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="H63" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I63" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W63" t="n">
+        <v>2</v>
+      </c>
+      <c r="X63" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY63" t="n">
         <v>3.6</v>
       </c>
-      <c r="I63" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="K63" t="n">
-        <v>13</v>
-      </c>
-      <c r="L63" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N63" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>2</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY63" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AZ63" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA63" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF63" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
         <v>2.98</v>
       </c>
       <c r="H64" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I64" t="n">
         <v>2.5</v>
@@ -12818,7 +12818,7 @@
         <v>2.8</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R64" t="n">
         <v>1.71</v>
@@ -12833,13 +12833,13 @@
         <v>2.8</v>
       </c>
       <c r="V64" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W64" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X64" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y64" t="n">
         <v>18.5</v>
@@ -12863,7 +12863,7 @@
         <v>26</v>
       </c>
       <c r="AF64" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG64" t="n">
         <v>16</v>
@@ -12902,7 +12902,7 @@
         <v>18</v>
       </c>
       <c r="AS64" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT64" t="n">
         <v>16</v>
@@ -12926,19 +12926,19 @@
         <v>12</v>
       </c>
       <c r="BA64" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB64" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC64" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD64" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE64" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF64" t="n">
         <v>11.5</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -12982,10 +12982,10 @@
         <v>1.99</v>
       </c>
       <c r="G65" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H65" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I65" t="n">
         <v>3.9</v>
@@ -13009,10 +13009,10 @@
         <v>1.2</v>
       </c>
       <c r="P65" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R65" t="n">
         <v>1.61</v>
@@ -13030,7 +13030,7 @@
         <v>1.34</v>
       </c>
       <c r="W65" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X65" t="n">
         <v>29</v>
@@ -13051,10 +13051,10 @@
         <v>12</v>
       </c>
       <c r="AD65" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE65" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF65" t="n">
         <v>19</v>
@@ -13063,10 +13063,10 @@
         <v>13.5</v>
       </c>
       <c r="AH65" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI65" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ65" t="n">
         <v>29</v>
@@ -13084,7 +13084,7 @@
         <v>11.5</v>
       </c>
       <c r="AO65" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP65" t="n">
         <v>20</v>
@@ -13093,10 +13093,10 @@
         <v>16.5</v>
       </c>
       <c r="AR65" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS65" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT65" t="n">
         <v>11.5</v>
@@ -13108,7 +13108,7 @@
         <v>13.5</v>
       </c>
       <c r="AW65" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX65" t="n">
         <v>13</v>
@@ -13129,20 +13129,20 @@
         <v>16</v>
       </c>
       <c r="BD65" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BE65" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF65" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG65" t="n">
         <v>19.5</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -13191,7 +13191,7 @@
         <v>4.6</v>
       </c>
       <c r="L66" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M66" t="n">
         <v>1.02</v>
@@ -13203,22 +13203,22 @@
         <v>1.12</v>
       </c>
       <c r="P66" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="R66" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S66" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="T66" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="U66" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V66" t="n">
         <v>1.83</v>
@@ -13269,25 +13269,25 @@
         <v>36</v>
       </c>
       <c r="AL66" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM66" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN66" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO66" t="n">
         <v>7.6</v>
       </c>
       <c r="AP66" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ66" t="n">
         <v>15</v>
       </c>
       <c r="AR66" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="AS66" t="n">
         <v>21</v>
@@ -13305,7 +13305,7 @@
         <v>14</v>
       </c>
       <c r="AX66" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY66" t="n">
         <v>11.5</v>
@@ -13317,7 +13317,7 @@
         <v>16.5</v>
       </c>
       <c r="BB66" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC66" t="n">
         <v>21</v>
@@ -13326,7 +13326,7 @@
         <v>21</v>
       </c>
       <c r="BE66" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF66" t="n">
         <v>10</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -13370,19 +13370,19 @@
         <v>2.88</v>
       </c>
       <c r="G67" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H67" t="n">
         <v>2.6</v>
       </c>
       <c r="I67" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J67" t="n">
         <v>3.55</v>
       </c>
       <c r="K67" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L67" t="n">
         <v>1.37</v>
@@ -13412,19 +13412,19 @@
         <v>1.67</v>
       </c>
       <c r="U67" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V67" t="n">
         <v>1.61</v>
       </c>
       <c r="W67" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X67" t="n">
         <v>16.5</v>
       </c>
       <c r="Y67" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z67" t="n">
         <v>18</v>
@@ -13478,7 +13478,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR67" t="n">
         <v>16</v>
@@ -13523,14 +13523,14 @@
         <v>34</v>
       </c>
       <c r="BF67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG67" t="n">
         <v>17</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13585,7 @@
         <v>1.06</v>
       </c>
       <c r="N68" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O68" t="n">
         <v>1.3</v>
@@ -13597,7 +13597,7 @@
         <v>1.89</v>
       </c>
       <c r="R68" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S68" t="n">
         <v>3.25</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -13761,7 +13761,7 @@
         <v>3.3</v>
       </c>
       <c r="H69" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I69" t="n">
         <v>2.36</v>
@@ -13782,7 +13782,7 @@
         <v>4.7</v>
       </c>
       <c r="O69" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P69" t="n">
         <v>2.26</v>
@@ -13800,7 +13800,7 @@
         <v>1.64</v>
       </c>
       <c r="U69" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V69" t="n">
         <v>1.73</v>
@@ -13812,7 +13812,7 @@
         <v>970</v>
       </c>
       <c r="Y69" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z69" t="n">
         <v>970</v>
@@ -13833,10 +13833,10 @@
         <v>23</v>
       </c>
       <c r="AF69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG69" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH69" t="n">
         <v>16</v>
@@ -13851,19 +13851,19 @@
         <v>34</v>
       </c>
       <c r="AL69" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM69" t="n">
         <v>70</v>
       </c>
       <c r="AN69" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO69" t="n">
         <v>14.5</v>
       </c>
       <c r="AP69" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ69" t="n">
         <v>11</v>
@@ -13872,7 +13872,7 @@
         <v>14.5</v>
       </c>
       <c r="AS69" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT69" t="n">
         <v>13.5</v>
@@ -13884,7 +13884,7 @@
         <v>10</v>
       </c>
       <c r="AW69" t="n">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="AX69" t="n">
         <v>21</v>
@@ -13893,32 +13893,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ69" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA69" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF69" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BB69" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC69" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD69" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE69" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF69" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BG69" t="n">
         <v>12</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -13973,7 +13973,7 @@
         <v>1.09</v>
       </c>
       <c r="N70" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O70" t="n">
         <v>1.4</v>
@@ -14012,10 +14012,10 @@
         <v>85</v>
       </c>
       <c r="AA70" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AB70" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC70" t="n">
         <v>11</v>
@@ -14027,7 +14027,7 @@
         <v>200</v>
       </c>
       <c r="AF70" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG70" t="n">
         <v>12</v>
@@ -14063,10 +14063,10 @@
         <v>18.5</v>
       </c>
       <c r="AR70" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS70" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT70" t="n">
         <v>5.6</v>
@@ -14075,22 +14075,22 @@
         <v>8.4</v>
       </c>
       <c r="AV70" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW70" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX70" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY70" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ70" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA70" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB70" t="n">
         <v>11.5</v>
@@ -14099,20 +14099,20 @@
         <v>16</v>
       </c>
       <c r="BD70" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE70" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF70" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG70" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -14143,22 +14143,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G71" t="n">
         <v>2.9</v>
       </c>
       <c r="H71" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I71" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J71" t="n">
         <v>3.7</v>
       </c>
       <c r="K71" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L71" t="n">
         <v>1.34</v>
@@ -14182,7 +14182,7 @@
         <v>1.5</v>
       </c>
       <c r="S71" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T71" t="n">
         <v>1.62</v>
@@ -14191,7 +14191,7 @@
         <v>2.42</v>
       </c>
       <c r="V71" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W71" t="n">
         <v>1.52</v>
@@ -14227,7 +14227,7 @@
         <v>13.5</v>
       </c>
       <c r="AH71" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI71" t="n">
         <v>36</v>
@@ -14251,7 +14251,7 @@
         <v>17.5</v>
       </c>
       <c r="AP71" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ71" t="n">
         <v>11</v>
@@ -14260,7 +14260,7 @@
         <v>16.5</v>
       </c>
       <c r="AS71" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT71" t="n">
         <v>12</v>
@@ -14287,26 +14287,26 @@
         <v>27</v>
       </c>
       <c r="BB71" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD71" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BC71" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD71" t="n">
-        <v>7.6</v>
       </c>
       <c r="BE71" t="n">
         <v>8.6</v>
       </c>
       <c r="BF71" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BG71" t="n">
         <v>14</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
         <v>2.14</v>
       </c>
       <c r="J72" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K72" t="n">
         <v>3.95</v>
@@ -14367,7 +14367,7 @@
         <v>1.2</v>
       </c>
       <c r="P72" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q72" t="n">
         <v>1.63</v>
@@ -14385,7 +14385,7 @@
         <v>2.66</v>
       </c>
       <c r="V72" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W72" t="n">
         <v>1.34</v>
@@ -14406,7 +14406,7 @@
         <v>23</v>
       </c>
       <c r="AC72" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD72" t="n">
         <v>13</v>
@@ -14469,7 +14469,7 @@
         <v>16</v>
       </c>
       <c r="AX72" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY72" t="n">
         <v>13.5</v>
@@ -14478,19 +14478,19 @@
         <v>12.5</v>
       </c>
       <c r="BA72" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB72" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD72" t="n">
         <v>5</v>
       </c>
-      <c r="BC72" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD72" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE72" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF72" t="n">
         <v>20</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
         <v>3.9</v>
       </c>
       <c r="H73" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I73" t="n">
         <v>2.02</v>
@@ -14567,7 +14567,7 @@
         <v>1.54</v>
       </c>
       <c r="R73" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S73" t="n">
         <v>2.34</v>
@@ -14576,7 +14576,7 @@
         <v>1.52</v>
       </c>
       <c r="U73" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V73" t="n">
         <v>1.98</v>
@@ -14621,37 +14621,37 @@
         <v>29</v>
       </c>
       <c r="AJ73" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK73" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL73" t="n">
         <v>42</v>
       </c>
       <c r="AM73" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN73" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO73" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP73" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AQ73" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR73" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS73" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT73" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AU73" t="n">
         <v>9.4</v>
@@ -14663,7 +14663,7 @@
         <v>15.5</v>
       </c>
       <c r="AX73" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AY73" t="n">
         <v>14</v>
@@ -14672,29 +14672,29 @@
         <v>13</v>
       </c>
       <c r="BA73" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB73" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD73" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC73" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD73" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE73" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF73" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BG73" t="n">
         <v>6.6</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14728,7 @@
         <v>1.82</v>
       </c>
       <c r="G74" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H74" t="n">
         <v>4.4</v>
@@ -14737,10 +14737,10 @@
         <v>4.8</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K74" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L74" t="n">
         <v>1.33</v>
@@ -14752,7 +14752,7 @@
         <v>5</v>
       </c>
       <c r="O74" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P74" t="n">
         <v>2.36</v>
@@ -14767,7 +14767,7 @@
         <v>2.74</v>
       </c>
       <c r="T74" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U74" t="n">
         <v>2.28</v>
@@ -14866,7 +14866,7 @@
         <v>14.5</v>
       </c>
       <c r="BA74" t="n">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="BB74" t="n">
         <v>5.7</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -14928,7 +14928,7 @@
         <v>3.7</v>
       </c>
       <c r="I75" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J75" t="n">
         <v>3.4</v>
@@ -14937,16 +14937,16 @@
         <v>3.95</v>
       </c>
       <c r="L75" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M75" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N75" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="O75" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P75" t="n">
         <v>1.87</v>
@@ -14955,134 +14955,134 @@
         <v>1.9</v>
       </c>
       <c r="R75" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="S75" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="T75" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U75" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V75" t="n">
         <v>1.3</v>
       </c>
       <c r="W75" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X75" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y75" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z75" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AA75" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB75" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC75" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF75" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD75" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO75" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ75" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT75" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU75" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV75" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX75" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY75" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ75" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE75" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF75" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG75" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G76" t="n">
         <v>1.93</v>
@@ -15137,13 +15137,13 @@
         <v>1.03</v>
       </c>
       <c r="N76" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O76" t="n">
         <v>1.19</v>
       </c>
       <c r="P76" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q76" t="n">
         <v>1.58</v>
@@ -15158,7 +15158,7 @@
         <v>1.58</v>
       </c>
       <c r="U76" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="V76" t="n">
         <v>1.28</v>
@@ -15167,7 +15167,7 @@
         <v>2.06</v>
       </c>
       <c r="X76" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y76" t="n">
         <v>24</v>
@@ -15188,7 +15188,7 @@
         <v>19</v>
       </c>
       <c r="AE76" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF76" t="n">
         <v>15.5</v>
@@ -15215,13 +15215,13 @@
         <v>60</v>
       </c>
       <c r="AN76" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO76" t="n">
         <v>38</v>
       </c>
       <c r="AP76" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ76" t="n">
         <v>19</v>
@@ -15230,7 +15230,7 @@
         <v>25</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT76" t="n">
         <v>11.5</v>
@@ -15257,13 +15257,13 @@
         <v>30</v>
       </c>
       <c r="BB76" t="n">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="BC76" t="n">
         <v>14.5</v>
       </c>
       <c r="BD76" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE76" t="n">
         <v>40</v>
@@ -15272,11 +15272,11 @@
         <v>7</v>
       </c>
       <c r="BG76" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -15310,19 +15310,19 @@
         <v>1.71</v>
       </c>
       <c r="G77" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H77" t="n">
         <v>4.6</v>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J77" t="n">
         <v>4.3</v>
       </c>
       <c r="K77" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L77" t="n">
         <v>1.27</v>
@@ -15343,7 +15343,7 @@
         <v>1.52</v>
       </c>
       <c r="R77" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S77" t="n">
         <v>2.32</v>
@@ -15358,22 +15358,22 @@
         <v>1.25</v>
       </c>
       <c r="W77" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X77" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Y77" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Z77" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA77" t="n">
         <v>120</v>
       </c>
       <c r="AB77" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AC77" t="n">
         <v>11.5</v>
@@ -15391,22 +15391,22 @@
         <v>11</v>
       </c>
       <c r="AH77" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI77" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AJ77" t="n">
         <v>19</v>
       </c>
       <c r="AK77" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL77" t="n">
         <v>26</v>
       </c>
       <c r="AM77" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN77" t="n">
         <v>6.8</v>
@@ -15415,16 +15415,16 @@
         <v>38</v>
       </c>
       <c r="AP77" t="n">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT77" t="n">
         <v>11.5</v>
@@ -15433,13 +15433,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV77" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AW77" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX77" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY77" t="n">
         <v>9.4</v>
@@ -15448,29 +15448,29 @@
         <v>14.5</v>
       </c>
       <c r="BA77" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB77" t="n">
         <v>16</v>
       </c>
       <c r="BC77" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BD77" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BE77" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF77" t="n">
         <v>5.1</v>
       </c>
       <c r="BG77" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -15501,7 +15501,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G78" t="n">
         <v>2.02</v>
@@ -15528,7 +15528,7 @@
         <v>5.2</v>
       </c>
       <c r="O78" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P78" t="n">
         <v>2.42</v>
@@ -15543,13 +15543,13 @@
         <v>2.66</v>
       </c>
       <c r="T78" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U78" t="n">
         <v>2.52</v>
       </c>
       <c r="V78" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W78" t="n">
         <v>1.98</v>
@@ -15603,7 +15603,7 @@
         <v>65</v>
       </c>
       <c r="AN78" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO78" t="n">
         <v>32</v>
@@ -15618,7 +15618,7 @@
         <v>27</v>
       </c>
       <c r="AS78" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT78" t="n">
         <v>11</v>
@@ -15642,7 +15642,7 @@
         <v>14.5</v>
       </c>
       <c r="BA78" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB78" t="n">
         <v>21</v>
@@ -15654,7 +15654,7 @@
         <v>24</v>
       </c>
       <c r="BE78" t="n">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BF78" t="n">
         <v>9.199999999999999</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>
@@ -15695,62 +15695,62 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="G79" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="H79" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I79" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="J79" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="K79" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X79" t="n">
         <v>950</v>
       </c>
-      <c r="L79" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M79" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N79" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P79" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S79" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U79" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V79" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X79" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y79" t="n">
         <v>1000</v>
       </c>
@@ -15764,7 +15764,7 @@
         <v>1000</v>
       </c>
       <c r="AC79" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD79" t="n">
         <v>1000</v>
@@ -15803,62 +15803,62 @@
         <v>1000</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG79" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-05-12 02:17:22</t>
+          <t>2026-05-12 04:34:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
         <v>4.7</v>
@@ -781,10 +781,10 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
         <v>1.66</v>
@@ -799,16 +799,16 @@
         <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
@@ -823,7 +823,7 @@
         <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
         <v>7.8</v>
@@ -862,7 +862,7 @@
         <v>25</v>
       </c>
       <c r="AO2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
         <v>8.199999999999999</v>
@@ -871,10 +871,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
         <v>6.2</v>
@@ -883,44 +883,44 @@
         <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY2" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF2" t="n">
         <v>19</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
         <v>2.04</v>
@@ -969,7 +969,7 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -981,13 +981,13 @@
         <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
         <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
         <v>3.7</v>
@@ -1065,22 +1065,22 @@
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU3" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
         <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
@@ -1104,17 +1104,17 @@
         <v>8.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
         <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -1148,28 +1148,28 @@
         <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H4" t="n">
         <v>2.94</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
         <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.37</v>
@@ -1181,7 +1181,7 @@
         <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
         <v>3.85</v>
@@ -1196,13 +1196,13 @@
         <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
         <v>25</v>
@@ -1211,13 +1211,13 @@
         <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>46</v>
@@ -1226,10 +1226,10 @@
         <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>60</v>
@@ -1247,22 +1247,22 @@
         <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>8.800000000000001</v>
@@ -1274,7 +1274,7 @@
         <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX4" t="n">
         <v>14.5</v>
@@ -1286,29 +1286,29 @@
         <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1366,7 +1366,7 @@
         <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
         <v>1.72</v>
@@ -1378,19 +1378,19 @@
         <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
         <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X5" t="n">
         <v>12</v>
@@ -1414,19 +1414,19 @@
         <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AF5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG5" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AH5" t="n">
         <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ5" t="n">
         <v>180</v>
@@ -1444,7 +1444,7 @@
         <v>150</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AP5" t="n">
         <v>10</v>
@@ -1483,16 +1483,16 @@
         <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF5" t="n">
         <v>8.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H6" t="n">
         <v>2.46</v>
       </c>
       <c r="I6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
@@ -1560,37 +1560,37 @@
         <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
         <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
         <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
@@ -1599,10 +1599,10 @@
         <v>48</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>14.5</v>
@@ -1650,7 +1650,7 @@
         <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
@@ -1662,7 +1662,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX6" t="n">
         <v>17.5</v>
@@ -1674,29 +1674,29 @@
         <v>16.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB6" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB6" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BC6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD6" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD6" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
         <v>18.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="G7" t="n">
         <v>1.23</v>
@@ -1739,10 +1739,10 @@
         <v>28</v>
       </c>
       <c r="J7" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>1.22</v>
@@ -1751,34 +1751,34 @@
         <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
         <v>1.53</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
         <v>1.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
         <v>950</v>
@@ -1793,7 +1793,7 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
         <v>970</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
@@ -1817,7 +1817,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AK7" t="n">
         <v>970</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1841,56 +1841,56 @@
         <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.52</v>
+        <v>1.97</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="AX7" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>6.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD7" t="n">
         <v>6.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.52</v>
+        <v>1.97</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>2.72</v>
       </c>
       <c r="G9" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H9" t="n">
         <v>3.05</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J9" t="n">
         <v>2.94</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
         <v>1.51</v>
@@ -2139,7 +2139,7 @@
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
         <v>1.61</v>
@@ -2166,7 +2166,7 @@
         <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
         <v>10</v>
@@ -2196,7 +2196,7 @@
         <v>16.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
         <v>27</v>
@@ -2223,10 +2223,10 @@
         <v>75</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR9" t="n">
         <v>6.6</v>
@@ -2235,16 +2235,16 @@
         <v>42</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
         <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX9" t="n">
         <v>6.2</v>
@@ -2253,22 +2253,22 @@
         <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
         <v>8.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
         <v>8.4</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2324,13 +2324,13 @@
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
         <v>3.3</v>
@@ -2342,7 +2342,7 @@
         <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
         <v>1.31</v>
@@ -2354,10 +2354,10 @@
         <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W10" t="n">
         <v>1.27</v>
@@ -2375,7 +2375,7 @@
         <v>28</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
@@ -2387,10 +2387,10 @@
         <v>26</v>
       </c>
       <c r="AF10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH10" t="n">
         <v>22</v>
@@ -2399,7 +2399,7 @@
         <v>46</v>
       </c>
       <c r="AJ10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="n">
         <v>60</v>
@@ -2447,32 +2447,32 @@
         <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC10" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC10" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF10" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.7</v>
       </c>
       <c r="BG10" t="n">
         <v>13.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.61</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H11" t="n">
         <v>5.1</v>
@@ -2554,7 +2554,7 @@
         <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X11" t="n">
         <v>25</v>
@@ -2605,7 +2605,7 @@
         <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AO11" t="n">
         <v>75</v>
@@ -2617,10 +2617,10 @@
         <v>18.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.3</v>
+        <v>36</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
@@ -2632,7 +2632,7 @@
         <v>17.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX11" t="n">
         <v>9.800000000000001</v>
@@ -2644,7 +2644,7 @@
         <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB11" t="n">
         <v>14.5</v>
@@ -2653,20 +2653,20 @@
         <v>14</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF11" t="n">
         <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
         <v>1.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
         <v>1.23</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="G13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L13" t="n">
         <v>1.23</v>
-      </c>
-      <c r="H13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>25</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.21</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
-        <v>2.78</v>
+        <v>2.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="R13" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="T13" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="U13" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -2951,16 +2951,16 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AD13" t="n">
         <v>950</v>
@@ -2969,92 +2969,92 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
         <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AK13" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM13" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.9</v>
+        <v>3.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>3.15</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
         <v>5.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>3.15</v>
       </c>
       <c r="AX13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB13" t="n">
         <v>7</v>
       </c>
-      <c r="AY13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>4</v>
-      </c>
       <c r="BC13" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>3.15</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>3.15</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
         <v>2.96</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J14" t="n">
         <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.42</v>
@@ -3115,7 +3115,7 @@
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
         <v>2.04</v>
@@ -3130,13 +3130,13 @@
         <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
         <v>1.41</v>
       </c>
       <c r="W14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X14" t="n">
         <v>15</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -3300,16 +3300,16 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
         <v>2.04</v>
@@ -3321,10 +3321,10 @@
         <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
         <v>1.8</v>
@@ -3345,7 +3345,7 @@
         <v>29</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
         <v>8.199999999999999</v>
@@ -3420,19 +3420,19 @@
         <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD15" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF15" t="n">
         <v>40</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -3500,19 +3500,19 @@
         <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P16" t="n">
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -3694,13 +3694,13 @@
         <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
         <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="R17" t="n">
         <v>1.24</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G18" t="n">
         <v>1.76</v>
@@ -3870,19 +3870,19 @@
         <v>5.6</v>
       </c>
       <c r="I18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
         <v>3.55</v>
@@ -3906,7 +3906,7 @@
         <v>1.92</v>
       </c>
       <c r="U18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
         <v>1.19</v>
@@ -3915,7 +3915,7 @@
         <v>2.3</v>
       </c>
       <c r="X18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
         <v>19.5</v>
@@ -3930,7 +3930,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>24</v>
@@ -3957,7 +3957,7 @@
         <v>19</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
         <v>160</v>
@@ -3969,16 +3969,16 @@
         <v>110</v>
       </c>
       <c r="AP18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT18" t="n">
         <v>7.2</v>
@@ -3990,10 +3990,10 @@
         <v>21</v>
       </c>
       <c r="AW18" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY18" t="n">
         <v>9</v>
@@ -4002,7 +4002,7 @@
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BB18" t="n">
         <v>15.5</v>
@@ -4014,17 +4014,17 @@
         <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
         <v>1.5</v>
@@ -4064,7 +4064,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
         <v>4.4</v>
@@ -4073,7 +4073,7 @@
         <v>4.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
@@ -4085,7 +4085,7 @@
         <v>1.33</v>
       </c>
       <c r="P19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
         <v>1.97</v>
@@ -4103,7 +4103,7 @@
         <v>1.67</v>
       </c>
       <c r="V19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
         <v>3</v>
@@ -4115,10 +4115,10 @@
         <v>27</v>
       </c>
       <c r="Z19" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AA19" t="n">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="AB19" t="n">
         <v>7.4</v>
@@ -4127,40 +4127,40 @@
         <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE19" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AF19" t="n">
         <v>8</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
         <v>32</v>
       </c>
       <c r="AI19" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AO19" t="n">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="AP19" t="n">
         <v>11.5</v>
@@ -4169,56 +4169,56 @@
         <v>21</v>
       </c>
       <c r="AR19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV19" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AW19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC19" t="n">
         <v>15</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -4273,16 +4273,16 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
         <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>2.48</v>
       </c>
       <c r="G21" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H21" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I21" t="n">
         <v>3.05</v>
@@ -4458,10 +4458,10 @@
         <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4473,10 +4473,10 @@
         <v>1.27</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R21" t="n">
         <v>1.4</v>
@@ -4500,70 +4500,70 @@
         <v>21</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AC21" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK21" t="n">
         <v>38</v>
       </c>
-      <c r="AF21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK21" t="n">
+      <c r="AL21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO21" t="n">
         <v>34</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>30</v>
       </c>
       <c r="AP21" t="n">
         <v>14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU21" t="n">
         <v>7</v>
@@ -4572,41 +4572,41 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>13.5</v>
       </c>
-      <c r="AY21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>12</v>
-      </c>
       <c r="BA21" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>27</v>
+        <v>6.4</v>
       </c>
       <c r="BC21" t="n">
         <v>19</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BF21" t="n">
         <v>14.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>1.77</v>
       </c>
       <c r="G22" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H22" t="n">
         <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
         <v>4.1</v>
@@ -4688,7 +4688,7 @@
         <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X22" t="n">
         <v>29</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -4855,10 +4855,10 @@
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P23" t="n">
         <v>2.2</v>
@@ -4873,7 +4873,7 @@
         <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U23" t="n">
         <v>2.32</v>
@@ -4885,10 +4885,10 @@
         <v>1.86</v>
       </c>
       <c r="X23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="n">
         <v>36</v>
@@ -4942,10 +4942,10 @@
         <v>3.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS23" t="n">
         <v>4.2</v>
@@ -4960,7 +4960,7 @@
         <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX23" t="n">
         <v>12.5</v>
@@ -4984,7 +4984,7 @@
         <v>4.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF23" t="n">
         <v>8.800000000000001</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>3.45</v>
       </c>
       <c r="I24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
         <v>3.45</v>
@@ -5049,7 +5049,7 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
         <v>1.32</v>
@@ -5058,19 +5058,19 @@
         <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T24" t="n">
         <v>1.76</v>
       </c>
       <c r="U24" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
         <v>1.37</v>
@@ -5085,7 +5085,7 @@
         <v>16.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
         <v>80</v>
@@ -5097,7 +5097,7 @@
         <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE24" t="n">
         <v>55</v>
@@ -5112,7 +5112,7 @@
         <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
         <v>36</v>
@@ -5130,7 +5130,7 @@
         <v>22</v>
       </c>
       <c r="AO24" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP24" t="n">
         <v>12.5</v>
@@ -5139,10 +5139,10 @@
         <v>12</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT24" t="n">
         <v>8.800000000000001</v>
@@ -5154,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX24" t="n">
         <v>12.5</v>
@@ -5163,22 +5163,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BB24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD24" t="n">
         <v>3.95</v>
       </c>
-      <c r="BC24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4</v>
-      </c>
       <c r="BE24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF24" t="n">
         <v>12.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -5252,13 +5252,13 @@
         <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
         <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -5437,13 +5437,13 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="O26" t="n">
         <v>1.22</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -5631,22 +5631,22 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="O27" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
         <v>1.24</v>
       </c>
       <c r="S27" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -5825,22 +5825,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P28" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -6019,13 +6019,13 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O29" t="n">
         <v>1.2</v>
       </c>
       <c r="P29" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Q29" t="n">
         <v>1.2</v>
@@ -6034,7 +6034,7 @@
         <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="T29" t="n">
         <v>1.11</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="G30" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H30" t="n">
         <v>2.92</v>
       </c>
       <c r="I30" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J30" t="n">
         <v>3.3</v>
@@ -6219,7 +6219,7 @@
         <v>1.42</v>
       </c>
       <c r="P30" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q30" t="n">
         <v>2.26</v>
@@ -6228,10 +6228,10 @@
         <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
         <v>2.02</v>
@@ -6240,7 +6240,7 @@
         <v>1.51</v>
       </c>
       <c r="W30" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X30" t="n">
         <v>11</v>
@@ -6273,13 +6273,13 @@
         <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ30" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK30" t="n">
         <v>34</v>
@@ -6297,13 +6297,13 @@
         <v>36</v>
       </c>
       <c r="AP30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ30" t="n">
         <v>9.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS30" t="n">
         <v>42</v>
@@ -6321,7 +6321,7 @@
         <v>32</v>
       </c>
       <c r="AX30" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
         <v>11.5</v>
@@ -6330,10 +6330,10 @@
         <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC30" t="n">
         <v>30</v>
@@ -6345,14 +6345,14 @@
         <v>40</v>
       </c>
       <c r="BF30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG30" t="n">
         <v>32</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G31" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H31" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I31" t="n">
         <v>3.1</v>
@@ -6398,7 +6398,7 @@
         <v>3.2</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.34</v>
@@ -6419,7 +6419,7 @@
         <v>1.95</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
         <v>3.3</v>
@@ -6431,7 +6431,7 @@
         <v>2.24</v>
       </c>
       <c r="V31" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W31" t="n">
         <v>1.53</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -6643,10 +6643,10 @@
         <v>55</v>
       </c>
       <c r="AB32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD32" t="n">
         <v>16</v>
@@ -6679,7 +6679,7 @@
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO32" t="n">
         <v>23</v>
@@ -6694,7 +6694,7 @@
         <v>15.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT32" t="n">
         <v>10</v>
@@ -6718,19 +6718,19 @@
         <v>11</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC32" t="n">
         <v>18</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF32" t="n">
         <v>11.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -6771,19 +6771,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="G33" t="n">
-        <v>990</v>
+        <v>1.54</v>
       </c>
       <c r="H33" t="n">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="I33" t="n">
         <v>990</v>
       </c>
       <c r="J33" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="K33" t="n">
         <v>950</v>
@@ -6822,7 +6822,7 @@
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -6989,22 +6989,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O34" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P34" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="R34" t="n">
         <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -7168,13 +7168,13 @@
         <v>3.95</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>3.4</v>
       </c>
       <c r="K35" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L35" t="n">
         <v>1.39</v>
@@ -7207,10 +7207,10 @@
         <v>2.28</v>
       </c>
       <c r="V35" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W35" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X35" t="n">
         <v>15</v>
@@ -7231,10 +7231,10 @@
         <v>7.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF35" t="n">
         <v>14</v>
@@ -7246,7 +7246,7 @@
         <v>16.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ35" t="n">
         <v>26</v>
@@ -7261,7 +7261,7 @@
         <v>85</v>
       </c>
       <c r="AN35" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO35" t="n">
         <v>40</v>
@@ -7318,11 +7318,11 @@
         <v>13</v>
       </c>
       <c r="BG35" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
         <v>1.26</v>
       </c>
       <c r="O36" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="P36" t="n">
         <v>1.25</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>2.78</v>
       </c>
       <c r="G37" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>3</v>
@@ -7595,10 +7595,10 @@
         <v>1.66</v>
       </c>
       <c r="V37" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W37" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X37" t="n">
         <v>7.4</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G39" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H39" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I39" t="n">
         <v>2.64</v>
@@ -7950,7 +7950,7 @@
         <v>3.75</v>
       </c>
       <c r="K39" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,7 +7959,7 @@
         <v>1.06</v>
       </c>
       <c r="N39" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O39" t="n">
         <v>1.27</v>
@@ -7968,7 +7968,7 @@
         <v>2.18</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R39" t="n">
         <v>1.46</v>
@@ -7983,7 +7983,7 @@
         <v>2.4</v>
       </c>
       <c r="V39" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W39" t="n">
         <v>1.53</v>
@@ -8028,7 +8028,7 @@
         <v>44</v>
       </c>
       <c r="AK39" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL39" t="n">
         <v>38</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G40" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H40" t="n">
         <v>2.52</v>
       </c>
       <c r="I40" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J40" t="n">
         <v>3.05</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L40" t="n">
         <v>1.42</v>
@@ -8177,7 +8177,7 @@
         <v>1.94</v>
       </c>
       <c r="V40" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W40" t="n">
         <v>1.42</v>
@@ -8204,7 +8204,7 @@
         <v>970</v>
       </c>
       <c r="AE40" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF40" t="n">
         <v>24</v>
@@ -8246,10 +8246,10 @@
         <v>4.1</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT40" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU40" t="n">
         <v>5.8</v>
@@ -8270,13 +8270,13 @@
         <v>4.2</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB40" t="n">
         <v>4.8</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD40" t="n">
         <v>4.8</v>
@@ -8288,11 +8288,11 @@
         <v>4.7</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G41" t="n">
         <v>3.05</v>
       </c>
       <c r="H41" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="I41" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>3.3</v>
       </c>
       <c r="K41" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L41" t="n">
         <v>1.33</v>
@@ -8347,7 +8347,7 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
         <v>1.33</v>
@@ -8356,7 +8356,7 @@
         <v>1.74</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R41" t="n">
         <v>1.26</v>
@@ -8371,122 +8371,122 @@
         <v>1.11</v>
       </c>
       <c r="V41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.49</v>
       </c>
-      <c r="W41" t="n">
-        <v>1.48</v>
-      </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL41" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM41" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -8532,10 +8532,10 @@
         <v>3.5</v>
       </c>
       <c r="K42" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L42" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M42" t="n">
         <v>1.07</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -8711,31 +8711,31 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="G43" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J43" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K43" t="n">
         <v>4.2</v>
       </c>
       <c r="L43" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M43" t="n">
         <v>1.07</v>
       </c>
       <c r="N43" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O43" t="n">
         <v>1.33</v>
@@ -8750,22 +8750,22 @@
         <v>1.34</v>
       </c>
       <c r="S43" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="U43" t="n">
         <v>1.97</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W43" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X43" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Y43" t="n">
         <v>970</v>
@@ -8774,7 +8774,7 @@
         <v>48</v>
       </c>
       <c r="AA43" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB43" t="n">
         <v>970</v>
@@ -8810,7 +8810,7 @@
         <v>44</v>
       </c>
       <c r="AM43" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN43" t="n">
         <v>14.5</v>
@@ -8828,13 +8828,13 @@
         <v>5.8</v>
       </c>
       <c r="AS43" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AV43" t="n">
         <v>5.2</v>
@@ -8843,7 +8843,7 @@
         <v>6.2</v>
       </c>
       <c r="AX43" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY43" t="n">
         <v>4.2</v>
@@ -8855,16 +8855,16 @@
         <v>6.2</v>
       </c>
       <c r="BB43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC43" t="n">
         <v>5.2</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE43" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BF43" t="n">
         <v>9.800000000000001</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -8917,13 +8917,13 @@
         <v>5.9</v>
       </c>
       <c r="J44" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K44" t="n">
         <v>4.3</v>
       </c>
       <c r="L44" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M44" t="n">
         <v>1.07</v>
@@ -8938,16 +8938,16 @@
         <v>1.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R44" t="n">
         <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T44" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U44" t="n">
         <v>1.94</v>
@@ -8956,22 +8956,22 @@
         <v>1.2</v>
       </c>
       <c r="W44" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X44" t="n">
         <v>17.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="Z44" t="n">
         <v>50</v>
       </c>
       <c r="AA44" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB44" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC44" t="n">
         <v>9.199999999999999</v>
@@ -8983,7 +8983,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG44" t="n">
         <v>12</v>
@@ -8998,34 +8998,34 @@
         <v>23</v>
       </c>
       <c r="AK44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL44" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM44" t="n">
         <v>150</v>
       </c>
       <c r="AN44" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO44" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP44" t="n">
         <v>12</v>
       </c>
       <c r="AQ44" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR44" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU44" t="n">
         <v>7.6</v>
@@ -9034,7 +9034,7 @@
         <v>17.5</v>
       </c>
       <c r="AW44" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AX44" t="n">
         <v>9</v>
@@ -9043,32 +9043,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ44" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA44" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BB44" t="n">
         <v>16</v>
       </c>
       <c r="BC44" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF44" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG44" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
         <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="V45" t="n">
         <v>1.25</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O46" t="n">
         <v>1.17</v>
@@ -9332,7 +9332,7 @@
         <v>1.24</v>
       </c>
       <c r="S46" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="T46" t="n">
         <v>1.11</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O47" t="n">
         <v>1.18</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -9681,16 +9681,16 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G48" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="H48" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J48" t="n">
         <v>4.8</v>
@@ -9708,10 +9708,10 @@
         <v>5</v>
       </c>
       <c r="O48" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P48" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q48" t="n">
         <v>1.59</v>
@@ -9720,19 +9720,19 @@
         <v>1.55</v>
       </c>
       <c r="S48" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="T48" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="U48" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V48" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W48" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="X48" t="n">
         <v>950</v>
@@ -9741,10 +9741,10 @@
         <v>950</v>
       </c>
       <c r="Z48" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA48" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB48" t="n">
         <v>11.5</v>
@@ -9753,22 +9753,22 @@
         <v>13.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AE48" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF48" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG48" t="n">
         <v>12</v>
       </c>
       <c r="AH48" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI48" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ48" t="n">
         <v>13.5</v>
@@ -9777,74 +9777,74 @@
         <v>16.5</v>
       </c>
       <c r="AL48" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM48" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO48" t="n">
         <v>130</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>150</v>
       </c>
       <c r="AP48" t="n">
         <v>19</v>
       </c>
       <c r="AQ48" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AR48" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS48" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AT48" t="n">
         <v>8</v>
       </c>
       <c r="AU48" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AV48" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW48" t="n">
         <v>5.9</v>
       </c>
-      <c r="AW48" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AX48" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY48" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ48" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BA48" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB48" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC48" t="n">
         <v>11</v>
       </c>
       <c r="BD48" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE48" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>6.6</v>
       </c>
       <c r="BF48" t="n">
         <v>5</v>
       </c>
       <c r="BG48" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
         <v>3.4</v>
       </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J49" t="n">
         <v>3.6</v>
@@ -9917,13 +9917,13 @@
         <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U49" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V49" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W49" t="n">
         <v>1.79</v>
@@ -9971,7 +9971,7 @@
         <v>27</v>
       </c>
       <c r="AL49" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AM49" t="n">
         <v>100</v>
@@ -9989,16 +9989,16 @@
         <v>11</v>
       </c>
       <c r="AR49" t="n">
-        <v>3.75</v>
+        <v>19.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AT49" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU49" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV49" t="n">
         <v>11</v>
@@ -10010,19 +10010,19 @@
         <v>10.5</v>
       </c>
       <c r="AY49" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ49" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA49" t="n">
-        <v>32</v>
+        <v>3.9</v>
       </c>
       <c r="BB49" t="n">
-        <v>3.75</v>
+        <v>19.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD49" t="n">
         <v>3.75</v>
@@ -10034,11 +10034,11 @@
         <v>10.5</v>
       </c>
       <c r="BG49" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G50" t="n">
         <v>1.57</v>
@@ -10078,16 +10078,16 @@
         <v>6.2</v>
       </c>
       <c r="I50" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J50" t="n">
         <v>4.8</v>
       </c>
       <c r="K50" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M50" t="n">
         <v>1.03</v>
@@ -10099,10 +10099,10 @@
         <v>1.2</v>
       </c>
       <c r="P50" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R50" t="n">
         <v>1.6</v>
@@ -10111,10 +10111,10 @@
         <v>2.48</v>
       </c>
       <c r="T50" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U50" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V50" t="n">
         <v>1.17</v>
@@ -10141,7 +10141,7 @@
         <v>11.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AE50" t="n">
         <v>80</v>
@@ -10156,7 +10156,7 @@
         <v>20</v>
       </c>
       <c r="AI50" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ50" t="n">
         <v>15</v>
@@ -10171,10 +10171,10 @@
         <v>95</v>
       </c>
       <c r="AN50" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO50" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP50" t="n">
         <v>21</v>
@@ -10183,10 +10183,10 @@
         <v>22</v>
       </c>
       <c r="AR50" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS50" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT50" t="n">
         <v>10</v>
@@ -10195,7 +10195,7 @@
         <v>10</v>
       </c>
       <c r="AV50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW50" t="n">
         <v>12</v>
@@ -10207,10 +10207,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ50" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA50" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB50" t="n">
         <v>13</v>
@@ -10222,7 +10222,7 @@
         <v>24</v>
       </c>
       <c r="BE50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF50" t="n">
         <v>5.5</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -10263,10 +10263,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G51" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H51" t="n">
         <v>7.6</v>
@@ -10287,34 +10287,34 @@
         <v>1.05</v>
       </c>
       <c r="N51" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O51" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P51" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q51" t="n">
         <v>1.71</v>
       </c>
       <c r="R51" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S51" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T51" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U51" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V51" t="n">
         <v>1.13</v>
       </c>
       <c r="W51" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X51" t="n">
         <v>19</v>
@@ -10323,10 +10323,10 @@
         <v>34</v>
       </c>
       <c r="Z51" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA51" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AB51" t="n">
         <v>11</v>
@@ -10338,25 +10338,25 @@
         <v>30</v>
       </c>
       <c r="AE51" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AF51" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG51" t="n">
         <v>10.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI51" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ51" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK51" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL51" t="n">
         <v>34</v>
@@ -10365,25 +10365,25 @@
         <v>120</v>
       </c>
       <c r="AN51" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AO51" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP51" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ51" t="n">
         <v>24</v>
       </c>
       <c r="AR51" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS51" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AT51" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU51" t="n">
         <v>9.6</v>
@@ -10392,7 +10392,7 @@
         <v>26</v>
       </c>
       <c r="AW51" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX51" t="n">
         <v>8.199999999999999</v>
@@ -10404,7 +10404,7 @@
         <v>21</v>
       </c>
       <c r="BA51" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB51" t="n">
         <v>11.5</v>
@@ -10413,20 +10413,20 @@
         <v>13.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="BE51" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF51" t="n">
         <v>6</v>
       </c>
       <c r="BG51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -10463,52 +10463,52 @@
         <v>4.9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="I52" t="n">
         <v>1.79</v>
       </c>
       <c r="J52" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K52" t="n">
         <v>4.6</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M52" t="n">
         <v>1.04</v>
       </c>
       <c r="N52" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O52" t="n">
         <v>1.19</v>
       </c>
       <c r="P52" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R52" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T52" t="n">
         <v>1.61</v>
       </c>
-      <c r="S52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1.6</v>
-      </c>
       <c r="U52" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V52" t="n">
         <v>2.26</v>
       </c>
       <c r="W52" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X52" t="n">
         <v>950</v>
@@ -10520,13 +10520,13 @@
         <v>14</v>
       </c>
       <c r="AA52" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AB52" t="n">
         <v>950</v>
       </c>
       <c r="AC52" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD52" t="n">
         <v>10.5</v>
@@ -10538,34 +10538,34 @@
         <v>40</v>
       </c>
       <c r="AG52" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH52" t="n">
         <v>17</v>
       </c>
       <c r="AI52" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ52" t="n">
         <v>110</v>
       </c>
       <c r="AK52" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL52" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM52" t="n">
         <v>75</v>
       </c>
       <c r="AN52" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO52" t="n">
         <v>8.4</v>
       </c>
       <c r="AP52" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AQ52" t="n">
         <v>11</v>
@@ -10574,7 +10574,7 @@
         <v>12</v>
       </c>
       <c r="AS52" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AT52" t="n">
         <v>20</v>
@@ -10586,41 +10586,41 @@
         <v>9.4</v>
       </c>
       <c r="AW52" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX52" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AY52" t="n">
         <v>16.5</v>
       </c>
       <c r="AZ52" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BB52" t="n">
         <v>4</v>
       </c>
       <c r="BC52" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BE52" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BF52" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BG52" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
         <v>1.95</v>
       </c>
       <c r="H53" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I53" t="n">
         <v>4.9</v>
@@ -10666,7 +10666,7 @@
         <v>3.65</v>
       </c>
       <c r="K53" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -10717,7 +10717,7 @@
         <v>130</v>
       </c>
       <c r="AB53" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC53" t="n">
         <v>8.4</v>
@@ -10765,10 +10765,10 @@
         <v>11.5</v>
       </c>
       <c r="AR53" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS53" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT53" t="n">
         <v>6.8</v>
@@ -10780,7 +10780,7 @@
         <v>16</v>
       </c>
       <c r="AW53" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AX53" t="n">
         <v>9.800000000000001</v>
@@ -10792,7 +10792,7 @@
         <v>19</v>
       </c>
       <c r="BA53" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB53" t="n">
         <v>19.5</v>
@@ -10801,20 +10801,20 @@
         <v>19.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE53" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF53" t="n">
         <v>14.5</v>
       </c>
       <c r="BG53" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -10851,13 +10851,13 @@
         <v>1.23</v>
       </c>
       <c r="H54" t="n">
+        <v>15</v>
+      </c>
+      <c r="I54" t="n">
         <v>16</v>
       </c>
-      <c r="I54" t="n">
-        <v>17</v>
-      </c>
       <c r="J54" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K54" t="n">
         <v>8.6</v>
@@ -10884,7 +10884,7 @@
         <v>1.86</v>
       </c>
       <c r="S54" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T54" t="n">
         <v>2.08</v>
@@ -10902,7 +10902,7 @@
         <v>38</v>
       </c>
       <c r="Y54" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z54" t="n">
         <v>150</v>
@@ -10914,13 +10914,13 @@
         <v>12.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AD54" t="n">
         <v>55</v>
       </c>
       <c r="AE54" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AF54" t="n">
         <v>8.6</v>
@@ -10929,7 +10929,7 @@
         <v>12</v>
       </c>
       <c r="AH54" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI54" t="n">
         <v>170</v>
@@ -10947,22 +10947,22 @@
         <v>170</v>
       </c>
       <c r="AN54" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AO54" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AP54" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AQ54" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AR54" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AS54" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="AT54" t="n">
         <v>12</v>
@@ -10971,22 +10971,22 @@
         <v>17</v>
       </c>
       <c r="AV54" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AW54" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AX54" t="n">
         <v>8.4</v>
       </c>
       <c r="AY54" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ54" t="n">
         <v>32</v>
       </c>
       <c r="BA54" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="BB54" t="n">
         <v>8.6</v>
@@ -11001,14 +11001,14 @@
         <v>130</v>
       </c>
       <c r="BF54" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BG54" t="n">
         <v>65</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
         <v>3.55</v>
       </c>
       <c r="G55" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H55" t="n">
         <v>2.02</v>
@@ -11054,7 +11054,7 @@
         <v>4.3</v>
       </c>
       <c r="K55" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L55" t="n">
         <v>1.24</v>
@@ -11063,7 +11063,7 @@
         <v>1.03</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O55" t="n">
         <v>1.18</v>
@@ -11072,7 +11072,7 @@
         <v>2.76</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R55" t="n">
         <v>1.71</v>
@@ -11084,16 +11084,16 @@
         <v>1.53</v>
       </c>
       <c r="U55" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V55" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W55" t="n">
         <v>1.37</v>
       </c>
       <c r="X55" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y55" t="n">
         <v>15</v>
@@ -11102,7 +11102,7 @@
         <v>16.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AB55" t="n">
         <v>22</v>
@@ -11129,7 +11129,7 @@
         <v>25</v>
       </c>
       <c r="AJ55" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK55" t="n">
         <v>36</v>
@@ -11171,7 +11171,7 @@
         <v>16.5</v>
       </c>
       <c r="AX55" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY55" t="n">
         <v>14.5</v>
@@ -11183,13 +11183,13 @@
         <v>22</v>
       </c>
       <c r="BB55" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BC55" t="n">
         <v>30</v>
       </c>
       <c r="BD55" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE55" t="n">
         <v>46</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -11233,16 +11233,16 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G56" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H56" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="I56" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="J56" t="n">
         <v>4</v>
@@ -11266,13 +11266,13 @@
         <v>2.78</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R56" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S56" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T56" t="n">
         <v>1.51</v>
@@ -11281,16 +11281,16 @@
         <v>2.82</v>
       </c>
       <c r="V56" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="W56" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X56" t="n">
         <v>25</v>
       </c>
       <c r="Y56" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z56" t="n">
         <v>17.5</v>
@@ -11311,7 +11311,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG56" t="n">
         <v>14.5</v>
@@ -11326,7 +11326,7 @@
         <v>60</v>
       </c>
       <c r="AK56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL56" t="n">
         <v>34</v>
@@ -11338,7 +11338,7 @@
         <v>19.5</v>
       </c>
       <c r="AO56" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP56" t="n">
         <v>23</v>
@@ -11350,10 +11350,10 @@
         <v>16</v>
       </c>
       <c r="AS56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT56" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU56" t="n">
         <v>9</v>
@@ -11362,10 +11362,10 @@
         <v>10.5</v>
       </c>
       <c r="AW56" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX56" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY56" t="n">
         <v>14</v>
@@ -11374,10 +11374,10 @@
         <v>13</v>
       </c>
       <c r="BA56" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB56" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC56" t="n">
         <v>28</v>
@@ -11386,17 +11386,17 @@
         <v>30</v>
       </c>
       <c r="BE56" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF56" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG56" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
         <v>1.13</v>
       </c>
       <c r="N57" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O57" t="n">
         <v>1.54</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -11624,10 +11624,10 @@
         <v>1.75</v>
       </c>
       <c r="G58" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H58" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I58" t="n">
         <v>5.8</v>
@@ -11636,7 +11636,7 @@
         <v>3.55</v>
       </c>
       <c r="K58" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11654,7 +11654,7 @@
         <v>1.87</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R58" t="n">
         <v>1.13</v>
@@ -11672,7 +11672,7 @@
         <v>1.2</v>
       </c>
       <c r="W58" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X58" t="n">
         <v>1000</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -11815,16 +11815,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="G59" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H59" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I59" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>3.05</v>
@@ -11839,7 +11839,7 @@
         <v>1.13</v>
       </c>
       <c r="N59" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O59" t="n">
         <v>1.54</v>
@@ -11863,13 +11863,13 @@
         <v>1.79</v>
       </c>
       <c r="V59" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W59" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X59" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y59" t="n">
         <v>13</v>
@@ -11881,10 +11881,10 @@
         <v>110</v>
       </c>
       <c r="AB59" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC59" t="n">
         <v>970</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AD59" t="n">
         <v>970</v>
@@ -11929,56 +11929,56 @@
         <v>10</v>
       </c>
       <c r="AR59" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS59" t="n">
         <v>6.6</v>
       </c>
       <c r="AT59" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="AU59" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AV59" t="n">
         <v>13.5</v>
       </c>
       <c r="AW59" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX59" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY59" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ59" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA59" t="n">
         <v>6.6</v>
       </c>
       <c r="BB59" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC59" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD59" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE59" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE59" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF59" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG59" t="n">
         <v>6.6</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -12027,13 +12027,13 @@
         <v>3.65</v>
       </c>
       <c r="L60" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M60" t="n">
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O60" t="n">
         <v>1.45</v>
@@ -12045,16 +12045,16 @@
         <v>2.28</v>
       </c>
       <c r="R60" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
       </c>
       <c r="T60" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U60" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V60" t="n">
         <v>1.32</v>
@@ -12063,116 +12063,116 @@
         <v>1.68</v>
       </c>
       <c r="X60" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y60" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z60" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA60" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB60" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC60" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD60" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE60" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF60" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG60" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH60" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI60" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK60" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL60" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM60" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN60" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO60" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU60" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV60" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ60" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA60" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB60" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD60" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG60" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -12206,7 +12206,7 @@
         <v>1.46</v>
       </c>
       <c r="G61" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H61" t="n">
         <v>5</v>
@@ -12215,13 +12215,13 @@
         <v>10.5</v>
       </c>
       <c r="J61" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K61" t="n">
         <v>5.1</v>
       </c>
       <c r="L61" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M61" t="n">
         <v>1.01</v>
@@ -12254,7 +12254,7 @@
         <v>1.1</v>
       </c>
       <c r="W61" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -12403,7 +12403,7 @@
         <v>2.36</v>
       </c>
       <c r="H62" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I62" t="n">
         <v>3.35</v>
@@ -12412,7 +12412,7 @@
         <v>3.65</v>
       </c>
       <c r="K62" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L62" t="n">
         <v>1.36</v>
@@ -12448,7 +12448,7 @@
         <v>1.42</v>
       </c>
       <c r="W62" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X62" t="n">
         <v>21</v>
@@ -12466,7 +12466,7 @@
         <v>14</v>
       </c>
       <c r="AC62" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD62" t="n">
         <v>16.5</v>
@@ -12514,7 +12514,7 @@
         <v>21</v>
       </c>
       <c r="AS62" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT62" t="n">
         <v>10.5</v>
@@ -12526,7 +12526,7 @@
         <v>12</v>
       </c>
       <c r="AW62" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AX62" t="n">
         <v>14.5</v>
@@ -12538,29 +12538,29 @@
         <v>14</v>
       </c>
       <c r="BA62" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB62" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BC62" t="n">
         <v>20</v>
       </c>
       <c r="BD62" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE62" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE62" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BF62" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG62" t="n">
         <v>20</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12594,7 @@
         <v>1.8</v>
       </c>
       <c r="G63" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="H63" t="n">
         <v>4.3</v>
@@ -12606,22 +12606,22 @@
         <v>2.96</v>
       </c>
       <c r="K63" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L63" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M63" t="n">
         <v>1.09</v>
       </c>
       <c r="N63" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="O63" t="n">
         <v>1.41</v>
       </c>
       <c r="P63" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q63" t="n">
         <v>2.06</v>
@@ -12630,7 +12630,7 @@
         <v>1.25</v>
       </c>
       <c r="S63" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T63" t="n">
         <v>1.98</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -12791,10 +12791,10 @@
         <v>2.98</v>
       </c>
       <c r="H64" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J64" t="n">
         <v>3.95</v>
@@ -12815,7 +12815,7 @@
         <v>1.17</v>
       </c>
       <c r="P64" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q64" t="n">
         <v>1.52</v>
@@ -12824,22 +12824,22 @@
         <v>1.71</v>
       </c>
       <c r="S64" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T64" t="n">
         <v>1.5</v>
       </c>
       <c r="U64" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V64" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W64" t="n">
         <v>1.51</v>
       </c>
       <c r="X64" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y64" t="n">
         <v>18.5</v>
@@ -12854,55 +12854,55 @@
         <v>20</v>
       </c>
       <c r="AC64" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD64" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE64" t="n">
         <v>26</v>
       </c>
       <c r="AF64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG64" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH64" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI64" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ64" t="n">
         <v>50</v>
       </c>
       <c r="AK64" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL64" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM64" t="n">
         <v>60</v>
       </c>
       <c r="AN64" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO64" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AP64" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR64" t="n">
         <v>18</v>
       </c>
       <c r="AS64" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AT64" t="n">
         <v>16</v>
@@ -12923,32 +12923,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ64" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA64" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB64" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC64" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BD64" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE64" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BF64" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG64" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -12979,13 +12979,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H65" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I65" t="n">
         <v>3.9</v>
@@ -13012,7 +13012,7 @@
         <v>2.52</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R65" t="n">
         <v>1.61</v>
@@ -13021,19 +13021,19 @@
         <v>2.5</v>
       </c>
       <c r="T65" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U65" t="n">
         <v>2.54</v>
       </c>
       <c r="V65" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W65" t="n">
         <v>1.94</v>
       </c>
       <c r="X65" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Y65" t="n">
         <v>24</v>
@@ -13045,13 +13045,13 @@
         <v>80</v>
       </c>
       <c r="AB65" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC65" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD65" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE65" t="n">
         <v>44</v>
@@ -13060,10 +13060,10 @@
         <v>19</v>
       </c>
       <c r="AG65" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH65" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI65" t="n">
         <v>46</v>
@@ -13072,7 +13072,7 @@
         <v>29</v>
       </c>
       <c r="AK65" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL65" t="n">
         <v>34</v>
@@ -13090,37 +13090,37 @@
         <v>20</v>
       </c>
       <c r="AQ65" t="n">
-        <v>16.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR65" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AS65" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT65" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU65" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV65" t="n">
         <v>13.5</v>
       </c>
       <c r="AW65" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AX65" t="n">
         <v>13</v>
       </c>
       <c r="AY65" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ65" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA65" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BB65" t="n">
         <v>20</v>
@@ -13129,20 +13129,20 @@
         <v>16</v>
       </c>
       <c r="BD65" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BE65" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF65" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG65" t="n">
         <v>19.5</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -13176,10 +13176,10 @@
         <v>3.15</v>
       </c>
       <c r="G66" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H66" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I66" t="n">
         <v>2.2</v>
@@ -13188,7 +13188,7 @@
         <v>4.3</v>
       </c>
       <c r="K66" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L66" t="n">
         <v>1.21</v>
@@ -13200,19 +13200,19 @@
         <v>8.6</v>
       </c>
       <c r="O66" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P66" t="n">
         <v>3.55</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R66" t="n">
         <v>2.04</v>
       </c>
       <c r="S66" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="T66" t="n">
         <v>1.4</v>
@@ -13275,19 +13275,19 @@
         <v>46</v>
       </c>
       <c r="AN66" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO66" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AP66" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ66" t="n">
         <v>15</v>
       </c>
       <c r="AR66" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AS66" t="n">
         <v>21</v>
@@ -13299,16 +13299,16 @@
         <v>10.5</v>
       </c>
       <c r="AV66" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AW66" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY66" t="n">
         <v>14</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>11.5</v>
       </c>
       <c r="AZ66" t="n">
         <v>12</v>
@@ -13317,26 +13317,26 @@
         <v>16.5</v>
       </c>
       <c r="BB66" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BC66" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD66" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE66" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF66" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG66" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -13367,10 +13367,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G67" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H67" t="n">
         <v>2.6</v>
@@ -13412,13 +13412,13 @@
         <v>1.67</v>
       </c>
       <c r="U67" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V67" t="n">
         <v>1.61</v>
       </c>
       <c r="W67" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X67" t="n">
         <v>16.5</v>
@@ -13496,10 +13496,10 @@
         <v>11</v>
       </c>
       <c r="AW67" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX67" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY67" t="n">
         <v>11.5</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G68" t="n">
         <v>3.1</v>
@@ -13573,7 +13573,7 @@
         <v>2.6</v>
       </c>
       <c r="J68" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K68" t="n">
         <v>3.75</v>
@@ -13588,7 +13588,7 @@
         <v>4.2</v>
       </c>
       <c r="O68" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P68" t="n">
         <v>2.06</v>
@@ -13597,10 +13597,10 @@
         <v>1.89</v>
       </c>
       <c r="R68" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S68" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T68" t="n">
         <v>1.7</v>
@@ -13690,7 +13690,7 @@
         <v>10.5</v>
       </c>
       <c r="AW68" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX68" t="n">
         <v>18.5</v>
@@ -13717,14 +13717,14 @@
         <v>10</v>
       </c>
       <c r="BF68" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG68" t="n">
         <v>17.5</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -13761,7 +13761,7 @@
         <v>3.3</v>
       </c>
       <c r="H69" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I69" t="n">
         <v>2.36</v>
@@ -13851,19 +13851,19 @@
         <v>34</v>
       </c>
       <c r="AL69" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM69" t="n">
         <v>70</v>
       </c>
       <c r="AN69" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO69" t="n">
         <v>14.5</v>
       </c>
       <c r="AP69" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ69" t="n">
         <v>11</v>
@@ -13872,7 +13872,7 @@
         <v>14.5</v>
       </c>
       <c r="AS69" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT69" t="n">
         <v>13.5</v>
@@ -13893,32 +13893,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ69" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA69" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB69" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC69" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD69" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE69" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF69" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG69" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -13949,7 +13949,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G70" t="n">
         <v>1.58</v>
@@ -13964,7 +13964,7 @@
         <v>4</v>
       </c>
       <c r="K70" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L70" t="n">
         <v>1.01</v>
@@ -13991,7 +13991,7 @@
         <v>4.1</v>
       </c>
       <c r="T70" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U70" t="n">
         <v>1.67</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14185,7 @@
         <v>2.86</v>
       </c>
       <c r="T71" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U71" t="n">
         <v>2.42</v>
@@ -14194,10 +14194,10 @@
         <v>1.61</v>
       </c>
       <c r="W71" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X71" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y71" t="n">
         <v>14</v>
@@ -14212,10 +14212,10 @@
         <v>15</v>
       </c>
       <c r="AC71" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD71" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE71" t="n">
         <v>26</v>
@@ -14224,7 +14224,7 @@
         <v>22</v>
       </c>
       <c r="AG71" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH71" t="n">
         <v>16</v>
@@ -14254,22 +14254,22 @@
         <v>17.5</v>
       </c>
       <c r="AQ71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR71" t="n">
         <v>16.5</v>
       </c>
       <c r="AS71" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT71" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU71" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV71" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW71" t="n">
         <v>21</v>
@@ -14281,32 +14281,32 @@
         <v>11</v>
       </c>
       <c r="AZ71" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA71" t="n">
         <v>27</v>
       </c>
       <c r="BB71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC71" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD71" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE71" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF71" t="n">
         <v>17</v>
       </c>
       <c r="BG71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -14337,22 +14337,22 @@
         </is>
       </c>
       <c r="F72" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J72" t="n">
         <v>3.7</v>
       </c>
-      <c r="G72" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H72" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I72" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J72" t="n">
-        <v>3.75</v>
-      </c>
       <c r="K72" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L72" t="n">
         <v>1.31</v>
@@ -14367,10 +14367,10 @@
         <v>1.2</v>
       </c>
       <c r="P72" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R72" t="n">
         <v>1.6</v>
@@ -14385,43 +14385,43 @@
         <v>2.66</v>
       </c>
       <c r="V72" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="W72" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X72" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y72" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z72" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA72" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB72" t="n">
         <v>23</v>
       </c>
       <c r="AC72" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD72" t="n">
         <v>13</v>
       </c>
       <c r="AE72" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF72" t="n">
         <v>36</v>
       </c>
       <c r="AG72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH72" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI72" t="n">
         <v>32</v>
@@ -14448,28 +14448,28 @@
         <v>19.5</v>
       </c>
       <c r="AQ72" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="AR72" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="AS72" t="n">
         <v>21</v>
       </c>
       <c r="AT72" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="AU72" t="n">
         <v>8</v>
       </c>
       <c r="AV72" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW72" t="n">
-        <v>16</v>
+        <v>5.2</v>
       </c>
       <c r="AX72" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY72" t="n">
         <v>13.5</v>
@@ -14478,29 +14478,29 @@
         <v>12.5</v>
       </c>
       <c r="BA72" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BB72" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC72" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BD72" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BE72" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BF72" t="n">
         <v>20</v>
       </c>
       <c r="BG72" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -14531,16 +14531,16 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G73" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H73" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="I73" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J73" t="n">
         <v>4.1</v>
@@ -14570,19 +14570,19 @@
         <v>1.71</v>
       </c>
       <c r="S73" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T73" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U73" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V73" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W73" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X73" t="n">
         <v>32</v>
@@ -14591,10 +14591,10 @@
         <v>17.5</v>
       </c>
       <c r="Z73" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA73" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB73" t="n">
         <v>26</v>
@@ -14639,19 +14639,19 @@
         <v>8.6</v>
       </c>
       <c r="AP73" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ73" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR73" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS73" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT73" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU73" t="n">
         <v>9.4</v>
@@ -14663,7 +14663,7 @@
         <v>15.5</v>
       </c>
       <c r="AX73" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY73" t="n">
         <v>14</v>
@@ -14672,29 +14672,29 @@
         <v>13</v>
       </c>
       <c r="BA73" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF73" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB73" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC73" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD73" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE73" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF73" t="n">
-        <v>5</v>
-      </c>
       <c r="BG73" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G74" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H74" t="n">
         <v>4.4</v>
@@ -14737,10 +14737,10 @@
         <v>4.8</v>
       </c>
       <c r="J74" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K74" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L74" t="n">
         <v>1.33</v>
@@ -14767,16 +14767,16 @@
         <v>2.74</v>
       </c>
       <c r="T74" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U74" t="n">
         <v>2.28</v>
       </c>
       <c r="V74" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W74" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X74" t="n">
         <v>26</v>
@@ -14794,19 +14794,19 @@
         <v>12</v>
       </c>
       <c r="AC74" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD74" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AE74" t="n">
         <v>55</v>
       </c>
       <c r="AF74" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG74" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH74" t="n">
         <v>18</v>
@@ -14827,68 +14827,68 @@
         <v>80</v>
       </c>
       <c r="AN74" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO74" t="n">
         <v>48</v>
       </c>
       <c r="AP74" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AQ74" t="n">
         <v>17.5</v>
       </c>
       <c r="AR74" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS74" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT74" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU74" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV74" t="n">
         <v>15.5</v>
       </c>
       <c r="AW74" t="n">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="AX74" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY74" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ74" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA74" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BB74" t="n">
-        <v>5.7</v>
+        <v>17</v>
       </c>
       <c r="BC74" t="n">
         <v>15</v>
       </c>
       <c r="BD74" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BE74" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF74" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG74" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -14949,7 +14949,7 @@
         <v>1.31</v>
       </c>
       <c r="P75" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q75" t="n">
         <v>1.9</v>
@@ -15072,7 +15072,7 @@
         <v>2.42</v>
       </c>
       <c r="BE75" t="n">
-        <v>1.67</v>
+        <v>2.96</v>
       </c>
       <c r="BF75" t="n">
         <v>11.5</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15113,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G76" t="n">
         <v>1.93</v>
@@ -15137,7 +15137,7 @@
         <v>1.03</v>
       </c>
       <c r="N76" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O76" t="n">
         <v>1.19</v>
@@ -15179,13 +15179,13 @@
         <v>85</v>
       </c>
       <c r="AB76" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC76" t="n">
         <v>10.5</v>
       </c>
       <c r="AD76" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE76" t="n">
         <v>46</v>
@@ -15194,10 +15194,10 @@
         <v>15.5</v>
       </c>
       <c r="AG76" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH76" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI76" t="n">
         <v>46</v>
@@ -15215,7 +15215,7 @@
         <v>60</v>
       </c>
       <c r="AN76" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO76" t="n">
         <v>38</v>
@@ -15227,13 +15227,13 @@
         <v>19</v>
       </c>
       <c r="AR76" t="n">
-        <v>25</v>
+        <v>7.8</v>
       </c>
       <c r="AS76" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT76" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU76" t="n">
         <v>8.6</v>
@@ -15248,7 +15248,7 @@
         <v>12.5</v>
       </c>
       <c r="AY76" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ76" t="n">
         <v>13</v>
@@ -15257,26 +15257,26 @@
         <v>30</v>
       </c>
       <c r="BB76" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC76" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BD76" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE76" t="n">
         <v>40</v>
       </c>
       <c r="BF76" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG76" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -15313,13 +15313,13 @@
         <v>1.76</v>
       </c>
       <c r="H77" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I77" t="n">
         <v>5.1</v>
       </c>
       <c r="J77" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K77" t="n">
         <v>4.8</v>
@@ -15337,22 +15337,22 @@
         <v>1.17</v>
       </c>
       <c r="P77" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q77" t="n">
         <v>1.52</v>
       </c>
       <c r="R77" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S77" t="n">
         <v>2.32</v>
       </c>
       <c r="T77" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U77" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V77" t="n">
         <v>1.25</v>
@@ -15373,7 +15373,7 @@
         <v>120</v>
       </c>
       <c r="AB77" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC77" t="n">
         <v>11.5</v>
@@ -15400,34 +15400,34 @@
         <v>19</v>
       </c>
       <c r="AK77" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL77" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM77" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN77" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO77" t="n">
         <v>38</v>
       </c>
       <c r="AP77" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ77" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR77" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="AS77" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT77" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU77" t="n">
         <v>9.800000000000001</v>
@@ -15436,10 +15436,10 @@
         <v>17</v>
       </c>
       <c r="AW77" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX77" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY77" t="n">
         <v>9.4</v>
@@ -15454,23 +15454,23 @@
         <v>16</v>
       </c>
       <c r="BC77" t="n">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD77" t="n">
         <v>18</v>
       </c>
       <c r="BE77" t="n">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="BF77" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BG77" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -15501,10 +15501,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G78" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H78" t="n">
         <v>3.75</v>
@@ -15513,10 +15513,10 @@
         <v>3.95</v>
       </c>
       <c r="J78" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K78" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L78" t="n">
         <v>1.32</v>
@@ -15525,40 +15525,40 @@
         <v>1.04</v>
       </c>
       <c r="N78" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O78" t="n">
         <v>1.21</v>
       </c>
       <c r="P78" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R78" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S78" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T78" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U78" t="n">
         <v>2.52</v>
       </c>
       <c r="V78" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W78" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X78" t="n">
         <v>23</v>
       </c>
       <c r="Y78" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Z78" t="n">
         <v>32</v>
@@ -15567,49 +15567,49 @@
         <v>80</v>
       </c>
       <c r="AB78" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC78" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD78" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE78" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF78" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG78" t="n">
         <v>10.5</v>
       </c>
       <c r="AH78" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI78" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ78" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL78" t="n">
         <v>27</v>
-      </c>
-      <c r="AK78" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL78" t="n">
-        <v>30</v>
       </c>
       <c r="AM78" t="n">
         <v>65</v>
       </c>
       <c r="AN78" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO78" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ78" t="n">
         <v>17</v>
@@ -15618,7 +15618,7 @@
         <v>27</v>
       </c>
       <c r="AS78" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AT78" t="n">
         <v>11</v>
@@ -15642,7 +15642,7 @@
         <v>14.5</v>
       </c>
       <c r="BA78" t="n">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BB78" t="n">
         <v>21</v>
@@ -15657,14 +15657,14 @@
         <v>55</v>
       </c>
       <c r="BF78" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG78" t="n">
         <v>26</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>
@@ -15695,22 +15695,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G79" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H79" t="n">
         <v>3.35</v>
       </c>
       <c r="I79" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J79" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K79" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L79" t="n">
         <v>1.01</v>
@@ -15719,7 +15719,7 @@
         <v>1.02</v>
       </c>
       <c r="N79" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O79" t="n">
         <v>1.25</v>
@@ -15731,25 +15731,25 @@
         <v>1.77</v>
       </c>
       <c r="R79" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S79" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T79" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U79" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V79" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W79" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X79" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y79" t="n">
         <v>1000</v>
@@ -15764,7 +15764,7 @@
         <v>1000</v>
       </c>
       <c r="AC79" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AD79" t="n">
         <v>1000</v>
@@ -15803,62 +15803,62 @@
         <v>1000</v>
       </c>
       <c r="AP79" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR79" t="n">
         <v>1.09</v>
       </c>
-      <c r="AQ79" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AS79" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AU79" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV79" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AW79" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AX79" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AY79" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BA79" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BB79" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BC79" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BD79" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BE79" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BF79" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BG79" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-05-12 04:34:57</t>
+          <t>2026-05-12 06:52:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-13.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G2" t="n">
         <v>2.34</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G3" t="n">
         <v>2.04</v>
@@ -969,7 +969,7 @@
         <v>3.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>2.96</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
@@ -1163,13 +1163,13 @@
         <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
         <v>1.37</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>4.8</v>
       </c>
       <c r="G5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H5" t="n">
         <v>1.79</v>
@@ -1375,7 +1375,7 @@
         <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
         <v>4.2</v>
@@ -1420,31 +1420,31 @@
         <v>46</v>
       </c>
       <c r="AG5" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AK5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL5" t="n">
         <v>110</v>
       </c>
       <c r="AM5" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP5" t="n">
         <v>10</v>
@@ -1471,7 +1471,7 @@
         <v>19</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
         <v>17.5</v>
@@ -1480,29 +1480,29 @@
         <v>18.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
         <v>14</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1653,7 +1653,7 @@
         <v>4.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
@@ -1665,7 +1665,7 @@
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="n">
         <v>11.5</v>
@@ -1674,7 +1674,7 @@
         <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
         <v>4.3</v>
@@ -1683,7 +1683,7 @@
         <v>4.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
         <v>4.2</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>2.1</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>3.75</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>2.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
         <v>1.39</v>
@@ -2527,7 +2527,7 @@
         <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
         <v>1.31</v>
@@ -2554,7 +2554,7 @@
         <v>1.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X11" t="n">
         <v>18.5</v>
@@ -2569,13 +2569,13 @@
         <v>22</v>
       </c>
       <c r="AB11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>22</v>
@@ -2596,7 +2596,7 @@
         <v>85</v>
       </c>
       <c r="AK11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL11" t="n">
         <v>60</v>
@@ -2629,44 +2629,44 @@
         <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW11" t="n">
         <v>14</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE11" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF11" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BG11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H12" t="n">
         <v>3.05</v>
@@ -2730,7 +2730,7 @@
         <v>1.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
         <v>1.16</v>
@@ -2829,10 +2829,10 @@
         <v>8.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="AY12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>8.800000000000001</v>
@@ -2844,7 +2844,7 @@
         <v>8.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BD12" t="n">
         <v>8.800000000000001</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2915,13 @@
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
         <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q13" t="n">
         <v>1.56</v>
@@ -2933,10 +2933,10 @@
         <v>2.48</v>
       </c>
       <c r="T13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
         <v>1.19</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="G15" t="n">
         <v>3.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="J15" t="n">
         <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3327,7 +3327,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W15" t="n">
         <v>1.38</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="G16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H16" t="n">
         <v>13</v>
@@ -3491,7 +3491,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
@@ -3500,31 +3500,31 @@
         <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.34</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
         <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
@@ -3551,7 +3551,7 @@
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG16" t="n">
         <v>14.5</v>
@@ -3581,28 +3581,28 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
         <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT16" t="n">
         <v>7.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX16" t="n">
         <v>6.4</v>
@@ -3611,10 +3611,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
         <v>6.8</v>
@@ -3623,20 +3623,20 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,7 +3691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.9</v>
+        <v>2.22</v>
       </c>
       <c r="O17" t="n">
         <v>1.25</v>
@@ -3703,7 +3703,7 @@
         <v>1.61</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
         <v>2.52</v>
@@ -3715,10 +3715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="H18" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
         <v>3.9</v>
       </c>
       <c r="K18" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3900,7 +3900,7 @@
         <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
         <v>1.28</v>
       </c>
       <c r="O20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P20" t="n">
         <v>1.28</v>
@@ -4288,7 +4288,7 @@
         <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>2.06</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J21" t="n">
         <v>3.3</v>
@@ -4485,10 +4485,10 @@
         <v>3.7</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U21" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>1.78</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>2.38</v>
       </c>
       <c r="G22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H22" t="n">
         <v>2.3</v>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,19 +4661,19 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
         <v>1.01</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
         <v>1.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
         <v>2.56</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.42</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.4</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -4849,31 +4849,31 @@
         <v>5.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R23" t="n">
         <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T23" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U23" t="n">
         <v>2.26</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>990</v>
       </c>
       <c r="H24" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="I24" t="n">
         <v>990</v>
@@ -5052,7 +5052,7 @@
         <v>1.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P24" t="n">
         <v>1.25</v>
@@ -5064,7 +5064,7 @@
         <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -5076,7 +5076,7 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5416,10 +5416,10 @@
         <v>1.5</v>
       </c>
       <c r="G26" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="H26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I26" t="n">
         <v>9.6</v>
@@ -5428,7 +5428,7 @@
         <v>4.3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L26" t="n">
         <v>1.4</v>
@@ -5437,7 +5437,7 @@
         <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.34</v>
@@ -5464,7 +5464,7 @@
         <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="X26" t="n">
         <v>13.5</v>
@@ -5506,7 +5506,7 @@
         <v>14.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="n">
         <v>50</v>
@@ -5524,7 +5524,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR26" t="n">
         <v>55</v>
@@ -5536,7 +5536,7 @@
         <v>6.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV26" t="n">
         <v>24</v>
@@ -5563,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="BD26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BE26" t="n">
         <v>9.800000000000001</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>990</v>
       </c>
       <c r="J27" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K27" t="n">
         <v>950</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
         <v>990</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
         <v>48</v>
       </c>
       <c r="AP31" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="AQ31" t="n">
         <v>4.1</v>
@@ -6515,7 +6515,7 @@
         <v>4.1</v>
       </c>
       <c r="AX31" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
         <v>3.55</v>
@@ -6530,23 +6530,23 @@
         <v>3.75</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.85</v>
+        <v>12.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.95</v>
+        <v>20</v>
       </c>
       <c r="BE31" t="n">
         <v>4.1</v>
       </c>
       <c r="BF31" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG31" t="n">
         <v>4.3</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
         <v>1.32</v>
       </c>
       <c r="P32" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q32" t="n">
         <v>1.96</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
         <v>3.55</v>
       </c>
       <c r="I33" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>3.75</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -7377,13 +7377,13 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O36" t="n">
         <v>1.21</v>
       </c>
       <c r="P36" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q36" t="n">
         <v>1.21</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G37" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H37" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I37" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J37" t="n">
         <v>3.3</v>
@@ -7595,10 +7595,10 @@
         <v>2.02</v>
       </c>
       <c r="V37" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W37" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X37" t="n">
         <v>11</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
         <v>1.34</v>
       </c>
       <c r="S40" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
         <v>1.83</v>
@@ -8177,7 +8177,7 @@
         <v>2.04</v>
       </c>
       <c r="V40" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W40" t="n">
         <v>1.98</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
         <v>3.45</v>
       </c>
       <c r="H42" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I42" t="n">
         <v>2.82</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8711,10 +8711,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G43" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H43" t="n">
         <v>2.58</v>
@@ -8744,13 +8744,13 @@
         <v>2.18</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R43" t="n">
         <v>1.46</v>
       </c>
       <c r="S43" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
         <v>1.68</v>
@@ -8789,7 +8789,7 @@
         <v>26</v>
       </c>
       <c r="AF43" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG43" t="n">
         <v>12.5</v>
@@ -8816,10 +8816,10 @@
         <v>22</v>
       </c>
       <c r="AO43" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ43" t="n">
         <v>12</v>
@@ -8840,7 +8840,7 @@
         <v>11</v>
       </c>
       <c r="AW43" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX43" t="n">
         <v>18.5</v>
@@ -8852,7 +8852,7 @@
         <v>14.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB43" t="n">
         <v>38</v>
@@ -8870,11 +8870,11 @@
         <v>20</v>
       </c>
       <c r="BG43" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8923,7 @@
         <v>4.2</v>
       </c>
       <c r="L44" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M44" t="n">
         <v>1.07</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -9293,13 +9293,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="G46" t="n">
         <v>990</v>
       </c>
       <c r="H46" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="I46" t="n">
         <v>990</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
         <v>2.16</v>
       </c>
       <c r="H47" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
         <v>4.1</v>
@@ -9529,7 +9529,7 @@
         <v>3.25</v>
       </c>
       <c r="T47" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U47" t="n">
         <v>2.28</v>
@@ -9562,7 +9562,7 @@
         <v>15.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF47" t="n">
         <v>14</v>
@@ -9586,7 +9586,7 @@
         <v>34</v>
       </c>
       <c r="AM47" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN47" t="n">
         <v>14.5</v>
@@ -9625,7 +9625,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ47" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA47" t="n">
         <v>44</v>
@@ -9640,7 +9640,7 @@
         <v>30</v>
       </c>
       <c r="BE47" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BF47" t="n">
         <v>13</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
         <v>990</v>
       </c>
       <c r="H49" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="I49" t="n">
         <v>990</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -10096,19 +10096,19 @@
         <v>1.34</v>
       </c>
       <c r="O50" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P50" t="n">
         <v>1.34</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R50" t="n">
         <v>1.24</v>
       </c>
       <c r="S50" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="T50" t="n">
         <v>1.11</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G51" t="n">
         <v>1.85</v>
@@ -10371,7 +10371,7 @@
         <v>120</v>
       </c>
       <c r="AP51" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ51" t="n">
         <v>15</v>
@@ -10419,14 +10419,14 @@
         <v>4.1</v>
       </c>
       <c r="BF51" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
         <v>990</v>
       </c>
       <c r="J53" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K53" t="n">
         <v>950</v>
@@ -10675,22 +10675,22 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="O53" t="n">
         <v>1.17</v>
       </c>
       <c r="P53" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="R53" t="n">
         <v>1.24</v>
       </c>
       <c r="S53" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="T53" t="n">
         <v>1.11</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
         <v>990</v>
       </c>
       <c r="J54" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K54" t="n">
         <v>950</v>
@@ -10896,7 +10896,7 @@
         <v>1.01</v>
       </c>
       <c r="W54" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -11248,7 +11248,7 @@
         <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L56" t="n">
         <v>1.38</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
         <v>1.61</v>
       </c>
       <c r="O57" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P57" t="n">
         <v>1.61</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
         <v>1.68</v>
       </c>
       <c r="U59" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V59" t="n">
         <v>1.37</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -12009,37 +12009,37 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="G60" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H60" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I60" t="n">
         <v>4.9</v>
       </c>
       <c r="J60" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K60" t="n">
         <v>4.6</v>
       </c>
       <c r="L60" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M60" t="n">
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O60" t="n">
         <v>1.31</v>
       </c>
       <c r="P60" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q60" t="n">
         <v>1.96</v>
@@ -12057,10 +12057,10 @@
         <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W60" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
         <v>1.6</v>
       </c>
       <c r="S61" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T61" t="n">
         <v>1.74</v>
@@ -12251,7 +12251,7 @@
         <v>2.22</v>
       </c>
       <c r="V61" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W61" t="n">
         <v>2.72</v>
@@ -12278,7 +12278,7 @@
         <v>24</v>
       </c>
       <c r="AE61" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF61" t="n">
         <v>11</v>
@@ -12293,7 +12293,7 @@
         <v>70</v>
       </c>
       <c r="AJ61" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK61" t="n">
         <v>15.5</v>
@@ -12317,7 +12317,7 @@
         <v>22</v>
       </c>
       <c r="AR61" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS61" t="n">
         <v>13</v>
@@ -12344,7 +12344,7 @@
         <v>17.5</v>
       </c>
       <c r="BA61" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB61" t="n">
         <v>13</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -12403,16 +12403,16 @@
         <v>4.9</v>
       </c>
       <c r="H62" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I62" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="J62" t="n">
         <v>4.3</v>
       </c>
       <c r="K62" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L62" t="n">
         <v>1.25</v>
@@ -12445,7 +12445,7 @@
         <v>2.44</v>
       </c>
       <c r="V62" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="W62" t="n">
         <v>1.25</v>
@@ -12478,7 +12478,7 @@
         <v>40</v>
       </c>
       <c r="AG62" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH62" t="n">
         <v>16.5</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -12594,16 +12594,16 @@
         <v>1.04</v>
       </c>
       <c r="G63" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H63" t="n">
         <v>1.04</v>
       </c>
       <c r="I63" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J63" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="K63" t="n">
         <v>950</v>
@@ -12615,13 +12615,13 @@
         <v>1.01</v>
       </c>
       <c r="N63" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O63" t="n">
         <v>1.25</v>
       </c>
       <c r="P63" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q63" t="n">
         <v>1.25</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
         <v>1.47</v>
       </c>
       <c r="H64" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I64" t="n">
         <v>8.800000000000001</v>
@@ -12824,7 +12824,7 @@
         <v>1.5</v>
       </c>
       <c r="S64" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T64" t="n">
         <v>1.9</v>
@@ -12899,7 +12899,7 @@
         <v>24</v>
       </c>
       <c r="AR64" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="AS64" t="n">
         <v>10</v>
@@ -12938,7 +12938,7 @@
         <v>29</v>
       </c>
       <c r="BE64" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BF64" t="n">
         <v>6</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -13081,7 +13081,7 @@
         <v>150</v>
       </c>
       <c r="AN65" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO65" t="n">
         <v>100</v>
@@ -13096,7 +13096,7 @@
         <v>6.2</v>
       </c>
       <c r="AS65" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT65" t="n">
         <v>6.8</v>
@@ -13120,7 +13120,7 @@
         <v>19</v>
       </c>
       <c r="BA65" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB65" t="n">
         <v>19.5</v>
@@ -13132,17 +13132,17 @@
         <v>6.6</v>
       </c>
       <c r="BE65" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF65" t="n">
         <v>14.5</v>
       </c>
       <c r="BG65" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13182,7 @@
         <v>15.5</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J66" t="n">
         <v>8.4</v>
@@ -13197,7 +13197,7 @@
         <v>1.02</v>
       </c>
       <c r="N66" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O66" t="n">
         <v>1.14</v>
@@ -13290,7 +13290,7 @@
         <v>55</v>
       </c>
       <c r="AS66" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AT66" t="n">
         <v>11.5</v>
@@ -13302,7 +13302,7 @@
         <v>48</v>
       </c>
       <c r="AW66" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AX66" t="n">
         <v>8.4</v>
@@ -13314,7 +13314,7 @@
         <v>32</v>
       </c>
       <c r="BA66" t="n">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="BB66" t="n">
         <v>8.800000000000001</v>
@@ -13332,11 +13332,11 @@
         <v>3.25</v>
       </c>
       <c r="BG66" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
         <v>1.72</v>
       </c>
       <c r="S67" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T67" t="n">
         <v>1.53</v>
@@ -13418,7 +13418,7 @@
         <v>1.94</v>
       </c>
       <c r="W67" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X67" t="n">
         <v>28</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G68" t="n">
         <v>3.45</v>
@@ -13666,7 +13666,7 @@
         <v>20</v>
       </c>
       <c r="AO68" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP68" t="n">
         <v>23</v>
@@ -13714,17 +13714,17 @@
         <v>30</v>
       </c>
       <c r="BE68" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF68" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG68" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -13755,16 +13755,16 @@
         </is>
       </c>
       <c r="F69" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G69" t="n">
         <v>2.3</v>
       </c>
-      <c r="G69" t="n">
-        <v>2.32</v>
-      </c>
       <c r="H69" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I69" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J69" t="n">
         <v>3.25</v>
@@ -13800,10 +13800,10 @@
         <v>2.26</v>
       </c>
       <c r="U69" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V69" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W69" t="n">
         <v>1.76</v>
@@ -13842,10 +13842,10 @@
         <v>25</v>
       </c>
       <c r="AI69" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ69" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK69" t="n">
         <v>30</v>
@@ -13869,10 +13869,10 @@
         <v>9.6</v>
       </c>
       <c r="AR69" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS69" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AT69" t="n">
         <v>7</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -13955,7 +13955,7 @@
         <v>1.97</v>
       </c>
       <c r="H70" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I70" t="n">
         <v>5.8</v>
@@ -13973,7 +13973,7 @@
         <v>1.01</v>
       </c>
       <c r="N70" t="n">
-        <v>3.3</v>
+        <v>2.24</v>
       </c>
       <c r="O70" t="n">
         <v>1.31</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -14415,7 +14415,7 @@
         <v>65</v>
       </c>
       <c r="AF72" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AG72" t="n">
         <v>13</v>
@@ -14448,13 +14448,13 @@
         <v>8</v>
       </c>
       <c r="AQ72" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR72" t="n">
         <v>19.5</v>
       </c>
       <c r="AS72" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT72" t="n">
         <v>6</v>
@@ -14466,7 +14466,7 @@
         <v>12.5</v>
       </c>
       <c r="AW72" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX72" t="n">
         <v>10</v>
@@ -14475,32 +14475,32 @@
         <v>9</v>
       </c>
       <c r="AZ72" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA72" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE72" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BB72" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC72" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD72" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE72" t="n">
-        <v>5.3</v>
       </c>
       <c r="BF72" t="n">
         <v>20</v>
       </c>
       <c r="BG72" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -14567,10 +14567,10 @@
         <v>1.84</v>
       </c>
       <c r="R73" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T73" t="n">
         <v>1.11</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -14740,7 +14740,7 @@
         <v>3.65</v>
       </c>
       <c r="K74" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L74" t="n">
         <v>1.36</v>
@@ -14776,7 +14776,7 @@
         <v>1.42</v>
       </c>
       <c r="W74" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X74" t="n">
         <v>21</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15143,7 @@
         <v>1.17</v>
       </c>
       <c r="P76" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q76" t="n">
         <v>1.52</v>
@@ -15170,7 +15170,7 @@
         <v>34</v>
       </c>
       <c r="Y76" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z76" t="n">
         <v>23</v>
@@ -15194,10 +15194,10 @@
         <v>29</v>
       </c>
       <c r="AG76" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH76" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI76" t="n">
         <v>32</v>
@@ -15221,7 +15221,7 @@
         <v>11</v>
       </c>
       <c r="AP76" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AQ76" t="n">
         <v>14.5</v>
@@ -15230,13 +15230,13 @@
         <v>18</v>
       </c>
       <c r="AS76" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT76" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU76" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV76" t="n">
         <v>10.5</v>
@@ -15257,16 +15257,16 @@
         <v>20</v>
       </c>
       <c r="BB76" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC76" t="n">
         <v>20</v>
       </c>
       <c r="BD76" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE76" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF76" t="n">
         <v>13.5</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -15346,7 +15346,7 @@
         <v>1.62</v>
       </c>
       <c r="S77" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T77" t="n">
         <v>1.58</v>
@@ -15421,10 +15421,10 @@
         <v>4.7</v>
       </c>
       <c r="AR77" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS77" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT77" t="n">
         <v>12</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15528,7 @@
         <v>8.6</v>
       </c>
       <c r="O78" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P78" t="n">
         <v>3.55</v>
@@ -15546,7 +15546,7 @@
         <v>1.4</v>
       </c>
       <c r="U78" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V78" t="n">
         <v>1.83</v>
@@ -15609,7 +15609,7 @@
         <v>7.2</v>
       </c>
       <c r="AP78" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ78" t="n">
         <v>15</v>
@@ -15633,7 +15633,7 @@
         <v>16.5</v>
       </c>
       <c r="AX78" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AY78" t="n">
         <v>14</v>
@@ -15645,7 +15645,7 @@
         <v>16.5</v>
       </c>
       <c r="BB78" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC78" t="n">
         <v>20</v>
@@ -15654,7 +15654,7 @@
         <v>20</v>
       </c>
       <c r="BE78" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF78" t="n">
         <v>12</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -15707,7 +15707,7 @@
         <v>2.64</v>
       </c>
       <c r="J79" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K79" t="n">
         <v>3.7</v>
@@ -15740,7 +15740,7 @@
         <v>1.68</v>
       </c>
       <c r="U79" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V79" t="n">
         <v>1.61</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -15889,13 +15889,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G80" t="n">
         <v>3.05</v>
       </c>
       <c r="H80" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I80" t="n">
         <v>2.6</v>
@@ -15922,13 +15922,13 @@
         <v>2.04</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R80" t="n">
         <v>1.41</v>
       </c>
       <c r="S80" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T80" t="n">
         <v>1.71</v>
@@ -16033,13 +16033,13 @@
         <v>9</v>
       </c>
       <c r="BB80" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC80" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BD80" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE80" t="n">
         <v>10</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -16119,13 +16119,13 @@
         <v>1.74</v>
       </c>
       <c r="R81" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S81" t="n">
         <v>2.92</v>
       </c>
       <c r="T81" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U81" t="n">
         <v>2.42</v>
@@ -16158,7 +16158,7 @@
         <v>13</v>
       </c>
       <c r="AE81" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF81" t="n">
         <v>28</v>
@@ -16191,7 +16191,7 @@
         <v>16.5</v>
       </c>
       <c r="AP81" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ81" t="n">
         <v>11</v>
@@ -16200,7 +16200,7 @@
         <v>14.5</v>
       </c>
       <c r="AS81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT81" t="n">
         <v>13.5</v>
@@ -16212,7 +16212,7 @@
         <v>10</v>
       </c>
       <c r="AW81" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX81" t="n">
         <v>18.5</v>
@@ -16221,22 +16221,22 @@
         <v>12</v>
       </c>
       <c r="AZ81" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB81" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC81" t="n">
         <v>5.3</v>
-      </c>
-      <c r="BC81" t="n">
-        <v>5.1</v>
       </c>
       <c r="BD81" t="n">
         <v>32</v>
       </c>
       <c r="BE81" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF81" t="n">
         <v>21</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -16307,7 +16307,7 @@
         <v>1.41</v>
       </c>
       <c r="P82" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q82" t="n">
         <v>2.2</v>
@@ -16325,7 +16325,7 @@
         <v>1.67</v>
       </c>
       <c r="V82" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W82" t="n">
         <v>2.72</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -16486,7 +16486,7 @@
         <v>3.75</v>
       </c>
       <c r="K83" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L83" t="n">
         <v>1.34</v>
@@ -16507,7 +16507,7 @@
         <v>1.73</v>
       </c>
       <c r="R83" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S83" t="n">
         <v>2.88</v>
@@ -16522,16 +16522,16 @@
         <v>1.61</v>
       </c>
       <c r="W83" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X83" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y83" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z83" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA83" t="n">
         <v>38</v>
@@ -16549,7 +16549,7 @@
         <v>30</v>
       </c>
       <c r="AF83" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG83" t="n">
         <v>13.5</v>
@@ -16588,7 +16588,7 @@
         <v>16</v>
       </c>
       <c r="AS83" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT83" t="n">
         <v>12.5</v>
@@ -16612,29 +16612,29 @@
         <v>13.5</v>
       </c>
       <c r="BA83" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB83" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC83" t="n">
         <v>21</v>
       </c>
       <c r="BD83" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE83" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF83" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BG83" t="n">
         <v>14.5</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -16680,7 +16680,7 @@
         <v>3.75</v>
       </c>
       <c r="K84" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L84" t="n">
         <v>1.3</v>
@@ -16695,7 +16695,7 @@
         <v>1.2</v>
       </c>
       <c r="P84" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q84" t="n">
         <v>1.64</v>
@@ -16713,7 +16713,7 @@
         <v>2.66</v>
       </c>
       <c r="V84" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W84" t="n">
         <v>1.34</v>
@@ -16722,10 +16722,10 @@
         <v>27</v>
       </c>
       <c r="Y84" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z84" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA84" t="n">
         <v>29</v>
@@ -16746,10 +16746,10 @@
         <v>36</v>
       </c>
       <c r="AG84" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AH84" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI84" t="n">
         <v>32</v>
@@ -16779,13 +16779,13 @@
         <v>12</v>
       </c>
       <c r="AR84" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS84" t="n">
         <v>21</v>
       </c>
       <c r="AT84" t="n">
-        <v>15.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU84" t="n">
         <v>8.199999999999999</v>
@@ -16794,13 +16794,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW84" t="n">
-        <v>16</v>
+        <v>5.5</v>
       </c>
       <c r="AX84" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AY84" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ84" t="n">
         <v>12.5</v>
@@ -16809,16 +16809,16 @@
         <v>20</v>
       </c>
       <c r="BB84" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC84" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD84" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE84" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF84" t="n">
         <v>21</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -16862,13 +16862,13 @@
         <v>3.9</v>
       </c>
       <c r="G85" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H85" t="n">
         <v>1.94</v>
       </c>
       <c r="I85" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="J85" t="n">
         <v>4.1</v>
@@ -16886,22 +16886,22 @@
         <v>6</v>
       </c>
       <c r="O85" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P85" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R85" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S85" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T85" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U85" t="n">
         <v>2.62</v>
@@ -16913,13 +16913,13 @@
         <v>1.32</v>
       </c>
       <c r="X85" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y85" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z85" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA85" t="n">
         <v>26</v>
@@ -16928,10 +16928,10 @@
         <v>26</v>
       </c>
       <c r="AC85" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD85" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE85" t="n">
         <v>970</v>
@@ -16943,7 +16943,7 @@
         <v>19</v>
       </c>
       <c r="AH85" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI85" t="n">
         <v>29</v>
@@ -16964,10 +16964,10 @@
         <v>27</v>
       </c>
       <c r="AO85" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AP85" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ85" t="n">
         <v>12.5</v>
@@ -16976,22 +16976,22 @@
         <v>13.5</v>
       </c>
       <c r="AS85" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT85" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="AU85" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV85" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW85" t="n">
         <v>15.5</v>
       </c>
       <c r="AX85" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AY85" t="n">
         <v>14</v>
@@ -17000,19 +17000,19 @@
         <v>13</v>
       </c>
       <c r="BA85" t="n">
-        <v>5.3</v>
+        <v>19.5</v>
       </c>
       <c r="BB85" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC85" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD85" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE85" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BF85" t="n">
         <v>20</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -17059,16 +17059,16 @@
         <v>1.86</v>
       </c>
       <c r="H86" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I86" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J86" t="n">
         <v>4</v>
       </c>
       <c r="K86" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L86" t="n">
         <v>1.33</v>
@@ -17086,13 +17086,13 @@
         <v>2.36</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R86" t="n">
         <v>1.53</v>
       </c>
       <c r="S86" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T86" t="n">
         <v>1.68</v>
@@ -17101,7 +17101,7 @@
         <v>2.3</v>
       </c>
       <c r="V86" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W86" t="n">
         <v>2.16</v>
@@ -17110,7 +17110,7 @@
         <v>26</v>
       </c>
       <c r="Y86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z86" t="n">
         <v>40</v>
@@ -17125,7 +17125,7 @@
         <v>10</v>
       </c>
       <c r="AD86" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE86" t="n">
         <v>60</v>
@@ -17161,16 +17161,16 @@
         <v>48</v>
       </c>
       <c r="AP86" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="AQ86" t="n">
         <v>17.5</v>
       </c>
       <c r="AR86" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS86" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT86" t="n">
         <v>9.800000000000001</v>
@@ -17197,7 +17197,7 @@
         <v>36</v>
       </c>
       <c r="BB86" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="BC86" t="n">
         <v>15.5</v>
@@ -17206,17 +17206,17 @@
         <v>21</v>
       </c>
       <c r="BE86" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF86" t="n">
         <v>8</v>
       </c>
       <c r="BG86" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
         <v>4.1</v>
       </c>
       <c r="L87" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M87" t="n">
         <v>1.06</v>
@@ -17289,13 +17289,13 @@
         <v>3.3</v>
       </c>
       <c r="T87" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U87" t="n">
         <v>2.04</v>
       </c>
       <c r="V87" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W87" t="n">
         <v>1.95</v>
@@ -17370,7 +17370,7 @@
         <v>8</v>
       </c>
       <c r="AU87" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV87" t="n">
         <v>13</v>
@@ -17379,19 +17379,19 @@
         <v>4</v>
       </c>
       <c r="AX87" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY87" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ87" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA87" t="n">
         <v>4</v>
       </c>
       <c r="BB87" t="n">
-        <v>3.65</v>
+        <v>18.5</v>
       </c>
       <c r="BC87" t="n">
         <v>15</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -17543,22 +17543,22 @@
         <v>70</v>
       </c>
       <c r="AN88" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO88" t="n">
         <v>42</v>
       </c>
       <c r="AP88" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AQ88" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AR88" t="n">
-        <v>30</v>
+        <v>4.2</v>
       </c>
       <c r="AS88" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT88" t="n">
         <v>12.5</v>
@@ -17567,10 +17567,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV88" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AW88" t="n">
-        <v>34</v>
+        <v>4.2</v>
       </c>
       <c r="AX88" t="n">
         <v>12</v>
@@ -17585,16 +17585,16 @@
         <v>4.2</v>
       </c>
       <c r="BB88" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BC88" t="n">
         <v>14</v>
       </c>
       <c r="BD88" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE88" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BF88" t="n">
         <v>5.8</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -17635,10 +17635,10 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H89" t="n">
         <v>3.85</v>
@@ -17680,7 +17680,7 @@
         <v>1.61</v>
       </c>
       <c r="U89" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V89" t="n">
         <v>1.33</v>
@@ -17701,7 +17701,7 @@
         <v>80</v>
       </c>
       <c r="AB89" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC89" t="n">
         <v>9.4</v>
@@ -17758,10 +17758,10 @@
         <v>12</v>
       </c>
       <c r="AU89" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV89" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW89" t="n">
         <v>34</v>
@@ -17776,7 +17776,7 @@
         <v>14.5</v>
       </c>
       <c r="BA89" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BB89" t="n">
         <v>21</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
         <v>1.81</v>
       </c>
       <c r="G90" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H90" t="n">
         <v>4.6</v>
@@ -17841,7 +17841,7 @@
         <v>5</v>
       </c>
       <c r="J90" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K90" t="n">
         <v>4.2</v>
@@ -17886,19 +17886,19 @@
         <v>27</v>
       </c>
       <c r="Y90" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Z90" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA90" t="n">
         <v>110</v>
       </c>
       <c r="AB90" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC90" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD90" t="n">
         <v>21</v>
@@ -17910,7 +17910,7 @@
         <v>14.5</v>
       </c>
       <c r="AG90" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH90" t="n">
         <v>16</v>
@@ -17931,31 +17931,31 @@
         <v>70</v>
       </c>
       <c r="AN90" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO90" t="n">
         <v>40</v>
       </c>
       <c r="AP90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ90" t="n">
         <v>19.5</v>
       </c>
       <c r="AR90" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS90" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT90" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU90" t="n">
         <v>8.4</v>
       </c>
       <c r="AV90" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AW90" t="n">
         <v>40</v>
@@ -17964,16 +17964,16 @@
         <v>12</v>
       </c>
       <c r="AY90" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ90" t="n">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA90" t="n">
         <v>30</v>
       </c>
       <c r="BB90" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC90" t="n">
         <v>14.5</v>
@@ -17982,17 +17982,17 @@
         <v>19</v>
       </c>
       <c r="BE90" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF90" t="n">
         <v>7</v>
       </c>
-      <c r="BF90" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG90" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -18023,13 +18023,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G91" t="n">
         <v>2.06</v>
       </c>
       <c r="H91" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I91" t="n">
         <v>5.8</v>
@@ -18038,34 +18038,34 @@
         <v>3.4</v>
       </c>
       <c r="K91" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L91" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M91" t="n">
         <v>1.07</v>
       </c>
       <c r="N91" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O91" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P91" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R91" t="n">
         <v>1.31</v>
       </c>
       <c r="S91" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T91" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U91" t="n">
         <v>1.96</v>
@@ -18077,7 +18077,7 @@
         <v>1.94</v>
       </c>
       <c r="X91" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y91" t="n">
         <v>18.5</v>
@@ -18092,7 +18092,7 @@
         <v>10.5</v>
       </c>
       <c r="AC91" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD91" t="n">
         <v>23</v>
@@ -18101,7 +18101,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG91" t="n">
         <v>12.5</v>
@@ -18113,37 +18113,37 @@
         <v>85</v>
       </c>
       <c r="AJ91" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK91" t="n">
         <v>27</v>
-      </c>
-      <c r="AK91" t="n">
-        <v>26</v>
       </c>
       <c r="AL91" t="n">
         <v>48</v>
       </c>
       <c r="AM91" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN91" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO91" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP91" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ91" t="n">
         <v>11</v>
       </c>
       <c r="AR91" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS91" t="n">
         <v>4.2</v>
       </c>
       <c r="AT91" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU91" t="n">
         <v>6.2</v>
@@ -18173,7 +18173,7 @@
         <v>15.5</v>
       </c>
       <c r="BD91" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE91" t="n">
         <v>4.2</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
@@ -18220,7 +18220,7 @@
         <v>2.14</v>
       </c>
       <c r="G92" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H92" t="n">
         <v>3.5</v>
@@ -18229,52 +18229,52 @@
         <v>3.85</v>
       </c>
       <c r="J92" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K92" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L92" t="n">
         <v>1.01</v>
       </c>
       <c r="M92" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N92" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="O92" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P92" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q92" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q92" t="n">
-        <v>1.9</v>
-      </c>
       <c r="R92" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S92" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T92" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U92" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V92" t="n">
         <v>1.35</v>
       </c>
       <c r="W92" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X92" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y92" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z92" t="n">
         <v>32</v>
@@ -18283,25 +18283,25 @@
         <v>80</v>
       </c>
       <c r="AB92" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC92" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD92" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE92" t="n">
         <v>50</v>
       </c>
       <c r="AF92" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG92" t="n">
         <v>11.5</v>
       </c>
       <c r="AH92" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI92" t="n">
         <v>60</v>
@@ -18319,34 +18319,34 @@
         <v>110</v>
       </c>
       <c r="AN92" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO92" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP92" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ92" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR92" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS92" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT92" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU92" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV92" t="n">
         <v>13</v>
       </c>
       <c r="AW92" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX92" t="n">
         <v>12</v>
@@ -18358,29 +18358,29 @@
         <v>15.5</v>
       </c>
       <c r="BA92" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB92" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BB92" t="n">
-        <v>5.8</v>
       </c>
       <c r="BC92" t="n">
         <v>19.5</v>
       </c>
       <c r="BD92" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE92" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF92" t="n">
         <v>14</v>
       </c>
       <c r="BG92" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-05-12 10:39:24</t>
+          <t>2026-05-12 11:21:48</t>
         </is>
       </c>
     </row>
